--- a/docs/financial-model-5yr-v2.xlsx
+++ b/docs/financial-model-5yr-v2.xlsx
@@ -546,7 +546,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>creatives.exchange — 5-year model v2: two tracks, every revenue source, three scenarios</t>
+          <t>theCreative.exchange — 5-year model v2: two tracks, every revenue source, three scenarios</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>creatives.exchange (this model)</t>
+          <t>theCreative.exchange (this model)</t>
         </is>
       </c>
       <c r="B15" s="11" t="inlineStr">

--- a/docs/financial-model-5yr-v2.xlsx
+++ b/docs/financial-model-5yr-v2.xlsx
@@ -122,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -169,6 +169,7 @@
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -622,14 +623,14 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>4. Results (computed 2026-09-30). Conservative = a San Diego house community with a few churches: $17k → $264k platform revenue over five years, never breaks even, founder pay $0/$0/$24k. Base = San Diego plus partner communities nationally through the mapped networks, plus organization seats: $36k / $132k / $361k / $777k / $1.42M, cumulative cash need peaks at $339k in Y4, breakeven in Y5, 4,500 members and 31 communities by Y3. Fundable = the Base with a funded team from day one and three metros by Y4: $80k / $310k / $1.0M / $2.4M / $5.3M, profitable in Y3, peak cash need $314k.</t>
+          <t>4. Results (updated 2026-09-30 after raising Base org seat packs to match the founder's 5,000-10,000 member estimate for schools and organizations). Conservative = a San Diego house community with a few churches: $17k → $264k platform revenue over five years, never breaks even, founder pay $0/$0/$24k. Base = San Diego plus partner communities nationally through the mapped networks, plus seats bought by schools, universities, churches and organizations: $36k / $133k / $385k / $810k / $1.47M, cumulative cash need peaks at $286k in Y4, annual EBITDA turns positive in Y5, 5,700 paying and covered members and 31 communities by Y3. Fundable = the Base with a funded team from day one and three metros by Y4: $80k / $310k / $996k / $2.4M / $5.3M, profitable in Y3, peak cash need $314k.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>4b. The market-sizing research (docs/funding/market-sizing.md) says San Diego alone supports about 1,000 paying INDIVIDUAL members in three years. The Conservative case matches that (1,270 paying and covered members in Y3). Everything above it comes from organization seat packs, partner communities outside San Diego, and paid plans, so the Base and Fundable cases are bets on partners, not on San Diego individuals.</t>
+          <t>4b. The market-sizing research (docs/funding/market-sizing.md) says San Diego alone supports about 1,000 paying INDIVIDUAL members in three years; the Conservative case matches that (1,270 paying and covered members in Y3). The founder estimates 5,000-10,000 members in three years once schools, universities, churches and other organizations buy seats (estimate not yet sourced; see the Market sheet). The Base case sits inside that range (5,700 in Y3), Fundable above it (12,700). Note that members are not revenue: an organization-bought seat earns the platform about $10 a year in fees plus the backings and classes its holder buys, so 1,200 extra Base seats added only about $24k of Y3 revenue. Revenue is driven by backing and class volume, partner plans and sponsorships.</t>
         </is>
       </c>
     </row>
@@ -646,7 +647,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>VALUES: this file was built with openpyxl and its formulas were evaluated with a Python formula engine (pycel; 722 formulas, 0 errors in every scenario) because LibreOffice is not available in the build sandbox. Excel and Google Sheets recalculate every formula on open, so what you see is live.</t>
+          <t>VALUES: this file was built with openpyxl and its formulas were evaluated with a Python formula engine (pycel; 724 formulas, 0 errors in every scenario) because LibreOffice is not available in the build sandbox. Excel and Google Sheets recalculate every formula on open, so what you see is live.</t>
         </is>
       </c>
     </row>
@@ -2540,7 +2541,7 @@
       </c>
       <c r="H84" s="8" t="inlineStr">
         <is>
-          <t>Churches and orgs buying seats inside partner communities; platform keeps 10% of these dues</t>
+          <t>Schools, universities, churches and other organizations buying seats for their people; platform keeps 10% of these dues. Base raised 2026-09-30 (Y3 800 to 2,000) to match the founder estimate of 5,000-10,000 members in three years</t>
         </is>
       </c>
     </row>
@@ -2555,16 +2556,16 @@
         <v>0</v>
       </c>
       <c r="D85" s="18" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E85" s="18" t="n">
-        <v>800</v>
+        <v>2000</v>
       </c>
       <c r="F85" s="18" t="n">
-        <v>2000</v>
+        <v>3500</v>
       </c>
       <c r="G85" s="18" t="n">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="H85" s="7" t="n"/>
     </row>
@@ -2605,19 +2606,19 @@
       </c>
       <c r="D87" s="19">
         <f>CHOOSE(Inputs!$B$23,D84,D85,D86)</f>
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E87" s="19">
         <f>CHOOSE(Inputs!$B$23,E84,E85,E86)</f>
-        <v>800</v>
+        <v>2000</v>
       </c>
       <c r="F87" s="19">
         <f>CHOOSE(Inputs!$B$23,F84,F85,F86)</f>
-        <v>2000</v>
+        <v>3500</v>
       </c>
       <c r="G87" s="19">
         <f>CHOOSE(Inputs!$B$23,G84,G85,G86)</f>
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="H87" s="7" t="n"/>
     </row>
@@ -5846,19 +5847,19 @@
       </c>
       <c r="C8" s="24">
         <f>Inputs!$D$87</f>
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="D8" s="24">
         <f>Inputs!$E$87</f>
-        <v>800</v>
+        <v>2000</v>
       </c>
       <c r="E8" s="24">
         <f>Inputs!$F$87</f>
-        <v>2000</v>
+        <v>3500</v>
       </c>
       <c r="F8" s="24">
         <f>Inputs!$G$87</f>
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="G8" s="7" t="n"/>
     </row>
@@ -6156,19 +6157,19 @@
       </c>
       <c r="C20" s="27">
         <f>C8*Inputs!$B$17</f>
-        <v>20000</v>
+        <v>30000</v>
       </c>
       <c r="D20" s="27">
         <f>D8*Inputs!$B$17</f>
-        <v>80000</v>
+        <v>200000</v>
       </c>
       <c r="E20" s="27">
         <f>E8*Inputs!$B$17</f>
-        <v>200000</v>
+        <v>350000</v>
       </c>
       <c r="F20" s="27">
         <f>F8*Inputs!$B$17</f>
-        <v>400000</v>
+        <v>600000</v>
       </c>
       <c r="G20" s="7" t="n"/>
     </row>
@@ -6184,19 +6185,19 @@
       </c>
       <c r="C21" s="27">
         <f>(C16+C8)*C10</f>
-        <v>73600</v>
+        <v>81600</v>
       </c>
       <c r="D21" s="27">
         <f>(D16+D8)*D10</f>
-        <v>320000</v>
+        <v>440000</v>
       </c>
       <c r="E21" s="27">
         <f>(E16+E8)*E10</f>
-        <v>960000</v>
+        <v>1140000</v>
       </c>
       <c r="F21" s="27">
         <f>(F16+F8)*F10</f>
-        <v>2240000</v>
+        <v>2520000</v>
       </c>
       <c r="G21" s="7" t="n"/>
     </row>
@@ -6380,19 +6381,19 @@
       </c>
       <c r="C28" s="28">
         <f>SUM(C19:C27)</f>
-        <v>341718.848</v>
+        <v>359718.848</v>
       </c>
       <c r="D28" s="28">
         <f>SUM(D19:D27)</f>
-        <v>1243776.1600000001</v>
+        <v>1483776.1600000001</v>
       </c>
       <c r="E28" s="28">
         <f>SUM(E19:E27)</f>
-        <v>3312190.4</v>
+        <v>3642190.4</v>
       </c>
       <c r="F28" s="28">
         <f>SUM(F19:F27)</f>
-        <v>6998380.8</v>
+        <v>7478380.8</v>
       </c>
       <c r="G28" s="7" t="n"/>
     </row>
@@ -6430,19 +6431,19 @@
       </c>
       <c r="C31" s="27">
         <f>(C19+C20)*Inputs!$B$10</f>
-        <v>10063.8848</v>
+        <v>11063.8848</v>
       </c>
       <c r="D31" s="27">
         <f>(D19+D20)*Inputs!$B$10</f>
-        <v>34879.616</v>
+        <v>46879.61600000001</v>
       </c>
       <c r="E31" s="27">
         <f>(E19+E20)*Inputs!$B$10</f>
-        <v>87199.04000000001</v>
+        <v>102199.04000000001</v>
       </c>
       <c r="F31" s="27">
         <f>(F19+F20)*Inputs!$B$10</f>
-        <v>174398.08000000002</v>
+        <v>194398.08000000002</v>
       </c>
       <c r="G31" s="7" t="n"/>
     </row>
@@ -6458,19 +6459,19 @@
       </c>
       <c r="C32" s="27">
         <f>C21*Inputs!$B$11</f>
-        <v>7360.0</v>
+        <v>8160.0</v>
       </c>
       <c r="D32" s="27">
         <f>D21*Inputs!$B$11</f>
-        <v>32000.0</v>
+        <v>44000.0</v>
       </c>
       <c r="E32" s="27">
         <f>E21*Inputs!$B$11</f>
-        <v>96000.0</v>
+        <v>114000.0</v>
       </c>
       <c r="F32" s="27">
         <f>F21*Inputs!$B$11</f>
-        <v>224000.0</v>
+        <v>252000.0</v>
       </c>
       <c r="G32" s="7" t="n"/>
     </row>
@@ -6654,19 +6655,19 @@
       </c>
       <c r="C39" s="28">
         <f>SUM(C31:C38)</f>
-        <v>60503.8848</v>
+        <v>62303.8848</v>
       </c>
       <c r="D39" s="28">
         <f>SUM(D31:D38)</f>
-        <v>203859.616</v>
+        <v>227859.616</v>
       </c>
       <c r="E39" s="28">
         <f>SUM(E31:E38)</f>
-        <v>514399.04000000004</v>
+        <v>547399.04</v>
       </c>
       <c r="F39" s="28">
         <f>SUM(F31:F38)</f>
-        <v>1042798.0800000001</v>
+        <v>1090798.08</v>
       </c>
       <c r="G39" s="7" t="n"/>
     </row>
@@ -6704,19 +6705,19 @@
       </c>
       <c r="C42" s="27">
         <f>(C19+C20)*(1-Inputs!$B$10)</f>
-        <v>90574.9632</v>
+        <v>99574.9632</v>
       </c>
       <c r="D42" s="27">
         <f>(D19+D20)*(1-Inputs!$B$10)</f>
-        <v>313916.54400000005</v>
+        <v>421916.54400000005</v>
       </c>
       <c r="E42" s="27">
         <f>(E19+E20)*(1-Inputs!$B$10)</f>
-        <v>784791.36</v>
+        <v>919791.36</v>
       </c>
       <c r="F42" s="27">
         <f>(F19+F20)*(1-Inputs!$B$10)</f>
-        <v>1569582.72</v>
+        <v>1749582.72</v>
       </c>
       <c r="G42" s="7" t="n"/>
     </row>
@@ -6732,19 +6733,19 @@
       </c>
       <c r="C43" s="27">
         <f>C21*(1-Inputs!$B$11)+C22*(1-Inputs!$B$12)</f>
-        <v>152640</v>
+        <v>159840</v>
       </c>
       <c r="D43" s="27">
         <f>D21*(1-Inputs!$B$11)+D22*(1-Inputs!$B$12)</f>
-        <v>612000</v>
+        <v>720000</v>
       </c>
       <c r="E43" s="27">
         <f>E21*(1-Inputs!$B$11)+E22*(1-Inputs!$B$12)</f>
-        <v>1728000</v>
+        <v>1890000</v>
       </c>
       <c r="F43" s="27">
         <f>F21*(1-Inputs!$B$11)+F22*(1-Inputs!$B$12)</f>
-        <v>3816000</v>
+        <v>4068000</v>
       </c>
       <c r="G43" s="7" t="n"/>
     </row>
@@ -6838,19 +6839,19 @@
       </c>
       <c r="C48" s="27">
         <f>(C42+C43)*Inputs!$B$22</f>
-        <v>2432.149632</v>
+        <v>2594.149632</v>
       </c>
       <c r="D48" s="27">
         <f>(D42+D43)*Inputs!$B$22</f>
-        <v>9259.16544</v>
+        <v>11419.16544</v>
       </c>
       <c r="E48" s="27">
         <f>(E42+E43)*Inputs!$B$22</f>
-        <v>25127.9136</v>
+        <v>28097.9136</v>
       </c>
       <c r="F48" s="27">
         <f>(F42+F43)*Inputs!$B$22</f>
-        <v>53855.8272</v>
+        <v>58175.8272</v>
       </c>
       <c r="G48" s="7" t="n"/>
     </row>
@@ -6866,19 +6867,19 @@
       </c>
       <c r="C49" s="28">
         <f>C39-C47-C48</f>
-        <v>54281.709312</v>
+        <v>55919.709312</v>
       </c>
       <c r="D49" s="28">
         <f>D39-D47-D48</f>
-        <v>181967.03104</v>
+        <v>203807.03104</v>
       </c>
       <c r="E49" s="28">
         <f>E39-E47-E48</f>
-        <v>457687.5776000001</v>
+        <v>487717.5776000001</v>
       </c>
       <c r="F49" s="28">
         <f>F39-F47-F48</f>
-        <v>925775.1552000002</v>
+        <v>969455.1552000002</v>
       </c>
       <c r="G49" s="7" t="n"/>
     </row>
@@ -6903,19 +6904,19 @@
       </c>
       <c r="C51" s="30">
         <f>IF((C16+C8)=0,0,C39/(C16+C8))</f>
-        <v>65.76509217391305</v>
+        <v>61.08224</v>
       </c>
       <c r="D51" s="30">
         <f>IF((D16+D8)=0,0,D39/(D16+D8))</f>
-        <v>63.70613</v>
+        <v>51.78627636363637</v>
       </c>
       <c r="E51" s="30">
         <f>IF((E16+E8)=0,0,E39/(E16+E8))</f>
-        <v>64.29988</v>
+        <v>57.62095157894737</v>
       </c>
       <c r="F51" s="30">
         <f>IF((F16+F8)=0,0,F39/(F16+F8))</f>
-        <v>65.17488</v>
+        <v>60.599893333333334</v>
       </c>
       <c r="G51" s="7" t="n"/>
     </row>
@@ -6931,19 +6932,19 @@
       </c>
       <c r="C52" s="27">
         <f>IF(C6=0,0,C39/C6)</f>
-        <v>5041.9904</v>
+        <v>5191.9904</v>
       </c>
       <c r="D52" s="27">
         <f>IF(D6=0,0,D39/D6)</f>
-        <v>6795.3205333333335</v>
+        <v>7595.3205333333335</v>
       </c>
       <c r="E52" s="27">
         <f>IF(E6=0,0,E39/E6)</f>
-        <v>8573.317333333334</v>
+        <v>9123.317333333334</v>
       </c>
       <c r="F52" s="27">
         <f>IF(F6=0,0,F39/F6)</f>
-        <v>10427.980800000001</v>
+        <v>10907.980800000001</v>
       </c>
       <c r="G52" s="8" t="inlineStr">
         <is>
@@ -7066,19 +7067,19 @@
       </c>
       <c r="C6" s="26">
         <f>Garden!C27+Exchange!C31</f>
-        <v>45823.5168</v>
+        <v>46823.5168</v>
       </c>
       <c r="D6" s="26">
         <f>Garden!D27+Exchange!D31</f>
-        <v>114758.832</v>
+        <v>126758.83200000001</v>
       </c>
       <c r="E6" s="26">
         <f>Garden!E27+Exchange!E31</f>
-        <v>219557.79200000002</v>
+        <v>234557.79200000002</v>
       </c>
       <c r="F6" s="26">
         <f>Garden!F27+Exchange!F31</f>
-        <v>360876.416</v>
+        <v>380876.416</v>
       </c>
       <c r="G6" s="7" t="n"/>
     </row>
@@ -7094,19 +7095,19 @@
       </c>
       <c r="C7" s="26">
         <f>Garden!C28+Exchange!C32</f>
-        <v>13360</v>
+        <v>14160</v>
       </c>
       <c r="D7" s="26">
         <f>Garden!D28+Exchange!D32</f>
-        <v>48250</v>
+        <v>60250</v>
       </c>
       <c r="E7" s="26">
         <f>Garden!E28+Exchange!E32</f>
-        <v>127500</v>
+        <v>145500</v>
       </c>
       <c r="F7" s="26">
         <f>Garden!F28+Exchange!F32</f>
-        <v>276500</v>
+        <v>304500</v>
       </c>
       <c r="G7" s="7" t="n"/>
     </row>
@@ -7290,19 +7291,19 @@
       </c>
       <c r="C14" s="28">
         <f>SUM(C6:C13)</f>
-        <v>131563.51679999998</v>
+        <v>133363.51679999998</v>
       </c>
       <c r="D14" s="28">
         <f>SUM(D6:D13)</f>
-        <v>361488.832</v>
+        <v>385488.832</v>
       </c>
       <c r="E14" s="28">
         <f>SUM(E6:E13)</f>
-        <v>777207.792</v>
+        <v>810207.792</v>
       </c>
       <c r="F14" s="28">
         <f>SUM(F6:F13)</f>
-        <v>1423776.416</v>
+        <v>1471776.416</v>
       </c>
       <c r="G14" s="7" t="n"/>
     </row>
@@ -7346,19 +7347,19 @@
       </c>
       <c r="C16" s="26">
         <f>Exchange!C39</f>
-        <v>60503.8848</v>
+        <v>62303.8848</v>
       </c>
       <c r="D16" s="26">
         <f>Exchange!D39</f>
-        <v>203859.616</v>
+        <v>227859.616</v>
       </c>
       <c r="E16" s="26">
         <f>Exchange!E39</f>
-        <v>514399.04000000004</v>
+        <v>547399.04</v>
       </c>
       <c r="F16" s="26">
         <f>Exchange!F39</f>
-        <v>1042798.0800000001</v>
+        <v>1090798.08</v>
       </c>
       <c r="G16" s="7" t="n"/>
     </row>
@@ -7374,19 +7375,19 @@
       </c>
       <c r="C17" s="31">
         <f>IF(C14=0,0,(C10+C12+C13)/C14)</f>
-        <v>0.18226937515248912</v>
+        <v>0.17980929549092398</v>
       </c>
       <c r="D17" s="31">
         <f>IF(D14=0,0,(D10+D12+D13)/D14)</f>
-        <v>0.19497144520359622</v>
+        <v>0.18283279345431205</v>
       </c>
       <c r="E17" s="31">
         <f>IF(E14=0,0,(E10+E12+E13)/E14)</f>
-        <v>0.22059737661508158</v>
+        <v>0.21161238103718458</v>
       </c>
       <c r="F17" s="31">
         <f>IF(F14=0,0,(F10+F12+F13)/F14)</f>
-        <v>0.23486833764213721</v>
+        <v>0.2272084240273626</v>
       </c>
       <c r="G17" s="7" t="n"/>
     </row>
@@ -7424,19 +7425,19 @@
       </c>
       <c r="C20" s="26">
         <f>Garden!C24+Exchange!C28</f>
-        <v>631238.112</v>
+        <v>649238.112</v>
       </c>
       <c r="D20" s="26">
         <f>Garden!D24+Exchange!D28</f>
-        <v>1906034.5920000002</v>
+        <v>2146034.592</v>
       </c>
       <c r="E20" s="26">
         <f>Garden!E24+Exchange!E28</f>
-        <v>4478907.904</v>
+        <v>4808907.904</v>
       </c>
       <c r="F20" s="26">
         <f>Garden!F24+Exchange!F28</f>
-        <v>8796337.472</v>
+        <v>9276337.472</v>
       </c>
       <c r="G20" s="7" t="n"/>
     </row>
@@ -7452,19 +7453,19 @@
       </c>
       <c r="C21" s="24">
         <f>Garden!C6+Garden!C7+Exchange!C16+Exchange!C8</f>
-        <v>1520</v>
+        <v>1620</v>
       </c>
       <c r="D21" s="24">
         <f>Garden!D6+Garden!D7+Exchange!D16+Exchange!D8</f>
-        <v>4500</v>
+        <v>5700</v>
       </c>
       <c r="E21" s="24">
         <f>Garden!E6+Garden!E7+Exchange!E16+Exchange!E8</f>
-        <v>10100</v>
+        <v>11600</v>
       </c>
       <c r="F21" s="24">
         <f>Garden!F6+Garden!F7+Exchange!F16+Exchange!F8</f>
-        <v>19000</v>
+        <v>21000</v>
       </c>
       <c r="G21" s="7" t="n"/>
     </row>
@@ -7508,19 +7509,19 @@
       </c>
       <c r="C23" s="26">
         <f>Garden!C19*(1-Inputs!$B$11)+Garden!C20*(1-Inputs!$B$12)+Garden!C38+Exchange!C43+Exchange!C44</f>
-        <v>357599.632</v>
+        <v>364799.632</v>
       </c>
       <c r="D23" s="26">
         <f>Garden!D19*(1-Inputs!$B$11)+Garden!D20*(1-Inputs!$B$12)+Garden!D38+Exchange!D43+Exchange!D44</f>
-        <v>1117129.216</v>
+        <v>1225129.216</v>
       </c>
       <c r="E23" s="26">
         <f>Garden!E19*(1-Inputs!$B$11)+Garden!E20*(1-Inputs!$B$12)+Garden!E38+Exchange!E43+Exchange!E44</f>
-        <v>2685658.752</v>
+        <v>2847658.752</v>
       </c>
       <c r="F23" s="26">
         <f>Garden!F19*(1-Inputs!$B$11)+Garden!F20*(1-Inputs!$B$12)+Garden!F38+Exchange!F43+Exchange!F44</f>
-        <v>5392978.336</v>
+        <v>5644978.336</v>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
@@ -7540,19 +7541,19 @@
       </c>
       <c r="C24" s="30">
         <f>IF(C21=0,0,C14/C21)</f>
-        <v>86.55494526315789</v>
+        <v>82.32315851851851</v>
       </c>
       <c r="D24" s="30">
         <f>IF(D21=0,0,D14/D21)</f>
-        <v>80.33085155555555</v>
+        <v>67.6296196491228</v>
       </c>
       <c r="E24" s="30">
         <f>IF(E21=0,0,E14/E21)</f>
-        <v>76.95126653465347</v>
+        <v>69.84549931034483</v>
       </c>
       <c r="F24" s="30">
         <f>IF(F21=0,0,F14/F21)</f>
-        <v>74.93560084210526</v>
+        <v>70.08459123809524</v>
       </c>
       <c r="G24" s="7" t="n"/>
     </row>
@@ -7568,19 +7569,19 @@
       </c>
       <c r="C25" s="31">
         <f>IF(C20=0,0,C14/C20)</f>
-        <v>0.20842137744686745</v>
+        <v>0.2054154159083008</v>
       </c>
       <c r="D25" s="31">
         <f>IF(D20=0,0,D14/D20)</f>
-        <v>0.18965491681905422</v>
+        <v>0.17962843350103835</v>
       </c>
       <c r="E25" s="31">
         <f>IF(E20=0,0,E14/E20)</f>
-        <v>0.1735261828683495</v>
+        <v>0.16848062141636722</v>
       </c>
       <c r="F25" s="31">
         <f>IF(F20=0,0,F14/F20)</f>
-        <v>0.1618601401472015</v>
+        <v>0.15865921441974898</v>
       </c>
       <c r="G25" s="7" t="n"/>
     </row>
@@ -7646,19 +7647,19 @@
       </c>
       <c r="C29" s="26">
         <f>Garden!C43+Garden!C44+Exchange!C47+Exchange!C48</f>
-        <v>9615.580896000001</v>
+        <v>9777.580896000001</v>
       </c>
       <c r="D29" s="26">
         <f>Garden!D43+Garden!D44+Exchange!D47+Exchange!D48</f>
-        <v>29683.731264000005</v>
+        <v>31843.731264000005</v>
       </c>
       <c r="E29" s="26">
         <f>Garden!E43+Garden!E44+Exchange!E47+Exchange!E48</f>
-        <v>70026.185088</v>
+        <v>72996.185088</v>
       </c>
       <c r="F29" s="26">
         <f>Garden!F43+Garden!F44+Exchange!F47+Exchange!F48</f>
-        <v>136476.888384</v>
+        <v>140796.888384</v>
       </c>
       <c r="G29" s="7" t="n"/>
     </row>
@@ -7870,19 +7871,19 @@
       </c>
       <c r="C37" s="28">
         <f>SUM(C28:C36)</f>
-        <v>239815.580896</v>
+        <v>239977.580896</v>
       </c>
       <c r="D37" s="28">
         <f>SUM(D28:D36)</f>
-        <v>477043.731264</v>
+        <v>479203.731264</v>
       </c>
       <c r="E37" s="28">
         <f>SUM(E28:E36)</f>
-        <v>874586.185088</v>
+        <v>877556.185088</v>
       </c>
       <c r="F37" s="28">
         <f>SUM(F28:F36)</f>
-        <v>1282276.888384</v>
+        <v>1286596.888384</v>
       </c>
       <c r="G37" s="7" t="n"/>
     </row>
@@ -7920,19 +7921,19 @@
       </c>
       <c r="C40" s="28">
         <f>C14-C37</f>
-        <v>-108252.06409600002</v>
+        <v>-106614.06409600002</v>
       </c>
       <c r="D40" s="28">
         <f>D14-D37</f>
-        <v>-115554.899264</v>
+        <v>-93714.899264</v>
       </c>
       <c r="E40" s="28">
         <f>E14-E37</f>
-        <v>-97378.39308800001</v>
+        <v>-67348.39308800001</v>
       </c>
       <c r="F40" s="28">
         <f>F14-F37</f>
-        <v>141499.52761600004</v>
+        <v>185179.52761600004</v>
       </c>
       <c r="G40" s="7" t="n"/>
     </row>
@@ -7948,19 +7949,19 @@
       </c>
       <c r="C41" s="32">
         <f>B41+C40</f>
-        <v>-126505.932234</v>
+        <v>-124867.932234</v>
       </c>
       <c r="D41" s="32">
         <f>C41+D40</f>
-        <v>-242060.831498</v>
+        <v>-218582.831498</v>
       </c>
       <c r="E41" s="32">
         <f>D41+E40</f>
-        <v>-339439.224586</v>
+        <v>-285931.224586</v>
       </c>
       <c r="F41" s="32">
         <f>E41+F40</f>
-        <v>-197939.69697</v>
+        <v>-100751.69696999999</v>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
@@ -7976,7 +7977,7 @@
       </c>
       <c r="B42" s="28">
         <f>-MIN(0,MIN(B41:F41))</f>
-        <v>339439.224586</v>
+        <v>285931.224586</v>
       </c>
       <c r="C42" s="28" t="inlineStr"/>
       <c r="D42" s="28" t="inlineStr"/>
@@ -8028,19 +8029,19 @@
       </c>
       <c r="C44" s="27">
         <f>C14/(1+Inputs!$D$128)</f>
-        <v>65781.75839999999</v>
+        <v>66681.75839999999</v>
       </c>
       <c r="D44" s="27">
         <f>D14/(1+Inputs!$E$128)</f>
-        <v>120496.27733333333</v>
+        <v>128496.27733333333</v>
       </c>
       <c r="E44" s="27">
         <f>E14/(1+Inputs!$F$128)</f>
-        <v>155441.5584</v>
+        <v>162041.5584</v>
       </c>
       <c r="F44" s="27">
         <f>F14/(1+Inputs!$G$128)</f>
-        <v>203396.63085714285</v>
+        <v>210253.77371428572</v>
       </c>
       <c r="G44" s="7" t="n"/>
     </row>
@@ -8087,7 +8088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -8294,165 +8295,167 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="n"/>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="7" t="n"/>
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>Three-year members incl. schools, churches and other organizations: low (founder estimate)</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Founder estimate 2026-09-30, NOT sourced. Individuals alone benchmark to about 1,000 (market-sizing.md); the rest is seats bought by schools and organizations. Source a count of San Diego schools, universities and organizations to firm this up</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>Three-year members incl. schools, churches and other organizations: high (founder estimate)</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Founder estimate 2026-09-30, NOT sourced</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="n"/>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>The ladder</t>
         </is>
       </c>
-      <c r="B17" s="10" t="n"/>
-      <c r="C17" s="10" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="B19" s="10" t="n"/>
+      <c r="C19" s="10" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>TAM — US working creatives + church-based creatives</t>
         </is>
       </c>
-      <c r="B18" s="29">
+      <c r="B20" s="29">
         <f>B11+B13</f>
         <v>4750000</v>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>people who could hold a seat</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>SAM — San Diego creatives + church creatives + mapped networks, less overlap</t>
         </is>
       </c>
-      <c r="B19" s="29">
+      <c r="B21" s="29">
         <f>(B7+B9+B14)*(1-B15)</f>
         <v>35280.0</v>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>reachable in three years through partners we already know; research range 26,000–45,000 (market-sizing.md §6)</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>Penetration of SAM</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>Paying members</t>
         </is>
-      </c>
-      <c r="C20" s="7" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="13" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="B21" s="33">
-        <f>A21*B19</f>
-        <v>352.8</v>
-      </c>
-      <c r="C21" s="7" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="13" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="B22" s="33">
-        <f>A22*B19</f>
-        <v>705.6</v>
       </c>
       <c r="C22" s="7" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="13" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="B23" s="33">
-        <f>A23*B19</f>
-        <v>1058.3999999999999</v>
+        <f>A23*B21</f>
+        <v>352.8</v>
       </c>
       <c r="C23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="13" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="B24" s="33">
-        <f>A24*B19</f>
-        <v>1764.0</v>
+        <f>A24*B21</f>
+        <v>705.6</v>
       </c>
       <c r="C24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="13" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="B25" s="33">
+        <f>A25*B21</f>
+        <v>1058.3999999999999</v>
+      </c>
+      <c r="C25" s="7" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="B26" s="33">
+        <f>A26*B21</f>
+        <v>1764.0</v>
+      </c>
+      <c r="C26" s="7" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="n">
         <v>0.1</v>
       </c>
-      <c r="B25" s="33">
-        <f>A25*B19</f>
+      <c r="B27" s="33">
+        <f>A27*B21</f>
         <v>3528.0</v>
       </c>
-      <c r="C25" s="7" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="n"/>
-      <c r="B26" s="7" t="n"/>
-      <c r="C26" s="7" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="C27" s="7" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="n"/>
+      <c r="B28" s="7" t="n"/>
+      <c r="C28" s="7" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>What the active scenario assumes</t>
         </is>
       </c>
-      <c r="B27" s="10" t="n"/>
-      <c r="C27" s="10" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="11" t="inlineStr">
-        <is>
-          <t>Paying and covered members, Y3 (Combined)</t>
-        </is>
-      </c>
-      <c r="B28" s="29">
-        <f>Combined!D21</f>
-        <v>4500</v>
-      </c>
-      <c r="C28" s="8" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  as a share of SAM</t>
-        </is>
-      </c>
-      <c r="B29" s="31">
-        <f>B28/B19</f>
-        <v>0.12755102040816327</v>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>Hope*Writers alone holds ~3,200 paying members; 2–3% of SAM by Y3 is the Base case</t>
-        </is>
-      </c>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="10" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>Paying and covered members, Y5 (Combined)</t>
+          <t>Paying and covered members, Y3 (Combined)</t>
         </is>
       </c>
       <c r="B30" s="29">
-        <f>Combined!F21</f>
-        <v>19000</v>
+        <f>Combined!D21</f>
+        <v>5700</v>
       </c>
       <c r="C30" s="8" t="inlineStr"/>
     </row>
@@ -8463,38 +8466,82 @@
         </is>
       </c>
       <c r="B31" s="31">
-        <f>B30/B19</f>
-        <v>0.5385487528344671</v>
-      </c>
-      <c r="C31" s="8" t="inlineStr"/>
+        <f>B30/B21</f>
+        <v>0.16156462585034015</v>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Hope*Writers alone holds ~3,200 paying members; 2–3% of SAM by Y3 is the Base case</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
+          <t>Paying and covered members, Y5 (Combined)</t>
+        </is>
+      </c>
+      <c r="B32" s="29">
+        <f>Combined!F21</f>
+        <v>21000</v>
+      </c>
+      <c r="C32" s="8" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  as a share of SAM</t>
+        </is>
+      </c>
+      <c r="B33" s="31">
+        <f>B32/B21</f>
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="C33" s="8" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
           <t>Garden members Y3 as a share of San Diego creatives + church creatives</t>
         </is>
       </c>
-      <c r="B32" s="31">
+      <c r="B34" s="31">
         <f>(Garden!D6+Garden!D7)/(B7+B9)</f>
         <v>0.043333333333333335</v>
       </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>the local sanity check</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="11" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>Active scenario Y3 members vs the founder-estimated range (5,000 to 10,000)</t>
+        </is>
+      </c>
+      <c r="B35" s="34" t="str">
+        <f>IF(Combined!D21&lt;B16,"below",IF(Combined!D21&gt;B17,"above","inside"))</f>
+        <v>inside</v>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>Base should sit inside the range; Conservative below it (individuals only); Fundable at or above the top</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
         <is>
           <t>Paying and covered members, Y5, as a share of US TAM</t>
         </is>
       </c>
-      <c r="B33" s="31">
-        <f>Combined!F21/B18</f>
-        <v>0.004</v>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
+      <c r="B36" s="31">
+        <f>Combined!F21/B20</f>
+        <v>0.004421052631578947</v>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
         <is>
           <t>the national sanity check: partner communities and org seats are not confined to San Diego from Y2 on</t>
         </is>
@@ -8570,7 +8617,7 @@
       </c>
       <c r="B4" s="24">
         <f>Combined!D21</f>
-        <v>4500</v>
+        <v>5700</v>
       </c>
       <c r="C4" s="7" t="n"/>
       <c r="D4" s="7" t="n"/>
@@ -8585,9 +8632,9 @@
           <t>Active scenario Y3 revenue per member</t>
         </is>
       </c>
-      <c r="B5" s="34">
+      <c r="B5" s="35">
         <f>Combined!D24</f>
-        <v>80.33085155555555</v>
+        <v>67.6296196491228</v>
       </c>
       <c r="C5" s="7" t="n"/>
       <c r="D5" s="7" t="n"/>
@@ -8604,7 +8651,7 @@
       </c>
       <c r="B6" s="26">
         <f>Combined!D37</f>
-        <v>477043.731264</v>
+        <v>479203.731264</v>
       </c>
       <c r="C6" s="7" t="n"/>
       <c r="D6" s="7" t="n"/>
@@ -8629,25 +8676,25 @@
           <t>Members \ $ per member</t>
         </is>
       </c>
-      <c r="B8" s="35" t="n">
+      <c r="B8" s="36" t="n">
         <v>20</v>
       </c>
-      <c r="C8" s="35" t="n">
+      <c r="C8" s="36" t="n">
         <v>40</v>
       </c>
-      <c r="D8" s="35" t="n">
+      <c r="D8" s="36" t="n">
         <v>60</v>
       </c>
-      <c r="E8" s="35" t="n">
+      <c r="E8" s="36" t="n">
         <v>90</v>
       </c>
-      <c r="F8" s="35" t="n">
+      <c r="F8" s="36" t="n">
         <v>120</v>
       </c>
-      <c r="G8" s="35" t="n">
+      <c r="G8" s="36" t="n">
         <v>160</v>
       </c>
-      <c r="H8" s="35" t="n">
+      <c r="H8" s="36" t="n">
         <v>200</v>
       </c>
     </row>
@@ -8655,31 +8702,31 @@
       <c r="A9" s="18" t="n">
         <v>1000</v>
       </c>
-      <c r="B9" s="36">
+      <c r="B9" s="37">
         <f>$A9*B$8</f>
         <v>20000</v>
       </c>
-      <c r="C9" s="36">
+      <c r="C9" s="37">
         <f>$A9*C$8</f>
         <v>40000</v>
       </c>
-      <c r="D9" s="36">
+      <c r="D9" s="37">
         <f>$A9*D$8</f>
         <v>60000</v>
       </c>
-      <c r="E9" s="36">
+      <c r="E9" s="37">
         <f>$A9*E$8</f>
         <v>90000</v>
       </c>
-      <c r="F9" s="36">
+      <c r="F9" s="37">
         <f>$A9*F$8</f>
         <v>120000</v>
       </c>
-      <c r="G9" s="36">
+      <c r="G9" s="37">
         <f>$A9*G$8</f>
         <v>160000</v>
       </c>
-      <c r="H9" s="36">
+      <c r="H9" s="37">
         <f>$A9*H$8</f>
         <v>200000</v>
       </c>
@@ -8688,31 +8735,31 @@
       <c r="A10" s="18" t="n">
         <v>2500</v>
       </c>
-      <c r="B10" s="36">
+      <c r="B10" s="37">
         <f>$A10*B$8</f>
         <v>50000</v>
       </c>
-      <c r="C10" s="36">
+      <c r="C10" s="37">
         <f>$A10*C$8</f>
         <v>100000</v>
       </c>
-      <c r="D10" s="36">
+      <c r="D10" s="37">
         <f>$A10*D$8</f>
         <v>150000</v>
       </c>
-      <c r="E10" s="36">
+      <c r="E10" s="37">
         <f>$A10*E$8</f>
         <v>225000</v>
       </c>
-      <c r="F10" s="36">
+      <c r="F10" s="37">
         <f>$A10*F$8</f>
         <v>300000</v>
       </c>
-      <c r="G10" s="36">
+      <c r="G10" s="37">
         <f>$A10*G$8</f>
         <v>400000</v>
       </c>
-      <c r="H10" s="36">
+      <c r="H10" s="37">
         <f>$A10*H$8</f>
         <v>500000</v>
       </c>
@@ -8721,31 +8768,31 @@
       <c r="A11" s="18" t="n">
         <v>5000</v>
       </c>
-      <c r="B11" s="36">
+      <c r="B11" s="37">
         <f>$A11*B$8</f>
         <v>100000</v>
       </c>
-      <c r="C11" s="36">
+      <c r="C11" s="37">
         <f>$A11*C$8</f>
         <v>200000</v>
       </c>
-      <c r="D11" s="36">
+      <c r="D11" s="37">
         <f>$A11*D$8</f>
         <v>300000</v>
       </c>
-      <c r="E11" s="36">
+      <c r="E11" s="37">
         <f>$A11*E$8</f>
         <v>450000</v>
       </c>
-      <c r="F11" s="36">
+      <c r="F11" s="37">
         <f>$A11*F$8</f>
         <v>600000</v>
       </c>
-      <c r="G11" s="36">
+      <c r="G11" s="37">
         <f>$A11*G$8</f>
         <v>800000</v>
       </c>
-      <c r="H11" s="36">
+      <c r="H11" s="37">
         <f>$A11*H$8</f>
         <v>1000000</v>
       </c>
@@ -8754,31 +8801,31 @@
       <c r="A12" s="18" t="n">
         <v>10000</v>
       </c>
-      <c r="B12" s="36">
+      <c r="B12" s="37">
         <f>$A12*B$8</f>
         <v>200000</v>
       </c>
-      <c r="C12" s="36">
+      <c r="C12" s="37">
         <f>$A12*C$8</f>
         <v>400000</v>
       </c>
-      <c r="D12" s="36">
+      <c r="D12" s="37">
         <f>$A12*D$8</f>
         <v>600000</v>
       </c>
-      <c r="E12" s="36">
+      <c r="E12" s="37">
         <f>$A12*E$8</f>
         <v>900000</v>
       </c>
-      <c r="F12" s="36">
+      <c r="F12" s="37">
         <f>$A12*F$8</f>
         <v>1200000</v>
       </c>
-      <c r="G12" s="36">
+      <c r="G12" s="37">
         <f>$A12*G$8</f>
         <v>1600000</v>
       </c>
-      <c r="H12" s="36">
+      <c r="H12" s="37">
         <f>$A12*H$8</f>
         <v>2000000</v>
       </c>
@@ -8787,31 +8834,31 @@
       <c r="A13" s="18" t="n">
         <v>20000</v>
       </c>
-      <c r="B13" s="36">
+      <c r="B13" s="37">
         <f>$A13*B$8</f>
         <v>400000</v>
       </c>
-      <c r="C13" s="36">
+      <c r="C13" s="37">
         <f>$A13*C$8</f>
         <v>800000</v>
       </c>
-      <c r="D13" s="36">
+      <c r="D13" s="37">
         <f>$A13*D$8</f>
         <v>1200000</v>
       </c>
-      <c r="E13" s="36">
+      <c r="E13" s="37">
         <f>$A13*E$8</f>
         <v>1800000</v>
       </c>
-      <c r="F13" s="36">
+      <c r="F13" s="37">
         <f>$A13*F$8</f>
         <v>2400000</v>
       </c>
-      <c r="G13" s="36">
+      <c r="G13" s="37">
         <f>$A13*G$8</f>
         <v>3200000</v>
       </c>
-      <c r="H13" s="36">
+      <c r="H13" s="37">
         <f>$A13*H$8</f>
         <v>4000000</v>
       </c>
@@ -8820,31 +8867,31 @@
       <c r="A14" s="18" t="n">
         <v>40000</v>
       </c>
-      <c r="B14" s="36">
+      <c r="B14" s="37">
         <f>$A14*B$8</f>
         <v>800000</v>
       </c>
-      <c r="C14" s="36">
+      <c r="C14" s="37">
         <f>$A14*C$8</f>
         <v>1600000</v>
       </c>
-      <c r="D14" s="36">
+      <c r="D14" s="37">
         <f>$A14*D$8</f>
         <v>2400000</v>
       </c>
-      <c r="E14" s="36">
+      <c r="E14" s="37">
         <f>$A14*E$8</f>
         <v>3600000</v>
       </c>
-      <c r="F14" s="36">
+      <c r="F14" s="37">
         <f>$A14*F$8</f>
         <v>4800000</v>
       </c>
-      <c r="G14" s="36">
+      <c r="G14" s="37">
         <f>$A14*G$8</f>
         <v>6400000</v>
       </c>
-      <c r="H14" s="36">
+      <c r="H14" s="37">
         <f>$A14*H$8</f>
         <v>8000000</v>
       </c>

--- a/docs/financial-model-5yr-v2.xlsx
+++ b/docs/financial-model-5yr-v2.xlsx
@@ -630,7 +630,7 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>4b. The market-sizing research (docs/funding/market-sizing.md) says San Diego alone supports about 1,000 paying INDIVIDUAL members in three years; the Conservative case matches that (1,270 paying and covered members in Y3). The founder estimates 5,000-10,000 members in three years once schools, universities, churches and other organizations buy seats (estimate not yet sourced; see the Market sheet). The Base case sits inside that range (5,700 in Y3), Fundable above it (12,700). Note that members are not revenue: an organization-bought seat earns the platform about $10 a year in fees plus the backings and classes its holder buys, so 1,200 extra Base seats added only about $24k of Y3 revenue. Revenue is driven by backing and class volume, partner plans and sponsorships.</t>
+          <t>4b. Founder targets (2026-09-30): at least 3,000 paying INDIVIDUALS by year three, and 5,000-10,000 members once organizations buy seats for their stakeholders. Base meets both (about 3,200 individuals and 5,700 members in Y3); Conservative does not (about 950 individuals, which is what the individual-conversion benchmark in market-sizing.md supports for San Diego alone). Reaching 3,000 individuals needs partner communities outside San Diego (Base has 30 by Y3). Organization-bought seats are about 2,500 of the 5,700 Y3 members but only about 20% of Y3 revenue (see Combined), because a seat earns the platform about $10 to $50 a year plus fees on what its holder buys. Neither target is sourced yet.</t>
         </is>
       </c>
     </row>
@@ -6963,7 +6963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -7472,606 +7472,726 @@
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
+          <t>Paying individuals (Garden members + partner-community members)</t>
+        </is>
+      </c>
+      <c r="B22" s="24">
+        <f>Garden!B6+Exchange!B16</f>
+        <v>310</v>
+      </c>
+      <c r="C22" s="24">
+        <f>Garden!C6+Exchange!C16</f>
+        <v>1120</v>
+      </c>
+      <c r="D22" s="24">
+        <f>Garden!D6+Exchange!D16</f>
+        <v>3200</v>
+      </c>
+      <c r="E22" s="24">
+        <f>Garden!E6+Exchange!E16</f>
+        <v>7200</v>
+      </c>
+      <c r="F22" s="24">
+        <f>Garden!F6+Exchange!F16</f>
+        <v>13600</v>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>founder minimum is 3,000 by year three</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>Seats bought by organizations (church-covered + org seat packs)</t>
+        </is>
+      </c>
+      <c r="B23" s="24">
+        <f>Garden!B7+Exchange!B8</f>
+        <v>50</v>
+      </c>
+      <c r="C23" s="24">
+        <f>Garden!C7+Exchange!C8</f>
+        <v>500</v>
+      </c>
+      <c r="D23" s="24">
+        <f>Garden!D7+Exchange!D8</f>
+        <v>2500</v>
+      </c>
+      <c r="E23" s="24">
+        <f>Garden!E7+Exchange!E8</f>
+        <v>4400</v>
+      </c>
+      <c r="F23" s="24">
+        <f>Garden!F7+Exchange!F8</f>
+        <v>7400</v>
+      </c>
+      <c r="G23" s="7" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>Revenue from organization-bought seats (seat fees + fees on what those holders buy)</t>
+        </is>
+      </c>
+      <c r="B24" s="27">
+        <f>Garden!B18*Inputs!$B$9+Exchange!B20*Inputs!$B$10+Garden!B7*(Garden!B9*Inputs!$B$11+Garden!B10*Inputs!$B$12)+Exchange!B8*Exchange!B10*Inputs!$B$11</f>
+        <v>3175</v>
+      </c>
+      <c r="C24" s="27">
+        <f>Garden!C18*Inputs!$B$9+Exchange!C20*Inputs!$B$10+Garden!C7*(Garden!C9*Inputs!$B$11+Garden!C10*Inputs!$B$12)+Exchange!C8*Exchange!C10*Inputs!$B$11</f>
+        <v>19000</v>
+      </c>
+      <c r="D24" s="27">
+        <f>Garden!D18*Inputs!$B$9+Exchange!D20*Inputs!$B$10+Garden!D7*(Garden!D9*Inputs!$B$11+Garden!D10*Inputs!$B$12)+Exchange!D8*Exchange!D10*Inputs!$B$11</f>
+        <v>76250</v>
+      </c>
+      <c r="E24" s="27">
+        <f>Garden!E18*Inputs!$B$9+Exchange!E20*Inputs!$B$10+Garden!E7*(Garden!E9*Inputs!$B$11+Garden!E10*Inputs!$B$12)+Exchange!E8*Exchange!E10*Inputs!$B$11</f>
+        <v>146300</v>
+      </c>
+      <c r="F24" s="27">
+        <f>Garden!F18*Inputs!$B$9+Exchange!F20*Inputs!$B$10+Garden!F7*(Garden!F9*Inputs!$B$11+Garden!F10*Inputs!$B$12)+Exchange!F8*Exchange!F10*Inputs!$B$11</f>
+        <v>258100</v>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>house share of church seat packs, 10% of org seat packs, plus 10% of the backings and classes those seat holders buy</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  share of platform revenue</t>
+        </is>
+      </c>
+      <c r="B25" s="31">
+        <f>IF(B14=0,0,B24/B14)</f>
+        <v>0.08777544979775899</v>
+      </c>
+      <c r="C25" s="31">
+        <f>IF(C14=0,0,C24/C14)</f>
+        <v>0.14246774872091558</v>
+      </c>
+      <c r="D25" s="31">
+        <f>IF(D14=0,0,D24/D14)</f>
+        <v>0.19780080165850306</v>
+      </c>
+      <c r="E25" s="31">
+        <f>IF(E14=0,0,E24/E14)</f>
+        <v>0.18057096147996562</v>
+      </c>
+      <c r="F25" s="31">
+        <f>IF(F14=0,0,F24/F14)</f>
+        <v>0.17536631053068866</v>
+      </c>
+      <c r="G25" s="7" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
           <t>Communities (Garden + partners)</t>
         </is>
       </c>
-      <c r="B22" s="24">
+      <c r="B26" s="24">
         <f>1+Exchange!B6</f>
         <v>5</v>
       </c>
-      <c r="C22" s="24">
+      <c r="C26" s="24">
         <f>1+Exchange!C6</f>
         <v>13</v>
       </c>
-      <c r="D22" s="24">
+      <c r="D26" s="24">
         <f>1+Exchange!D6</f>
         <v>31</v>
       </c>
-      <c r="E22" s="24">
+      <c r="E26" s="24">
         <f>1+Exchange!E6</f>
         <v>61</v>
       </c>
-      <c r="F22" s="24">
+      <c r="F26" s="24">
         <f>1+Exchange!F6</f>
         <v>101</v>
       </c>
-      <c r="G22" s="7" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="G26" s="7" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>Dollars to creatives, hosts and programs (impact)</t>
         </is>
       </c>
-      <c r="B23" s="26">
+      <c r="B27" s="26">
         <f>Garden!B19*(1-Inputs!$B$11)+Garden!B20*(1-Inputs!$B$12)+Garden!B38+Exchange!B43+Exchange!B44</f>
         <v>81369.871</v>
       </c>
-      <c r="C23" s="26">
+      <c r="C27" s="26">
         <f>Garden!C19*(1-Inputs!$B$11)+Garden!C20*(1-Inputs!$B$12)+Garden!C38+Exchange!C43+Exchange!C44</f>
         <v>364799.632</v>
       </c>
-      <c r="D23" s="26">
+      <c r="D27" s="26">
         <f>Garden!D19*(1-Inputs!$B$11)+Garden!D20*(1-Inputs!$B$12)+Garden!D38+Exchange!D43+Exchange!D44</f>
         <v>1225129.216</v>
       </c>
-      <c r="E23" s="26">
+      <c r="E27" s="26">
         <f>Garden!E19*(1-Inputs!$B$11)+Garden!E20*(1-Inputs!$B$12)+Garden!E38+Exchange!E43+Exchange!E44</f>
         <v>2847658.752</v>
       </c>
-      <c r="F23" s="26">
+      <c r="F27" s="26">
         <f>Garden!F19*(1-Inputs!$B$11)+Garden!F20*(1-Inputs!$B$12)+Garden!F38+Exchange!F43+Exchange!F44</f>
         <v>5644978.336</v>
       </c>
-      <c r="G23" s="8" t="inlineStr">
+      <c r="G27" s="8" t="inlineStr">
         <is>
           <t>what the impact report counts</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>Platform revenue per paying/covered member per year</t>
         </is>
       </c>
-      <c r="B24" s="30">
+      <c r="B28" s="30">
         <f>IF(B21=0,0,B14/B21)</f>
         <v>100.47734833333335</v>
       </c>
-      <c r="C24" s="30">
+      <c r="C28" s="30">
         <f>IF(C21=0,0,C14/C21)</f>
         <v>82.32315851851851</v>
       </c>
-      <c r="D24" s="30">
+      <c r="D28" s="30">
         <f>IF(D21=0,0,D14/D21)</f>
         <v>67.6296196491228</v>
       </c>
-      <c r="E24" s="30">
+      <c r="E28" s="30">
         <f>IF(E21=0,0,E14/E21)</f>
         <v>69.84549931034483</v>
       </c>
-      <c r="F24" s="30">
+      <c r="F28" s="30">
         <f>IF(F21=0,0,F14/F21)</f>
         <v>70.08459123809524</v>
       </c>
-      <c r="G24" s="7" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="G28" s="7" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>Effective take rate (revenue / GMV)</t>
         </is>
       </c>
-      <c r="B25" s="31">
+      <c r="B29" s="31">
         <f>IF(B20=0,0,B14/B20)</f>
         <v>0.23500497786225719</v>
       </c>
-      <c r="C25" s="31">
+      <c r="C29" s="31">
         <f>IF(C20=0,0,C14/C20)</f>
         <v>0.2054154159083008</v>
       </c>
-      <c r="D25" s="31">
+      <c r="D29" s="31">
         <f>IF(D20=0,0,D14/D20)</f>
         <v>0.17962843350103835</v>
       </c>
-      <c r="E25" s="31">
+      <c r="E29" s="31">
         <f>IF(E20=0,0,E14/E20)</f>
         <v>0.16848062141636722</v>
       </c>
-      <c r="F25" s="31">
+      <c r="F29" s="31">
         <f>IF(F20=0,0,F14/F20)</f>
         <v>0.15865921441974898</v>
       </c>
-      <c r="G25" s="7" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="n"/>
-      <c r="B26" s="7" t="n"/>
-      <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="n"/>
-      <c r="E26" s="7" t="n"/>
-      <c r="F26" s="7" t="n"/>
-      <c r="G26" s="7" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="G29" s="7" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="n"/>
+      <c r="B30" s="7" t="n"/>
+      <c r="C30" s="7" t="n"/>
+      <c r="D30" s="7" t="n"/>
+      <c r="E30" s="7" t="n"/>
+      <c r="F30" s="7" t="n"/>
+      <c r="G30" s="7" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>Costs</t>
         </is>
       </c>
-      <c r="B27" s="10" t="n"/>
-      <c r="C27" s="10" t="n"/>
-      <c r="D27" s="10" t="n"/>
-      <c r="E27" s="10" t="n"/>
-      <c r="F27" s="10" t="n"/>
-      <c r="G27" s="10" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="11" t="inlineStr">
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="n"/>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="10" t="n"/>
+      <c r="F31" s="10" t="n"/>
+      <c r="G31" s="10" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>Garden community engagement (hourly)</t>
         </is>
       </c>
-      <c r="B28" s="26">
+      <c r="B32" s="26">
         <f>Garden!B42</f>
         <v>15600</v>
       </c>
-      <c r="C28" s="26">
+      <c r="C32" s="26">
         <f>Garden!C42</f>
         <v>31200</v>
       </c>
-      <c r="D28" s="26">
+      <c r="D32" s="26">
         <f>Garden!D42</f>
         <v>48360</v>
       </c>
-      <c r="E28" s="26">
+      <c r="E32" s="26">
         <f>Garden!E42</f>
         <v>66560</v>
       </c>
-      <c r="F28" s="26">
+      <c r="F32" s="26">
         <f>Garden!F42</f>
         <v>85800</v>
       </c>
-      <c r="G28" s="7" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="11" t="inlineStr">
+      <c r="G32" s="7" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>Card processing absorbed + payout costs</t>
         </is>
       </c>
-      <c r="B29" s="26">
+      <c r="B33" s="26">
         <f>Garden!B43+Garden!B44+Exchange!B47+Exchange!B48</f>
         <v>2325.7135380000004</v>
       </c>
-      <c r="C29" s="26">
+      <c r="C33" s="26">
         <f>Garden!C43+Garden!C44+Exchange!C47+Exchange!C48</f>
         <v>9777.580896000001</v>
       </c>
-      <c r="D29" s="26">
+      <c r="D33" s="26">
         <f>Garden!D43+Garden!D44+Exchange!D47+Exchange!D48</f>
         <v>31843.731264000005</v>
       </c>
-      <c r="E29" s="26">
+      <c r="E33" s="26">
         <f>Garden!E43+Garden!E44+Exchange!E47+Exchange!E48</f>
         <v>72996.185088</v>
       </c>
-      <c r="F29" s="26">
+      <c r="F33" s="26">
         <f>Garden!F43+Garden!F44+Exchange!F47+Exchange!F48</f>
         <v>140796.888384</v>
       </c>
-      <c r="G29" s="7" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="G33" s="7" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t>Full-time staff (loaded)</t>
         </is>
       </c>
-      <c r="B30" s="26">
+      <c r="B34" s="26">
         <f>Inputs!$C$128*Inputs!$C$133</f>
         <v>0</v>
       </c>
-      <c r="C30" s="26">
+      <c r="C34" s="26">
         <f>Inputs!$D$128*Inputs!$D$133</f>
         <v>90000</v>
       </c>
-      <c r="D30" s="26">
+      <c r="D34" s="26">
         <f>Inputs!$E$128*Inputs!$E$133</f>
         <v>190000</v>
       </c>
-      <c r="E30" s="26">
+      <c r="E34" s="26">
         <f>Inputs!$F$128*Inputs!$F$133</f>
         <v>400000</v>
       </c>
-      <c r="F30" s="26">
+      <c r="F34" s="26">
         <f>Inputs!$G$128*Inputs!$G$133</f>
         <v>630000</v>
       </c>
-      <c r="G30" s="7" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="G34" s="7" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>Founder compensation</t>
         </is>
       </c>
-      <c r="B31" s="26">
+      <c r="B35" s="26">
         <f>Inputs!$C$138</f>
         <v>0</v>
       </c>
-      <c r="C31" s="26">
+      <c r="C35" s="26">
         <f>Inputs!$D$138</f>
         <v>48000</v>
       </c>
-      <c r="D31" s="26">
+      <c r="D35" s="26">
         <f>Inputs!$E$138</f>
         <v>96000</v>
       </c>
-      <c r="E31" s="26">
+      <c r="E35" s="26">
         <f>Inputs!$F$138</f>
         <v>144000</v>
       </c>
-      <c r="F31" s="26">
+      <c r="F35" s="26">
         <f>Inputs!$G$138</f>
         <v>160000</v>
       </c>
-      <c r="G31" s="7" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="11" t="inlineStr">
+      <c r="G35" s="7" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
         <is>
           <t>Marketing and outreach</t>
         </is>
       </c>
-      <c r="B32" s="26">
+      <c r="B36" s="26">
         <f>Inputs!$C$143</f>
         <v>5000</v>
       </c>
-      <c r="C32" s="26">
+      <c r="C36" s="26">
         <f>Inputs!$D$143</f>
         <v>20000</v>
       </c>
-      <c r="D32" s="26">
+      <c r="D36" s="26">
         <f>Inputs!$E$143</f>
         <v>50000</v>
       </c>
-      <c r="E32" s="26">
+      <c r="E36" s="26">
         <f>Inputs!$F$143</f>
         <v>100000</v>
       </c>
-      <c r="F32" s="26">
+      <c r="F36" s="26">
         <f>Inputs!$G$143</f>
         <v>150000</v>
       </c>
-      <c r="G32" s="7" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="11" t="inlineStr">
+      <c r="G36" s="7" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t>Legal, accounting, insurance</t>
         </is>
       </c>
-      <c r="B33" s="26">
+      <c r="B37" s="26">
         <f>Inputs!$C$148</f>
         <v>8000</v>
       </c>
-      <c r="C33" s="26">
+      <c r="C37" s="26">
         <f>Inputs!$D$148</f>
         <v>12000</v>
       </c>
-      <c r="D33" s="26">
+      <c r="D37" s="26">
         <f>Inputs!$E$148</f>
         <v>20000</v>
       </c>
-      <c r="E33" s="26">
+      <c r="E37" s="26">
         <f>Inputs!$F$148</f>
         <v>30000</v>
       </c>
-      <c r="F33" s="26">
+      <c r="F37" s="26">
         <f>Inputs!$G$148</f>
         <v>40000</v>
       </c>
-      <c r="G33" s="7" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="11" t="inlineStr">
+      <c r="G37" s="7" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>Launch and annual events</t>
         </is>
       </c>
-      <c r="B34" s="26">
+      <c r="B38" s="26">
         <f>Inputs!$C$153</f>
         <v>12000</v>
       </c>
-      <c r="C34" s="26">
+      <c r="C38" s="26">
         <f>Inputs!$D$153</f>
         <v>15000</v>
       </c>
-      <c r="D34" s="26">
+      <c r="D38" s="26">
         <f>Inputs!$E$153</f>
         <v>20000</v>
       </c>
-      <c r="E34" s="26">
+      <c r="E38" s="26">
         <f>Inputs!$F$153</f>
         <v>30000</v>
       </c>
-      <c r="F34" s="26">
+      <c r="F38" s="26">
         <f>Inputs!$G$153</f>
         <v>40000</v>
       </c>
-      <c r="G34" s="7" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="11" t="inlineStr">
+      <c r="G38" s="7" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>Film and story production</t>
         </is>
       </c>
-      <c r="B35" s="26">
+      <c r="B39" s="26">
         <f>Inputs!$C$158</f>
         <v>10000</v>
       </c>
-      <c r="C35" s="26">
+      <c r="C39" s="26">
         <f>Inputs!$D$158</f>
         <v>10000</v>
       </c>
-      <c r="D35" s="26">
+      <c r="D39" s="26">
         <f>Inputs!$E$158</f>
         <v>15000</v>
       </c>
-      <c r="E35" s="26">
+      <c r="E39" s="26">
         <f>Inputs!$F$158</f>
         <v>20000</v>
       </c>
-      <c r="F35" s="26">
+      <c r="F39" s="26">
         <f>Inputs!$G$158</f>
         <v>20000</v>
       </c>
-      <c r="G35" s="7" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+      <c r="G39" s="7" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>Hosting, tools, video, email, SMS</t>
         </is>
       </c>
-      <c r="B36" s="26">
+      <c r="B40" s="26">
         <f>Inputs!$C$163</f>
         <v>1500</v>
       </c>
-      <c r="C36" s="26">
+      <c r="C40" s="26">
         <f>Inputs!$D$163</f>
         <v>4000</v>
       </c>
-      <c r="D36" s="26">
+      <c r="D40" s="26">
         <f>Inputs!$E$163</f>
         <v>8000</v>
       </c>
-      <c r="E36" s="26">
+      <c r="E40" s="26">
         <f>Inputs!$F$163</f>
         <v>14000</v>
       </c>
-      <c r="F36" s="26">
+      <c r="F40" s="26">
         <f>Inputs!$G$163</f>
         <v>20000</v>
       </c>
-      <c r="G36" s="7" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="15" t="inlineStr">
-        <is>
-          <t>TOTAL COSTS</t>
-        </is>
-      </c>
-      <c r="B37" s="28">
-        <f>SUM(B28:B36)</f>
-        <v>54425.713537999996</v>
-      </c>
-      <c r="C37" s="28">
-        <f>SUM(C28:C36)</f>
-        <v>239977.580896</v>
-      </c>
-      <c r="D37" s="28">
-        <f>SUM(D28:D36)</f>
-        <v>479203.731264</v>
-      </c>
-      <c r="E37" s="28">
-        <f>SUM(E28:E36)</f>
-        <v>877556.185088</v>
-      </c>
-      <c r="F37" s="28">
-        <f>SUM(F28:F36)</f>
-        <v>1286596.888384</v>
-      </c>
-      <c r="G37" s="7" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="n"/>
-      <c r="B38" s="7" t="n"/>
-      <c r="C38" s="7" t="n"/>
-      <c r="D38" s="7" t="n"/>
-      <c r="E38" s="7" t="n"/>
-      <c r="F38" s="7" t="n"/>
-      <c r="G38" s="7" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="9" t="inlineStr">
-        <is>
-          <t>Result</t>
-        </is>
-      </c>
-      <c r="B39" s="10" t="n"/>
-      <c r="C39" s="10" t="n"/>
-      <c r="D39" s="10" t="n"/>
-      <c r="E39" s="10" t="n"/>
-      <c r="F39" s="10" t="n"/>
-      <c r="G39" s="10" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="15" t="inlineStr">
-        <is>
-          <t>EBITDA</t>
-        </is>
-      </c>
-      <c r="B40" s="28">
-        <f>B14-B37</f>
-        <v>-18253.86813799999</v>
-      </c>
-      <c r="C40" s="28">
-        <f>C14-C37</f>
-        <v>-106614.06409600002</v>
-      </c>
-      <c r="D40" s="28">
-        <f>D14-D37</f>
-        <v>-93714.899264</v>
-      </c>
-      <c r="E40" s="28">
-        <f>E14-E37</f>
-        <v>-67348.39308800001</v>
-      </c>
-      <c r="F40" s="28">
-        <f>F14-F37</f>
-        <v>185179.52761600004</v>
-      </c>
       <c r="G40" s="7" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="15" t="inlineStr">
         <is>
+          <t>TOTAL COSTS</t>
+        </is>
+      </c>
+      <c r="B41" s="28">
+        <f>SUM(B32:B40)</f>
+        <v>54425.713537999996</v>
+      </c>
+      <c r="C41" s="28">
+        <f>SUM(C32:C40)</f>
+        <v>239977.580896</v>
+      </c>
+      <c r="D41" s="28">
+        <f>SUM(D32:D40)</f>
+        <v>479203.731264</v>
+      </c>
+      <c r="E41" s="28">
+        <f>SUM(E32:E40)</f>
+        <v>877556.185088</v>
+      </c>
+      <c r="F41" s="28">
+        <f>SUM(F32:F40)</f>
+        <v>1286596.888384</v>
+      </c>
+      <c r="G41" s="7" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="n"/>
+      <c r="B42" s="7" t="n"/>
+      <c r="C42" s="7" t="n"/>
+      <c r="D42" s="7" t="n"/>
+      <c r="E42" s="7" t="n"/>
+      <c r="F42" s="7" t="n"/>
+      <c r="G42" s="7" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="10" t="n"/>
+      <c r="D43" s="10" t="n"/>
+      <c r="E43" s="10" t="n"/>
+      <c r="F43" s="10" t="n"/>
+      <c r="G43" s="10" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="15" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B44" s="28">
+        <f>B14-B41</f>
+        <v>-18253.86813799999</v>
+      </c>
+      <c r="C44" s="28">
+        <f>C14-C41</f>
+        <v>-106614.06409600002</v>
+      </c>
+      <c r="D44" s="28">
+        <f>D14-D41</f>
+        <v>-93714.899264</v>
+      </c>
+      <c r="E44" s="28">
+        <f>E14-E41</f>
+        <v>-67348.39308800001</v>
+      </c>
+      <c r="F44" s="28">
+        <f>F14-F41</f>
+        <v>185179.52761600004</v>
+      </c>
+      <c r="G44" s="7" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="15" t="inlineStr">
+        <is>
           <t>Cumulative cash need (before any raise)</t>
         </is>
       </c>
-      <c r="B41" s="32">
-        <f>MIN(0,B40)</f>
+      <c r="B45" s="32">
+        <f>MIN(0,B44)</f>
         <v>-18253.86813799999</v>
       </c>
-      <c r="C41" s="32">
-        <f>B41+C40</f>
+      <c r="C45" s="32">
+        <f>B45+C44</f>
         <v>-124867.932234</v>
       </c>
-      <c r="D41" s="32">
-        <f>C41+D40</f>
+      <c r="D45" s="32">
+        <f>C45+D44</f>
         <v>-218582.831498</v>
       </c>
-      <c r="E41" s="32">
-        <f>D41+E40</f>
+      <c r="E45" s="32">
+        <f>D45+E44</f>
         <v>-285931.224586</v>
       </c>
-      <c r="F41" s="32">
-        <f>E41+F40</f>
+      <c r="F45" s="32">
+        <f>E45+F44</f>
         <v>-100751.69696999999</v>
       </c>
-      <c r="G41" s="8" t="inlineStr">
+      <c r="G45" s="8" t="inlineStr">
         <is>
           <t>running total of EBITDA; the low point is the raise</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="15" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="15" t="inlineStr">
         <is>
           <t>Peak cash need (the raise, before buffer)</t>
         </is>
       </c>
-      <c r="B42" s="28">
-        <f>-MIN(0,MIN(B41:F41))</f>
+      <c r="B46" s="28">
+        <f>-MIN(0,MIN(B45:F45))</f>
         <v>285931.224586</v>
       </c>
-      <c r="C42" s="28" t="inlineStr"/>
-      <c r="D42" s="28" t="inlineStr"/>
-      <c r="E42" s="28" t="inlineStr"/>
-      <c r="F42" s="28" t="inlineStr"/>
-      <c r="G42" s="8" t="inlineStr">
+      <c r="C46" s="28" t="inlineStr"/>
+      <c r="D46" s="28" t="inlineStr"/>
+      <c r="E46" s="28" t="inlineStr"/>
+      <c r="F46" s="28" t="inlineStr"/>
+      <c r="G46" s="8" t="inlineStr">
         <is>
           <t>add ~25% buffer for the ask</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="11" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t>Headcount incl. founder</t>
         </is>
       </c>
-      <c r="B43" s="24">
+      <c r="B47" s="24">
         <f>1+Inputs!$C$128</f>
         <v>1</v>
       </c>
-      <c r="C43" s="24">
+      <c r="C47" s="24">
         <f>1+Inputs!$D$128</f>
         <v>2</v>
       </c>
-      <c r="D43" s="24">
+      <c r="D47" s="24">
         <f>1+Inputs!$E$128</f>
         <v>3</v>
       </c>
-      <c r="E43" s="24">
+      <c r="E47" s="24">
         <f>1+Inputs!$F$128</f>
         <v>5</v>
       </c>
-      <c r="F43" s="24">
+      <c r="F47" s="24">
         <f>1+Inputs!$G$128</f>
         <v>7</v>
       </c>
-      <c r="G43" s="7" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="11" t="inlineStr">
+      <c r="G47" s="7" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t>Revenue per employee</t>
         </is>
       </c>
-      <c r="B44" s="27">
+      <c r="B48" s="27">
         <f>B14/(1+Inputs!$C$128)</f>
         <v>36171.845400000006</v>
       </c>
-      <c r="C44" s="27">
+      <c r="C48" s="27">
         <f>C14/(1+Inputs!$D$128)</f>
         <v>66681.75839999999</v>
       </c>
-      <c r="D44" s="27">
+      <c r="D48" s="27">
         <f>D14/(1+Inputs!$E$128)</f>
         <v>128496.27733333333</v>
       </c>
-      <c r="E44" s="27">
+      <c r="E48" s="27">
         <f>E14/(1+Inputs!$F$128)</f>
         <v>162041.5584</v>
       </c>
-      <c r="F44" s="27">
+      <c r="F48" s="27">
         <f>F14/(1+Inputs!$G$128)</f>
         <v>210253.77371428572</v>
       </c>
-      <c r="G44" s="7" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="11" t="inlineStr">
+      <c r="G48" s="7" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>Founder-comp gap vs $200k market rate</t>
         </is>
       </c>
-      <c r="B45" s="27">
+      <c r="B49" s="27">
         <f>200000-Inputs!$C$138</f>
         <v>200000</v>
       </c>
-      <c r="C45" s="27">
+      <c r="C49" s="27">
         <f>200000-Inputs!$D$138</f>
         <v>152000</v>
       </c>
-      <c r="D45" s="27">
+      <c r="D49" s="27">
         <f>200000-Inputs!$E$138</f>
         <v>104000</v>
       </c>
-      <c r="E45" s="27">
+      <c r="E49" s="27">
         <f>200000-Inputs!$F$138</f>
         <v>56000</v>
       </c>
-      <c r="F45" s="27">
+      <c r="F49" s="27">
         <f>200000-Inputs!$G$138</f>
         <v>40000</v>
       </c>
-      <c r="G45" s="8" t="inlineStr">
+      <c r="G49" s="8" t="inlineStr">
         <is>
           <t>the subsidy nobody invoices (Business Model §05)</t>
         </is>
@@ -8088,7 +8208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" min="1" max="1"/>
@@ -8325,223 +8445,254 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="n"/>
-      <c r="B18" s="7" t="n"/>
-      <c r="C18" s="7" t="n"/>
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>Paying individuals in three years, minimum (founder)</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Founder 2026-09-30: individuals need to be at least 3,000 by year three. The individual-conversion benchmark supports about 1,000 for San Diego alone, so this needs partner communities outside San Diego (Base has 30 by year three)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="7" t="n"/>
+      <c r="B19" s="7" t="n"/>
+      <c r="C19" s="7" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>The ladder</t>
         </is>
       </c>
-      <c r="B19" s="10" t="n"/>
-      <c r="C19" s="10" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="B20" s="10" t="n"/>
+      <c r="C20" s="10" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>TAM — US working creatives + church-based creatives</t>
         </is>
       </c>
-      <c r="B20" s="29">
+      <c r="B21" s="29">
         <f>B11+B13</f>
         <v>4750000</v>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>people who could hold a seat</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="11" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>SAM — San Diego creatives + church creatives + mapped networks, less overlap</t>
         </is>
       </c>
-      <c r="B21" s="29">
+      <c r="B22" s="29">
         <f>(B7+B9+B14)*(1-B15)</f>
         <v>35280.0</v>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>reachable in three years through partners we already know; research range 26,000–45,000 (market-sizing.md §6)</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>Penetration of SAM</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B23" s="15" t="inlineStr">
         <is>
           <t>Paying members</t>
         </is>
-      </c>
-      <c r="C22" s="7" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="13" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="B23" s="33">
-        <f>A23*B21</f>
-        <v>352.8</v>
       </c>
       <c r="C23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="13" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="B24" s="33">
-        <f>A24*B21</f>
-        <v>705.6</v>
+        <f>A24*B22</f>
+        <v>352.8</v>
       </c>
       <c r="C24" s="7" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="13" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="B25" s="33">
-        <f>A25*B21</f>
-        <v>1058.3999999999999</v>
+        <f>A25*B22</f>
+        <v>705.6</v>
       </c>
       <c r="C25" s="7" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="13" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="B26" s="33">
-        <f>A26*B21</f>
-        <v>1764.0</v>
+        <f>A26*B22</f>
+        <v>1058.3999999999999</v>
       </c>
       <c r="C26" s="7" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="B27" s="33">
+        <f>A27*B22</f>
+        <v>1764.0</v>
+      </c>
+      <c r="C27" s="7" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="n">
         <v>0.1</v>
       </c>
-      <c r="B27" s="33">
-        <f>A27*B21</f>
+      <c r="B28" s="33">
+        <f>A28*B22</f>
         <v>3528.0</v>
       </c>
-      <c r="C27" s="7" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="n"/>
-      <c r="B28" s="7" t="n"/>
       <c r="C28" s="7" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="A29" s="7" t="n"/>
+      <c r="B29" s="7" t="n"/>
+      <c r="C29" s="7" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>What the active scenario assumes</t>
         </is>
       </c>
-      <c r="B29" s="10" t="n"/>
-      <c r="C29" s="10" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>Paying and covered members, Y3 (Combined)</t>
         </is>
       </c>
-      <c r="B30" s="29">
+      <c r="B31" s="29">
         <f>Combined!D21</f>
         <v>5700</v>
       </c>
-      <c r="C30" s="8" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  as a share of SAM</t>
-        </is>
-      </c>
-      <c r="B31" s="31">
-        <f>B30/B21</f>
-        <v>0.16156462585034015</v>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>Hope*Writers alone holds ~3,200 paying members; 2–3% of SAM by Y3 is the Base case</t>
-        </is>
-      </c>
+      <c r="C31" s="8" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">  as a share of SAM</t>
+        </is>
+      </c>
+      <c r="B32" s="31">
+        <f>B31/B22</f>
+        <v>0.16156462585034015</v>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Hope*Writers alone holds ~3,200 paying members; 2–3% of SAM by Y3 is the Base case</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
           <t>Paying and covered members, Y5 (Combined)</t>
         </is>
       </c>
-      <c r="B32" s="29">
+      <c r="B33" s="29">
         <f>Combined!F21</f>
         <v>21000</v>
       </c>
-      <c r="C32" s="8" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  as a share of SAM</t>
-        </is>
-      </c>
-      <c r="B33" s="31">
-        <f>B32/B21</f>
-        <v>0.5952380952380952</v>
-      </c>
       <c r="C33" s="8" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">  as a share of SAM</t>
+        </is>
+      </c>
+      <c r="B34" s="31">
+        <f>B33/B22</f>
+        <v>0.5952380952380952</v>
+      </c>
+      <c r="C34" s="8" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
           <t>Garden members Y3 as a share of San Diego creatives + church creatives</t>
         </is>
       </c>
-      <c r="B34" s="31">
+      <c r="B35" s="31">
         <f>(Garden!D6+Garden!D7)/(B7+B9)</f>
         <v>0.043333333333333335</v>
       </c>
-      <c r="C34" s="8" t="inlineStr">
+      <c r="C35" s="8" t="inlineStr">
         <is>
           <t>the local sanity check</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="11" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
         <is>
           <t>Active scenario Y3 members vs the founder-estimated range (5,000 to 10,000)</t>
         </is>
       </c>
-      <c r="B35" s="34" t="str">
+      <c r="B36" s="34" t="str">
         <f>IF(Combined!D21&lt;B16,"below",IF(Combined!D21&gt;B17,"above","inside"))</f>
         <v>inside</v>
       </c>
-      <c r="C35" s="8" t="inlineStr">
+      <c r="C36" s="8" t="inlineStr">
         <is>
           <t>Base should sit inside the range; Conservative below it (individuals only); Fundable at or above the top</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>Active scenario Y3 paying individuals vs the 3,000 minimum</t>
+        </is>
+      </c>
+      <c r="B37" s="34" t="str">
+        <f>IF(Combined!D22&gt;=B18,"meets","below")</f>
+        <v>meets</v>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>Base meets it (about 3,200); Conservative is below (about 950, the individual-conversion benchmark)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>Paying and covered members, Y5, as a share of US TAM</t>
         </is>
       </c>
-      <c r="B36" s="31">
-        <f>Combined!F21/B20</f>
+      <c r="B38" s="31">
+        <f>Combined!F21/B21</f>
         <v>0.004421052631578947</v>
       </c>
-      <c r="C36" s="8" t="inlineStr">
+      <c r="C38" s="8" t="inlineStr">
         <is>
           <t>the national sanity check: partner communities and org seats are not confined to San Diego from Y2 on</t>
         </is>
@@ -8633,7 +8784,7 @@
         </is>
       </c>
       <c r="B5" s="35">
-        <f>Combined!D24</f>
+        <f>Combined!D28</f>
         <v>67.6296196491228</v>
       </c>
       <c r="C5" s="7" t="n"/>
@@ -8650,7 +8801,7 @@
         </is>
       </c>
       <c r="B6" s="26">
-        <f>Combined!D37</f>
+        <f>Combined!D41</f>
         <v>479203.731264</v>
       </c>
       <c r="C6" s="7" t="n"/>

--- a/docs/financial-model-5yr-v2.xlsx
+++ b/docs/financial-model-5yr-v2.xlsx
@@ -124,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -170,12 +170,16 @@
     <xf numFmtId="168" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -636,7 +640,7 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>4b. The ask (Use of Funds sheet): an 18-month window at Base, what it spends by function, what it earns, and the net cash need; runway by raise size below it. Founder pay in Base starts at month 10 ($60k/yr each), ramps to $90k through Y2, then $110k / $135k / $150k. The first employee (community &amp; partnerships lead) starts at month 18.</t>
+          <t>4b. The ask (Use of Funds sheet): an 18-month window at Base, what it spends by function, what it earns, and the net cash need; runway by raise size below it. Founder pay in Base is conditional on a first close of at least $150k and starts the month after it on a ramp ($4k/mo, then $5.5k/mo; $51k each in Y1, $78k in Y2, then $105k / $125k / $140k). The first employee (community &amp; partnerships lead) starts at month 18; the team is 2 / 2.5 / 4.5 / 7 / 8 FTE including founders (Headcount plan on the Use of Funds sheet).</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3636,7 @@
       </c>
       <c r="H131" s="8" t="inlineStr">
         <is>
-          <t>Founders go full time before any employee, and pay starts when there is money for it, then ramps. Base: from month 10 at $60k/yr (3 months in Y1), ramping $60k→$90k through Y2, then $110k/$135k/$150k. Fundable: from month 7. Conservative: day jobs kept, part-time pay from Y3</t>
+          <t>Pay is conditional on a first close of at least $150k and starts the month after it (assumed month 2), on a ramp: Base $4k/mo for six months, $5.5k/mo for the rest of Y1 (= $51k), $6k→$7k/mo through Y2 ($78k), then $105k / $125k / $140k. Fundable starts at $5k/mo. Conservative: day jobs kept, part-time pay from Y3. Both founders are full time before anyone else is hired full time</t>
         </is>
       </c>
     </row>
@@ -3644,19 +3648,19 @@
         </is>
       </c>
       <c r="C132" s="12" t="n">
-        <v>15000</v>
+        <v>51000</v>
       </c>
       <c r="D132" s="12" t="n">
-        <v>75000</v>
+        <v>78000</v>
       </c>
       <c r="E132" s="12" t="n">
-        <v>110000</v>
+        <v>105000</v>
       </c>
       <c r="F132" s="12" t="n">
-        <v>135000</v>
+        <v>125000</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>150000</v>
+        <v>140000</v>
       </c>
       <c r="H132" s="7" t="n"/>
     </row>
@@ -3668,19 +3672,19 @@
         </is>
       </c>
       <c r="C133" s="12" t="n">
-        <v>30000</v>
+        <v>66000</v>
       </c>
       <c r="D133" s="12" t="n">
         <v>100000</v>
       </c>
       <c r="E133" s="12" t="n">
-        <v>140000</v>
+        <v>130000</v>
       </c>
       <c r="F133" s="12" t="n">
-        <v>170000</v>
+        <v>160000</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>200000</v>
+        <v>190000</v>
       </c>
       <c r="H133" s="7" t="n"/>
     </row>
@@ -3693,23 +3697,23 @@
       </c>
       <c r="C134" s="21">
         <f>CHOOSE(Inputs!$B$29,C131,C132,C133)</f>
-        <v>15000</v>
+        <v>51000</v>
       </c>
       <c r="D134" s="21">
         <f>CHOOSE(Inputs!$B$29,D131,D132,D133)</f>
-        <v>75000</v>
+        <v>78000</v>
       </c>
       <c r="E134" s="21">
         <f>CHOOSE(Inputs!$B$29,E131,E132,E133)</f>
-        <v>110000</v>
+        <v>105000</v>
       </c>
       <c r="F134" s="21">
         <f>CHOOSE(Inputs!$B$29,F131,F132,F133)</f>
-        <v>135000</v>
+        <v>125000</v>
       </c>
       <c r="G134" s="21">
         <f>CHOOSE(Inputs!$B$29,G131,G132,G133)</f>
-        <v>150000</v>
+        <v>140000</v>
       </c>
       <c r="H134" s="7" t="n"/>
     </row>
@@ -3763,19 +3767,19 @@
         </is>
       </c>
       <c r="C137" s="12" t="n">
-        <v>15000</v>
+        <v>51000</v>
       </c>
       <c r="D137" s="12" t="n">
-        <v>75000</v>
+        <v>78000</v>
       </c>
       <c r="E137" s="12" t="n">
-        <v>110000</v>
+        <v>105000</v>
       </c>
       <c r="F137" s="12" t="n">
-        <v>135000</v>
+        <v>125000</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>150000</v>
+        <v>140000</v>
       </c>
       <c r="H137" s="7" t="n"/>
     </row>
@@ -3787,19 +3791,19 @@
         </is>
       </c>
       <c r="C138" s="12" t="n">
-        <v>30000</v>
+        <v>66000</v>
       </c>
       <c r="D138" s="12" t="n">
         <v>100000</v>
       </c>
       <c r="E138" s="12" t="n">
-        <v>140000</v>
+        <v>130000</v>
       </c>
       <c r="F138" s="12" t="n">
-        <v>170000</v>
+        <v>160000</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>200000</v>
+        <v>190000</v>
       </c>
       <c r="H138" s="7" t="n"/>
     </row>
@@ -3812,23 +3816,23 @@
       </c>
       <c r="C139" s="21">
         <f>CHOOSE(Inputs!$B$29,C136,C137,C138)</f>
-        <v>15000</v>
+        <v>51000</v>
       </c>
       <c r="D139" s="21">
         <f>CHOOSE(Inputs!$B$29,D136,D137,D138)</f>
-        <v>75000</v>
+        <v>78000</v>
       </c>
       <c r="E139" s="21">
         <f>CHOOSE(Inputs!$B$29,E136,E137,E138)</f>
-        <v>110000</v>
+        <v>105000</v>
       </c>
       <c r="F139" s="21">
         <f>CHOOSE(Inputs!$B$29,F136,F137,F138)</f>
-        <v>135000</v>
+        <v>125000</v>
       </c>
       <c r="G139" s="21">
         <f>CHOOSE(Inputs!$B$29,G136,G137,G138)</f>
-        <v>150000</v>
+        <v>140000</v>
       </c>
       <c r="H139" s="7" t="n"/>
     </row>
@@ -3989,7 +3993,7 @@
       </c>
       <c r="H146" s="8" t="inlineStr">
         <is>
-          <t>No full-time employee before both founders are full time. First hire: community &amp; partnerships lead, from month 18 in Base (0.5 FTE in Y2)</t>
+          <t>No full-time employee before both founders are full time. First hire: community &amp; partnerships lead at month 18 in Base (0.5 FTE in Y2, full in Y3); a second community person in Y4–Y5 as communities pass 60</t>
         </is>
       </c>
     </row>
@@ -4010,10 +4014,10 @@
         <v>1</v>
       </c>
       <c r="F147" s="18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G147" s="18" t="n">
         <v>2</v>
-      </c>
-      <c r="G147" s="18" t="n">
-        <v>2.5</v>
       </c>
       <c r="H147" s="7" t="n"/>
     </row>
@@ -4062,11 +4066,11 @@
       </c>
       <c r="F149" s="19">
         <f>CHOOSE(Inputs!$B$29,F146,F147,F148)</f>
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G149" s="19">
         <f>CHOOSE(Inputs!$B$29,G146,G147,G148)</f>
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="H149" s="7" t="n"/>
     </row>
@@ -4106,7 +4110,11 @@
       <c r="G151" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="H151" s="7" t="n"/>
+      <c r="H151" s="8" t="inlineStr">
+        <is>
+          <t>Base: half-time support in Y3 when members pass 4,000; full time in Y4</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="11" t="inlineStr"/>
@@ -4119,16 +4127,16 @@
         <v>0</v>
       </c>
       <c r="D152" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E152" s="18" t="n">
         <v>0.5</v>
-      </c>
-      <c r="E152" s="18" t="n">
-        <v>1</v>
       </c>
       <c r="F152" s="18" t="n">
         <v>1</v>
       </c>
       <c r="G152" s="18" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H152" s="7" t="n"/>
     </row>
@@ -4169,11 +4177,11 @@
       </c>
       <c r="D154" s="19">
         <f>CHOOSE(Inputs!$B$29,D151,D152,D153)</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E154" s="19">
         <f>CHOOSE(Inputs!$B$29,E151,E152,E153)</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F154" s="19">
         <f>CHOOSE(Inputs!$B$29,F151,F152,F153)</f>
@@ -4181,7 +4189,7 @@
       </c>
       <c r="G154" s="19">
         <f>CHOOSE(Inputs!$B$29,G151,G152,G153)</f>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="H154" s="7" t="n"/>
     </row>
@@ -4221,7 +4229,11 @@
       <c r="G156" s="18" t="n">
         <v>0.5</v>
       </c>
-      <c r="H156" s="7" t="n"/>
+      <c r="H156" s="8" t="inlineStr">
+        <is>
+          <t>Base: a half-time marketer in Y3, full in Y4; contractors before that</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="11" t="inlineStr"/>
@@ -4338,7 +4350,7 @@
       </c>
       <c r="H161" s="8" t="inlineStr">
         <is>
-          <t>Founder 1 is the engineering team until Y3</t>
+          <t>Founder 1 is the engineering team until Y3; first engineer half time in Y3, full in Y4</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4467,11 @@
       <c r="G166" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="H166" s="7" t="n"/>
+      <c r="H166" s="8" t="inlineStr">
+        <is>
+          <t>Base: half-time ops/finance from Y4; bookkeeping is outsourced before that</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="11" t="inlineStr"/>
@@ -4477,7 +4493,7 @@
         <v>0.5</v>
       </c>
       <c r="G167" s="18" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H167" s="7" t="n"/>
     </row>
@@ -4530,7 +4546,7 @@
       </c>
       <c r="G169" s="19">
         <f>CHOOSE(Inputs!$B$29,G166,G167,G168)</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H169" s="7" t="n"/>
     </row>
@@ -9572,23 +9588,23 @@
       </c>
       <c r="B32" s="26">
         <f>Inputs!$C$139*(1+Inputs!$C$144)</f>
-        <v>16800.0</v>
+        <v>57120.00000000001</v>
       </c>
       <c r="C32" s="26">
         <f>Inputs!$D$139*(1+Inputs!$D$144)</f>
-        <v>86250.0</v>
+        <v>89700.0</v>
       </c>
       <c r="D32" s="26">
         <f>Inputs!$E$139*(1+Inputs!$E$144)</f>
-        <v>129800.0</v>
+        <v>123900.0</v>
       </c>
       <c r="E32" s="26">
         <f>Inputs!$F$139*(1+Inputs!$F$144)</f>
-        <v>162000.0</v>
+        <v>150000.0</v>
       </c>
       <c r="F32" s="26">
         <f>Inputs!$G$139*(1+Inputs!$G$144)</f>
-        <v>180000.0</v>
+        <v>168000.0</v>
       </c>
       <c r="G32" s="7" t="n"/>
     </row>
@@ -9612,11 +9628,11 @@
       </c>
       <c r="E33" s="26">
         <f>Inputs!$F$149*Inputs!$B$23*(1+Inputs!$F$144)</f>
-        <v>156000.0</v>
+        <v>117000.0</v>
       </c>
       <c r="F33" s="26">
         <f>Inputs!$G$149*Inputs!$B$23*(1+Inputs!$G$144)</f>
-        <v>195000.0</v>
+        <v>156000.0</v>
       </c>
       <c r="G33" s="7" t="n"/>
     </row>
@@ -9712,23 +9728,23 @@
       </c>
       <c r="B37" s="28">
         <f>SUM(B32:B36)</f>
-        <v>42400.0</v>
+        <v>82720.0</v>
       </c>
       <c r="C37" s="28">
         <f>SUM(C32:C36)</f>
-        <v>167025.0</v>
+        <v>170475.0</v>
       </c>
       <c r="D37" s="28">
         <f>SUM(D32:D36)</f>
-        <v>257620.0</v>
+        <v>251720.0</v>
       </c>
       <c r="E37" s="28">
         <f>SUM(E32:E36)</f>
-        <v>373000.0</v>
+        <v>322000.0</v>
       </c>
       <c r="F37" s="28">
         <f>SUM(F32:F36)</f>
-        <v>455000.0</v>
+        <v>404000.0</v>
       </c>
       <c r="G37" s="7" t="n"/>
     </row>
@@ -9912,11 +9928,11 @@
       </c>
       <c r="C44" s="26">
         <f>Inputs!$D$154*Inputs!$B$24*(1+Inputs!$D$144)</f>
-        <v>31624.999999999996</v>
+        <v>0.0</v>
       </c>
       <c r="D44" s="26">
         <f>Inputs!$E$154*Inputs!$B$24*(1+Inputs!$E$144)</f>
-        <v>64900.0</v>
+        <v>32450.0</v>
       </c>
       <c r="E44" s="26">
         <f>Inputs!$F$154*Inputs!$B$24*(1+Inputs!$F$144)</f>
@@ -9924,7 +9940,7 @@
       </c>
       <c r="F44" s="26">
         <f>Inputs!$G$154*Inputs!$B$24*(1+Inputs!$G$144)</f>
-        <v>99000.0</v>
+        <v>66000.0</v>
       </c>
       <c r="G44" s="7" t="n"/>
     </row>
@@ -9968,11 +9984,11 @@
       </c>
       <c r="C46" s="28">
         <f>SUM(C44:C45)</f>
-        <v>37625.0</v>
+        <v>6000.0</v>
       </c>
       <c r="D46" s="28">
         <f>SUM(D44:D45)</f>
-        <v>72900.0</v>
+        <v>40450.0</v>
       </c>
       <c r="E46" s="28">
         <f>SUM(E44:E45)</f>
@@ -9980,7 +9996,7 @@
       </c>
       <c r="F46" s="28">
         <f>SUM(F44:F45)</f>
-        <v>111000.0</v>
+        <v>78000.0</v>
       </c>
       <c r="G46" s="7" t="n"/>
     </row>
@@ -9992,23 +10008,23 @@
       </c>
       <c r="B47" s="26">
         <f>Inputs!$C$134*(1+Inputs!$C$144)</f>
-        <v>16800.0</v>
+        <v>57120.00000000001</v>
       </c>
       <c r="C47" s="26">
         <f>Inputs!$D$134*(1+Inputs!$D$144)</f>
-        <v>86250.0</v>
+        <v>89700.0</v>
       </c>
       <c r="D47" s="26">
         <f>Inputs!$E$134*(1+Inputs!$E$144)</f>
-        <v>129800.0</v>
+        <v>123900.0</v>
       </c>
       <c r="E47" s="26">
         <f>Inputs!$F$134*(1+Inputs!$F$144)</f>
-        <v>162000.0</v>
+        <v>150000.0</v>
       </c>
       <c r="F47" s="26">
         <f>Inputs!$G$134*(1+Inputs!$G$144)</f>
-        <v>180000.0</v>
+        <v>168000.0</v>
       </c>
       <c r="G47" s="7" t="n"/>
     </row>
@@ -10132,23 +10148,23 @@
       </c>
       <c r="B52" s="28">
         <f>SUM(B47:B51)</f>
-        <v>29300.0</v>
+        <v>69620.0</v>
       </c>
       <c r="C52" s="28">
         <f>SUM(C47:C51)</f>
-        <v>110250.0</v>
+        <v>113700.0</v>
       </c>
       <c r="D52" s="28">
         <f>SUM(D47:D51)</f>
-        <v>242500.0</v>
+        <v>236600.0</v>
       </c>
       <c r="E52" s="28">
         <f>SUM(E47:E51)</f>
-        <v>367000.0</v>
+        <v>355000.0</v>
       </c>
       <c r="F52" s="28">
         <f>SUM(F47:F51)</f>
-        <v>476000.0</v>
+        <v>464000.0</v>
       </c>
       <c r="G52" s="7" t="n"/>
     </row>
@@ -10176,7 +10192,7 @@
       </c>
       <c r="F53" s="26">
         <f>Inputs!$G$169*Inputs!$B$27*(1+Inputs!$G$144)</f>
-        <v>84000.0</v>
+        <v>42000.0</v>
       </c>
       <c r="G53" s="7" t="n"/>
     </row>
@@ -10316,7 +10332,7 @@
       </c>
       <c r="F58" s="28">
         <f>SUM(F53:F57)</f>
-        <v>159000.0</v>
+        <v>117000.0</v>
       </c>
       <c r="G58" s="7" t="n"/>
     </row>
@@ -10393,23 +10409,23 @@
       </c>
       <c r="B62" s="28">
         <f>B37+B43+B46+B52+B58+B60</f>
-        <v>126525.713538</v>
+        <v>207165.713538</v>
       </c>
       <c r="C62" s="28">
         <f>C37+C43+C46+C52+C58+C60</f>
-        <v>401677.580896</v>
+        <v>376952.580896</v>
       </c>
       <c r="D62" s="28">
         <f>D37+D43+D46+D52+D58+D60</f>
-        <v>776113.7312640001</v>
+        <v>731863.7312640001</v>
       </c>
       <c r="E62" s="28">
         <f>E37+E43+E46+E52+E58+E60</f>
-        <v>1212996.185088</v>
+        <v>1149996.185088</v>
       </c>
       <c r="F62" s="28">
         <f>F37+F43+F46+F52+F58+F60</f>
-        <v>1616796.888384</v>
+        <v>1478796.888384</v>
       </c>
       <c r="G62" s="7" t="n"/>
     </row>
@@ -10421,23 +10437,23 @@
       </c>
       <c r="B63" s="27">
         <f>B32+B33+B38+B44+B47+B48+B53</f>
-        <v>33600</v>
+        <v>114240.00000000001</v>
       </c>
       <c r="C63" s="27">
         <f>C32+C33+C38+C44+C47+C48+C53</f>
-        <v>241500</v>
+        <v>216775</v>
       </c>
       <c r="D63" s="27">
         <f>D32+D33+D38+D44+D47+D48+D53</f>
-        <v>522150</v>
+        <v>477900</v>
       </c>
       <c r="E63" s="27">
         <f>E32+E33+E38+E44+E47+E48+E53</f>
-        <v>834000</v>
+        <v>771000</v>
       </c>
       <c r="F63" s="27">
         <f>F32+F33+F38+F44+F47+F48+F53</f>
-        <v>1062000</v>
+        <v>924000</v>
       </c>
       <c r="G63" s="7" t="n"/>
     </row>
@@ -10449,23 +10465,23 @@
       </c>
       <c r="B64" s="27">
         <f>B32+B47</f>
-        <v>33600</v>
+        <v>114240.00000000001</v>
       </c>
       <c r="C64" s="27">
         <f>C32+C47</f>
-        <v>172500</v>
+        <v>179400</v>
       </c>
       <c r="D64" s="27">
         <f>D32+D47</f>
-        <v>259600</v>
+        <v>247800</v>
       </c>
       <c r="E64" s="27">
         <f>E32+E47</f>
-        <v>324000</v>
+        <v>300000</v>
       </c>
       <c r="F64" s="27">
         <f>F32+F47</f>
-        <v>360000</v>
+        <v>336000</v>
       </c>
       <c r="G64" s="7" t="n"/>
     </row>
@@ -10477,23 +10493,23 @@
       </c>
       <c r="B65" s="31">
         <f>IF(B62=0,0,B63/B62)</f>
-        <v>0.2655586683564426</v>
+        <v>0.5514426014276015</v>
       </c>
       <c r="C65" s="31">
         <f>IF(C62=0,0,C63/C62)</f>
-        <v>0.6012284764842969</v>
+        <v>0.5750723326651198</v>
       </c>
       <c r="D65" s="31">
         <f>IF(D62=0,0,D63/D62)</f>
-        <v>0.6727751088099063</v>
+        <v>0.652990412811713</v>
       </c>
       <c r="E65" s="31">
         <f>IF(E62=0,0,E63/E62)</f>
-        <v>0.6875536875159218</v>
+        <v>0.6704370066592886</v>
       </c>
       <c r="F65" s="31">
         <f>IF(F62=0,0,F63/F62)</f>
-        <v>0.6568543071983993</v>
+        <v>0.6248322587490219</v>
       </c>
       <c r="G65" s="7" t="n"/>
     </row>
@@ -10527,23 +10543,23 @@
       </c>
       <c r="B68" s="28">
         <f>B14-B62</f>
-        <v>-90353.86813799999</v>
+        <v>-170993.86813800002</v>
       </c>
       <c r="C68" s="28">
         <f>C14-C62</f>
-        <v>-268314.06409600005</v>
+        <v>-243589.06409600005</v>
       </c>
       <c r="D68" s="28">
         <f>D14-D62</f>
-        <v>-390624.89926400007</v>
+        <v>-346374.89926400007</v>
       </c>
       <c r="E68" s="28">
         <f>E14-E62</f>
-        <v>-402788.393088</v>
+        <v>-339788.393088</v>
       </c>
       <c r="F68" s="28">
         <f>F14-F62</f>
-        <v>-145020.47238399996</v>
+        <v>-7020.472383999964</v>
       </c>
       <c r="G68" s="7" t="n"/>
     </row>
@@ -10555,23 +10571,23 @@
       </c>
       <c r="B69" s="32">
         <f>MIN(0,B68)</f>
-        <v>-90353.86813799999</v>
+        <v>-170993.86813800002</v>
       </c>
       <c r="C69" s="32">
         <f>B69+C68</f>
-        <v>-358667.93223400007</v>
+        <v>-414582.93223400007</v>
       </c>
       <c r="D69" s="32">
         <f>C69+D68</f>
-        <v>-749292.8314980001</v>
+        <v>-760957.8314980001</v>
       </c>
       <c r="E69" s="32">
         <f>D69+E68</f>
-        <v>-1152081.2245860002</v>
+        <v>-1100746.2245860002</v>
       </c>
       <c r="F69" s="32">
         <f>E69+F68</f>
-        <v>-1297101.6969700002</v>
+        <v>-1107766.6969700002</v>
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
@@ -10587,7 +10603,7 @@
       </c>
       <c r="B70" s="28">
         <f>-MIN(0,MIN(B69:F69))</f>
-        <v>1297101.6969700002</v>
+        <v>1107766.6969700002</v>
       </c>
       <c r="C70" s="28" t="inlineStr"/>
       <c r="D70" s="28" t="inlineStr"/>
@@ -10605,25 +10621,25 @@
           <t>Headcount incl. both founders (FTE)</t>
         </is>
       </c>
-      <c r="B71" s="24">
+      <c r="B71" s="33">
         <f>2+Inputs!$C$149+Inputs!$C$154+Inputs!$C$159+Inputs!$C$164+Inputs!$C$169</f>
         <v>2</v>
       </c>
-      <c r="C71" s="24">
+      <c r="C71" s="33">
         <f>2+Inputs!$D$149+Inputs!$D$154+Inputs!$D$159+Inputs!$D$164+Inputs!$D$169</f>
-        <v>3</v>
-      </c>
-      <c r="D71" s="24">
+        <v>2.5</v>
+      </c>
+      <c r="D71" s="33">
         <f>2+Inputs!$E$149+Inputs!$E$154+Inputs!$E$159+Inputs!$E$164+Inputs!$E$169</f>
-        <v>5</v>
-      </c>
-      <c r="E71" s="24">
+        <v>4.5</v>
+      </c>
+      <c r="E71" s="33">
         <f>2+Inputs!$F$149+Inputs!$F$154+Inputs!$F$159+Inputs!$F$164+Inputs!$F$169</f>
-        <v>7.5</v>
-      </c>
-      <c r="F71" s="24">
+        <v>7.0</v>
+      </c>
+      <c r="F71" s="33">
         <f>2+Inputs!$G$149+Inputs!$G$154+Inputs!$G$159+Inputs!$G$164+Inputs!$G$169</f>
-        <v>9.5</v>
+        <v>8.0</v>
       </c>
       <c r="G71" s="7" t="n"/>
     </row>
@@ -10639,19 +10655,19 @@
       </c>
       <c r="C72" s="27">
         <f>C14/C71</f>
-        <v>44454.5056</v>
+        <v>53345.40671999999</v>
       </c>
       <c r="D72" s="27">
         <f>D14/D71</f>
-        <v>77097.7664</v>
+        <v>85664.18488888889</v>
       </c>
       <c r="E72" s="27">
         <f>E14/E71</f>
-        <v>108027.7056</v>
+        <v>115743.97028571428</v>
       </c>
       <c r="F72" s="27">
         <f>F14/F71</f>
-        <v>154923.8332631579</v>
+        <v>183972.052</v>
       </c>
       <c r="G72" s="7" t="n"/>
     </row>
@@ -10663,23 +10679,23 @@
       </c>
       <c r="B73" s="27">
         <f>2*Inputs!$B$28-Inputs!$C$134-Inputs!$C$139</f>
-        <v>320000</v>
+        <v>248000</v>
       </c>
       <c r="C73" s="27">
         <f>2*Inputs!$B$28-Inputs!$D$134-Inputs!$D$139</f>
-        <v>200000</v>
+        <v>194000</v>
       </c>
       <c r="D73" s="27">
         <f>2*Inputs!$B$28-Inputs!$E$134-Inputs!$E$139</f>
-        <v>130000</v>
+        <v>140000</v>
       </c>
       <c r="E73" s="27">
         <f>2*Inputs!$B$28-Inputs!$F$134-Inputs!$F$139</f>
-        <v>80000</v>
+        <v>100000</v>
       </c>
       <c r="F73" s="27">
         <f>2*Inputs!$B$28-Inputs!$G$134-Inputs!$G$139</f>
-        <v>50000</v>
+        <v>70000</v>
       </c>
       <c r="G73" s="8" t="inlineStr">
         <is>
@@ -11012,7 +11028,7 @@
       <c r="A24" s="13" t="n">
         <v>0.01</v>
       </c>
-      <c r="B24" s="33">
+      <c r="B24" s="34">
         <f>A24*B22</f>
         <v>352.8</v>
       </c>
@@ -11022,7 +11038,7 @@
       <c r="A25" s="13" t="n">
         <v>0.02</v>
       </c>
-      <c r="B25" s="33">
+      <c r="B25" s="34">
         <f>A25*B22</f>
         <v>705.6</v>
       </c>
@@ -11032,7 +11048,7 @@
       <c r="A26" s="13" t="n">
         <v>0.03</v>
       </c>
-      <c r="B26" s="33">
+      <c r="B26" s="34">
         <f>A26*B22</f>
         <v>1058.3999999999999</v>
       </c>
@@ -11042,7 +11058,7 @@
       <c r="A27" s="13" t="n">
         <v>0.05</v>
       </c>
-      <c r="B27" s="33">
+      <c r="B27" s="34">
         <f>A27*B22</f>
         <v>1764.0</v>
       </c>
@@ -11052,7 +11068,7 @@
       <c r="A28" s="13" t="n">
         <v>0.1</v>
       </c>
-      <c r="B28" s="33">
+      <c r="B28" s="34">
         <f>A28*B22</f>
         <v>3528.0</v>
       </c>
@@ -11146,7 +11162,7 @@
           <t>Active scenario Y3 members vs the founder-estimated range (5,000 to 10,000)</t>
         </is>
       </c>
-      <c r="B36" s="34" t="str">
+      <c r="B36" s="35" t="str">
         <f>IF(Combined!D21&lt;B16,"below",IF(Combined!D21&gt;B17,"above","inside"))</f>
         <v>inside</v>
       </c>
@@ -11162,7 +11178,7 @@
           <t>Active scenario Y3 paying individuals vs the 3,000 minimum</t>
         </is>
       </c>
-      <c r="B37" s="34" t="str">
+      <c r="B37" s="35" t="str">
         <f>IF(Combined!D22&gt;=B18,"meets","below")</f>
         <v>meets</v>
       </c>
@@ -11199,7 +11215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -11256,7 +11272,7 @@
           <t>Raise amount, $</t>
         </is>
       </c>
-      <c r="B4" s="35" t="n">
+      <c r="B4" s="36" t="n">
         <v>350000</v>
       </c>
       <c r="C4" s="7" t="n"/>
@@ -11272,7 +11288,7 @@
           <t>Months the raise must cover</t>
         </is>
       </c>
-      <c r="B5" s="36" t="n">
+      <c r="B5" s="37" t="n">
         <v>18</v>
       </c>
       <c r="C5" s="7" t="n"/>
@@ -11288,7 +11304,7 @@
           <t>Share of Y1 in the window</t>
         </is>
       </c>
-      <c r="B6" s="37">
+      <c r="B6" s="38">
         <f>MIN(B5,12)/12</f>
         <v>1.0</v>
       </c>
@@ -11305,7 +11321,7 @@
           <t>Share of Y2 in the window</t>
         </is>
       </c>
-      <c r="B7" s="37">
+      <c r="B7" s="38">
         <f>MAX(0,B5-12)/12</f>
         <v>0.5</v>
       </c>
@@ -11390,27 +11406,27 @@
       </c>
       <c r="B11" s="26">
         <f>Combined!B37*$B$6+Combined!C37*$B$7</f>
-        <v>125912.5</v>
-      </c>
-      <c r="C11" s="37">
+        <v>167957.5</v>
+      </c>
+      <c r="C11" s="38">
         <f>IF(B17=0,0,B11/B17)</f>
-        <v>0.3846247790059265</v>
+        <v>0.4245188789558938</v>
       </c>
       <c r="D11" s="26">
         <f>Combined!B37</f>
-        <v>42400.0</v>
+        <v>82720.0</v>
       </c>
       <c r="E11" s="26">
         <f>Combined!C37</f>
-        <v>167025.0</v>
+        <v>170475.0</v>
       </c>
       <c r="F11" s="26">
         <f>Combined!D37</f>
-        <v>257620.0</v>
+        <v>251720.0</v>
       </c>
       <c r="G11" s="26">
         <f>Combined!E37</f>
-        <v>373000.0</v>
+        <v>322000.0</v>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
@@ -11428,9 +11444,9 @@
         <f>Combined!B43*$B$6+Combined!C43*$B$7</f>
         <v>54500</v>
       </c>
-      <c r="C12" s="37">
+      <c r="C12" s="38">
         <f>IF(B17=0,0,B12/B17)</f>
-        <v>0.16648109167733938</v>
+        <v>0.13775079352274364</v>
       </c>
       <c r="D12" s="26">
         <f>Combined!B43</f>
@@ -11462,11 +11478,11 @@
       </c>
       <c r="B13" s="26">
         <f>Combined!B46*$B$6+Combined!C46*$B$7</f>
-        <v>20812.5</v>
-      </c>
-      <c r="C13" s="37">
+        <v>5000</v>
+      </c>
+      <c r="C13" s="38">
         <f>IF(B17=0,0,B13/B17)</f>
-        <v>0.06357592147769955</v>
+        <v>0.012637687479150792</v>
       </c>
       <c r="D13" s="26">
         <f>Combined!B46</f>
@@ -11474,11 +11490,11 @@
       </c>
       <c r="E13" s="26">
         <f>Combined!C46</f>
-        <v>37625.0</v>
+        <v>6000.0</v>
       </c>
       <c r="F13" s="26">
         <f>Combined!D46</f>
-        <v>72900.0</v>
+        <v>40450.0</v>
       </c>
       <c r="G13" s="26">
         <f>Combined!E46</f>
@@ -11498,27 +11514,27 @@
       </c>
       <c r="B14" s="26">
         <f>Combined!B52*$B$6+Combined!C52*$B$7</f>
-        <v>84425</v>
-      </c>
-      <c r="C14" s="37">
+        <v>126470</v>
+      </c>
+      <c r="C14" s="38">
         <f>IF(B17=0,0,B14/B17)</f>
-        <v>0.25789295715338306</v>
+        <v>0.3196576670976401</v>
       </c>
       <c r="D14" s="26">
         <f>Combined!B52</f>
-        <v>29300.0</v>
+        <v>69620.0</v>
       </c>
       <c r="E14" s="26">
         <f>Combined!C52</f>
-        <v>110250.0</v>
+        <v>113700.0</v>
       </c>
       <c r="F14" s="26">
         <f>Combined!D52</f>
-        <v>242500.0</v>
+        <v>236600.0</v>
       </c>
       <c r="G14" s="26">
         <f>Combined!E52</f>
-        <v>367000.0</v>
+        <v>355000.0</v>
       </c>
       <c r="H14" s="8" t="inlineStr">
         <is>
@@ -11536,9 +11552,9 @@
         <f>Combined!B58*$B$6+Combined!C58*$B$7</f>
         <v>34500</v>
       </c>
-      <c r="C15" s="37">
+      <c r="C15" s="38">
         <f>IF(B17=0,0,B15/B17)</f>
-        <v>0.10538711308015061</v>
+        <v>0.08720004360614046</v>
       </c>
       <c r="D15" s="26">
         <f>Combined!B58</f>
@@ -11572,9 +11588,9 @@
         <f>Combined!B60*$B$6+Combined!C60*$B$7</f>
         <v>7214.5039860000015</v>
       </c>
-      <c r="C16" s="37">
+      <c r="C16" s="38">
         <f>IF(B17=0,0,B16/B17)</f>
-        <v>0.022038137605500854</v>
+        <v>0.018234929338431138</v>
       </c>
       <c r="D16" s="26">
         <f>Combined!B60</f>
@@ -11606,24 +11622,24 @@
       </c>
       <c r="B17" s="32">
         <f>SUM(B11:B16)</f>
-        <v>327364.503986</v>
+        <v>395642.003986</v>
       </c>
       <c r="C17" s="7" t="n"/>
       <c r="D17" s="32">
         <f>SUM(D11:D16)</f>
-        <v>126525.713538</v>
+        <v>207165.713538</v>
       </c>
       <c r="E17" s="32">
         <f>SUM(E11:E16)</f>
-        <v>401677.580896</v>
+        <v>376952.580896</v>
       </c>
       <c r="F17" s="32">
         <f>SUM(F11:F16)</f>
-        <v>776113.7312640001</v>
+        <v>731863.7312640001</v>
       </c>
       <c r="G17" s="32">
         <f>SUM(G11:G16)</f>
-        <v>1212996.185088</v>
+        <v>1149996.185088</v>
       </c>
       <c r="H17" s="7" t="n"/>
     </row>
@@ -11635,27 +11651,27 @@
       </c>
       <c r="B18" s="26">
         <f>Combined!B64*$B$6+Combined!C64*$B$7</f>
-        <v>119850</v>
-      </c>
-      <c r="C18" s="37">
+        <v>203940.0</v>
+      </c>
+      <c r="C18" s="38">
         <f>IF(B17=0,0,B18/B17)</f>
-        <v>0.36610566674365363</v>
+        <v>0.5154659968996025</v>
       </c>
       <c r="D18" s="26">
         <f>Combined!B64</f>
-        <v>33600</v>
+        <v>114240.00000000001</v>
       </c>
       <c r="E18" s="26">
         <f>Combined!C64</f>
-        <v>172500</v>
+        <v>179400</v>
       </c>
       <c r="F18" s="26">
         <f>Combined!D64</f>
-        <v>259600</v>
+        <v>247800</v>
       </c>
       <c r="G18" s="26">
         <f>Combined!E64</f>
-        <v>324000</v>
+        <v>300000</v>
       </c>
       <c r="H18" s="7" t="n"/>
     </row>
@@ -11667,27 +11683,27 @@
       </c>
       <c r="B19" s="26">
         <f>Combined!B63*$B$6+Combined!C63*$B$7</f>
-        <v>154350</v>
-      </c>
-      <c r="C19" s="37">
+        <v>222627.5</v>
+      </c>
+      <c r="C19" s="38">
         <f>IF(B17=0,0,B19/B17)</f>
-        <v>0.4714927798238043</v>
+        <v>0.5626993538529286</v>
       </c>
       <c r="D19" s="26">
         <f>Combined!B63</f>
-        <v>33600</v>
+        <v>114240.00000000001</v>
       </c>
       <c r="E19" s="26">
         <f>Combined!C63</f>
-        <v>241500</v>
+        <v>216775</v>
       </c>
       <c r="F19" s="26">
         <f>Combined!D63</f>
-        <v>522150</v>
+        <v>477900</v>
       </c>
       <c r="G19" s="26">
         <f>Combined!E63</f>
-        <v>834000</v>
+        <v>771000</v>
       </c>
       <c r="H19" s="7" t="n"/>
     </row>
@@ -11738,7 +11754,7 @@
       </c>
       <c r="B22" s="32">
         <f>B17-B21</f>
-        <v>224510.90018600004</v>
+        <v>292788.40018600004</v>
       </c>
       <c r="C22" s="7" t="n"/>
       <c r="D22" s="7" t="n"/>
@@ -11755,11 +11771,11 @@
       </c>
       <c r="B23" s="32">
         <f>B4-B22</f>
-        <v>125489.09981399996</v>
-      </c>
-      <c r="C23" s="37">
+        <v>57211.59981399996</v>
+      </c>
+      <c r="C23" s="38">
         <f>IF(B22=0,0,B23/B22)</f>
-        <v>0.5589443528578625</v>
+        <v>0.19540254934162377</v>
       </c>
       <c r="D23" s="7" t="n"/>
       <c r="E23" s="7" t="n"/>
@@ -11784,7 +11800,7 @@
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>Runway by raise size (active scenario; burn = costs less revenue, spent evenly within each year)</t>
+          <t>Headcount plan (FTE by year; founders first, then hires gated on revenue)</t>
         </is>
       </c>
       <c r="B25" s="10" t="n"/>
@@ -11796,208 +11812,295 @@
       <c r="H25" s="10" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>Net burn by year</t>
-        </is>
-      </c>
-      <c r="B26" s="26">
-        <f>MAX(0,Combined!B62-Combined!B14)</f>
-        <v>90353.86813799999</v>
-      </c>
-      <c r="C26" s="26">
-        <f>MAX(0,Combined!C62-Combined!C14)</f>
-        <v>268314.06409600005</v>
-      </c>
-      <c r="D26" s="26">
-        <f>MAX(0,Combined!D62-Combined!D14)</f>
-        <v>390624.89926400007</v>
-      </c>
-      <c r="E26" s="26">
-        <f>MAX(0,Combined!E62-Combined!E14)</f>
-        <v>402788.393088</v>
-      </c>
-      <c r="F26" s="26">
-        <f>MAX(0,Combined!F62-Combined!F14)</f>
-        <v>145020.47238399996</v>
-      </c>
-      <c r="G26" s="7" t="n"/>
-      <c r="H26" s="7" t="n"/>
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="inlineStr"/>
+      <c r="C26" s="17" t="inlineStr"/>
+      <c r="D26" s="17" t="inlineStr">
+        <is>
+          <t>Y1</t>
+        </is>
+      </c>
+      <c r="E26" s="17" t="inlineStr">
+        <is>
+          <t>Y2</t>
+        </is>
+      </c>
+      <c r="F26" s="17" t="inlineStr">
+        <is>
+          <t>Y3</t>
+        </is>
+      </c>
+      <c r="G26" s="17" t="inlineStr">
+        <is>
+          <t>Y4</t>
+        </is>
+      </c>
+      <c r="H26" s="17" t="inlineStr">
+        <is>
+          <t>Y5</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>Monthly burn by year</t>
-        </is>
-      </c>
-      <c r="B27" s="38">
-        <f>B26/12</f>
-        <v>7529.489011499999</v>
-      </c>
-      <c r="C27" s="38">
-        <f>C26/12</f>
-        <v>22359.505341333337</v>
-      </c>
-      <c r="D27" s="38">
-        <f>D26/12</f>
-        <v>32552.074938666672</v>
-      </c>
-      <c r="E27" s="38">
-        <f>E26/12</f>
-        <v>33565.699424</v>
-      </c>
-      <c r="F27" s="38">
-        <f>F26/12</f>
-        <v>12085.03936533333</v>
-      </c>
-      <c r="G27" s="7" t="n"/>
-      <c r="H27" s="7" t="n"/>
+          <t>Founders (Rick: product &amp; engineering; Haley: community &amp; programs)</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n"/>
+      <c r="C27" s="7" t="n"/>
+      <c r="D27" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="G27" s="39" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" s="39" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="n"/>
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>Community &amp; partnerships</t>
+        </is>
+      </c>
       <c r="B28" s="7" t="n"/>
       <c r="C28" s="7" t="n"/>
-      <c r="D28" s="7" t="n"/>
-      <c r="E28" s="7" t="n"/>
-      <c r="F28" s="7" t="n"/>
-      <c r="G28" s="7" t="n"/>
-      <c r="H28" s="7" t="n"/>
+      <c r="D28" s="33">
+        <f>Inputs!$C$149</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="33">
+        <f>Inputs!$D$149</f>
+        <v>0.5</v>
+      </c>
+      <c r="F28" s="33">
+        <f>Inputs!$E$149</f>
+        <v>1</v>
+      </c>
+      <c r="G28" s="33">
+        <f>Inputs!$F$149</f>
+        <v>1.5</v>
+      </c>
+      <c r="H28" s="33">
+        <f>Inputs!$G$149</f>
+        <v>2</v>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="17" t="inlineStr">
-        <is>
-          <t>Raise, $</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="inlineStr">
-        <is>
-          <t>Runway, months</t>
-        </is>
-      </c>
-      <c r="C29" s="17" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="n"/>
-      <c r="E29" s="7" t="n"/>
-      <c r="F29" s="7" t="n"/>
-      <c r="G29" s="7" t="n"/>
-      <c r="H29" s="7" t="n"/>
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>Member support</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="n"/>
+      <c r="C29" s="7" t="n"/>
+      <c r="D29" s="33">
+        <f>Inputs!$C$154</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="33">
+        <f>Inputs!$D$154</f>
+        <v>0</v>
+      </c>
+      <c r="F29" s="33">
+        <f>Inputs!$E$154</f>
+        <v>0.5</v>
+      </c>
+      <c r="G29" s="33">
+        <f>Inputs!$F$154</f>
+        <v>1</v>
+      </c>
+      <c r="H29" s="33">
+        <f>Inputs!$G$154</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="12" t="n">
-        <v>150000</v>
-      </c>
-      <c r="B30" s="39">
-        <f>MIN(60,IF(A30&lt;=$B$26,A30/MAX(1,$B$26/12),IF(A30&lt;=$B$26+$C$26,12+(A30-$B$26)/MAX(1,$C$26/12),IF(A30&lt;=$B$26+$C$26+$D$26,24+(A30-$B$26-$C$26)/MAX(1,$D$26/12),IF(A30&lt;=$B$26+$C$26+$D$26+$E$26,36+(A30-$B$26-$C$26-$D$26)/MAX(1,$E$26/12),IF(A30&lt;=$B$26+$C$26+$D$26+$E$26+$F$26,48+(A30-$B$26-$C$26-$D$26-$E$26)/MAX(1,$F$26/12),60))))))</f>
-        <v>14.667596216976204</v>
-      </c>
-      <c r="C30" s="8" t="inlineStr">
-        <is>
-          <t>60 = the raise outlasts the five-year model</t>
-        </is>
-      </c>
-      <c r="D30" s="7" t="n"/>
-      <c r="E30" s="7" t="n"/>
-      <c r="F30" s="7" t="n"/>
-      <c r="G30" s="7" t="n"/>
-      <c r="H30" s="7" t="n"/>
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="n"/>
+      <c r="C30" s="7" t="n"/>
+      <c r="D30" s="33">
+        <f>Inputs!$C$159</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="33">
+        <f>Inputs!$D$159</f>
+        <v>0</v>
+      </c>
+      <c r="F30" s="33">
+        <f>Inputs!$E$159</f>
+        <v>0.5</v>
+      </c>
+      <c r="G30" s="33">
+        <f>Inputs!$F$159</f>
+        <v>1</v>
+      </c>
+      <c r="H30" s="33">
+        <f>Inputs!$G$159</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="n">
-        <v>250000</v>
-      </c>
-      <c r="B31" s="39">
-        <f>MIN(60,IF(A31&lt;=$B$26,A31/MAX(1,$B$26/12),IF(A31&lt;=$B$26+$C$26,12+(A31-$B$26)/MAX(1,$C$26/12),IF(A31&lt;=$B$26+$C$26+$D$26,24+(A31-$B$26-$C$26)/MAX(1,$D$26/12),IF(A31&lt;=$B$26+$C$26+$D$26+$E$26,36+(A31-$B$26-$C$26-$D$26)/MAX(1,$E$26/12),IF(A31&lt;=$B$26+$C$26+$D$26+$E$26+$F$26,48+(A31-$B$26-$C$26-$D$26-$E$26)/MAX(1,$F$26/12),60))))))</f>
-        <v>19.139967071046126</v>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>60 = the raise outlasts the five-year model</t>
-        </is>
-      </c>
-      <c r="D31" s="7" t="n"/>
-      <c r="E31" s="7" t="n"/>
-      <c r="F31" s="7" t="n"/>
-      <c r="G31" s="7" t="n"/>
-      <c r="H31" s="7" t="n"/>
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="n"/>
+      <c r="C31" s="7" t="n"/>
+      <c r="D31" s="33">
+        <f>Inputs!$C$164</f>
+        <v>0</v>
+      </c>
+      <c r="E31" s="33">
+        <f>Inputs!$D$164</f>
+        <v>0</v>
+      </c>
+      <c r="F31" s="33">
+        <f>Inputs!$E$164</f>
+        <v>0.5</v>
+      </c>
+      <c r="G31" s="33">
+        <f>Inputs!$F$164</f>
+        <v>1</v>
+      </c>
+      <c r="H31" s="33">
+        <f>Inputs!$G$164</f>
+        <v>1.5</v>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="12" t="n">
-        <v>350000</v>
-      </c>
-      <c r="B32" s="39">
-        <f>MIN(60,IF(A32&lt;=$B$26,A32/MAX(1,$B$26/12),IF(A32&lt;=$B$26+$C$26,12+(A32-$B$26)/MAX(1,$C$26/12),IF(A32&lt;=$B$26+$C$26+$D$26,24+(A32-$B$26-$C$26)/MAX(1,$D$26/12),IF(A32&lt;=$B$26+$C$26+$D$26+$E$26,36+(A32-$B$26-$C$26-$D$26)/MAX(1,$E$26/12),IF(A32&lt;=$B$26+$C$26+$D$26+$E$26+$F$26,48+(A32-$B$26-$C$26-$D$26-$E$26)/MAX(1,$F$26/12),60))))))</f>
-        <v>23.61233792511605</v>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>60 = the raise outlasts the five-year model</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="n"/>
-      <c r="E32" s="7" t="n"/>
-      <c r="F32" s="7" t="n"/>
-      <c r="G32" s="7" t="n"/>
-      <c r="H32" s="7" t="n"/>
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>Operations / finance</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="n"/>
+      <c r="C32" s="7" t="n"/>
+      <c r="D32" s="33">
+        <f>Inputs!$C$169</f>
+        <v>0</v>
+      </c>
+      <c r="E32" s="33">
+        <f>Inputs!$D$169</f>
+        <v>0</v>
+      </c>
+      <c r="F32" s="33">
+        <f>Inputs!$E$169</f>
+        <v>0</v>
+      </c>
+      <c r="G32" s="33">
+        <f>Inputs!$F$169</f>
+        <v>0.5</v>
+      </c>
+      <c r="H32" s="33">
+        <f>Inputs!$G$169</f>
+        <v>0.5</v>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="12" t="n">
-        <v>500000</v>
-      </c>
-      <c r="B33" s="39">
-        <f>MIN(60,IF(A33&lt;=$B$26,A33/MAX(1,$B$26/12),IF(A33&lt;=$B$26+$C$26,12+(A33-$B$26)/MAX(1,$C$26/12),IF(A33&lt;=$B$26+$C$26+$D$26,24+(A33-$B$26-$C$26)/MAX(1,$D$26/12),IF(A33&lt;=$B$26+$C$26+$D$26+$E$26,36+(A33-$B$26-$C$26-$D$26)/MAX(1,$E$26/12),IF(A33&lt;=$B$26+$C$26+$D$26+$E$26+$F$26,48+(A33-$B$26-$C$26-$D$26-$E$26)/MAX(1,$F$26/12),60))))))</f>
-        <v>28.34172224143291</v>
-      </c>
-      <c r="C33" s="8" t="inlineStr">
-        <is>
-          <t>60 = the raise outlasts the five-year model</t>
-        </is>
-      </c>
-      <c r="D33" s="7" t="n"/>
-      <c r="E33" s="7" t="n"/>
-      <c r="F33" s="7" t="n"/>
-      <c r="G33" s="7" t="n"/>
-      <c r="H33" s="7" t="n"/>
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>TOTAL FTE</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="n"/>
+      <c r="C33" s="7" t="n"/>
+      <c r="D33" s="40">
+        <f>SUM(D27:D32)</f>
+        <v>2</v>
+      </c>
+      <c r="E33" s="40">
+        <f>SUM(E27:E32)</f>
+        <v>2.5</v>
+      </c>
+      <c r="F33" s="40">
+        <f>SUM(F27:F32)</f>
+        <v>4.5</v>
+      </c>
+      <c r="G33" s="40">
+        <f>SUM(G27:G32)</f>
+        <v>7.0</v>
+      </c>
+      <c r="H33" s="40">
+        <f>SUM(H27:H32)</f>
+        <v>8.0</v>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="12" t="n">
-        <v>650000</v>
-      </c>
-      <c r="B34" s="39">
-        <f>MIN(60,IF(A34&lt;=$B$26,A34/MAX(1,$B$26/12),IF(A34&lt;=$B$26+$C$26,12+(A34-$B$26)/MAX(1,$C$26/12),IF(A34&lt;=$B$26+$C$26+$D$26,24+(A34-$B$26-$C$26)/MAX(1,$D$26/12),IF(A34&lt;=$B$26+$C$26+$D$26+$E$26,36+(A34-$B$26-$C$26-$D$26)/MAX(1,$E$26/12),IF(A34&lt;=$B$26+$C$26+$D$26+$E$26+$F$26,48+(A34-$B$26-$C$26-$D$26-$E$26)/MAX(1,$F$26/12),60))))))</f>
-        <v>32.949723429763424</v>
-      </c>
-      <c r="C34" s="8" t="inlineStr">
-        <is>
-          <t>60 = the raise outlasts the five-year model</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="n"/>
-      <c r="E34" s="7" t="n"/>
-      <c r="F34" s="7" t="n"/>
-      <c r="G34" s="7" t="n"/>
-      <c r="H34" s="7" t="n"/>
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>Revenue per FTE</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="n"/>
+      <c r="C34" s="7" t="n"/>
+      <c r="D34" s="41">
+        <f>IF(D33=0,0,Combined!B14/D33)</f>
+        <v>18085.922700000003</v>
+      </c>
+      <c r="E34" s="41">
+        <f>IF(E33=0,0,Combined!C14/E33)</f>
+        <v>53345.40671999999</v>
+      </c>
+      <c r="F34" s="41">
+        <f>IF(F33=0,0,Combined!D14/F33)</f>
+        <v>85664.18488888889</v>
+      </c>
+      <c r="G34" s="41">
+        <f>IF(G33=0,0,Combined!E14/G33)</f>
+        <v>115743.97028571428</v>
+      </c>
+      <c r="H34" s="41">
+        <f>IF(H33=0,0,Combined!F14/H33)</f>
+        <v>183972.052</v>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="12" t="n">
-        <v>800000</v>
-      </c>
-      <c r="B35" s="39">
-        <f>MIN(60,IF(A35&lt;=$B$26,A35/MAX(1,$B$26/12),IF(A35&lt;=$B$26+$C$26,12+(A35-$B$26)/MAX(1,$C$26/12),IF(A35&lt;=$B$26+$C$26+$D$26,24+(A35-$B$26-$C$26)/MAX(1,$D$26/12),IF(A35&lt;=$B$26+$C$26+$D$26+$E$26,36+(A35-$B$26-$C$26-$D$26)/MAX(1,$E$26/12),IF(A35&lt;=$B$26+$C$26+$D$26+$E$26+$F$26,48+(A35-$B$26-$C$26-$D$26-$E$26)/MAX(1,$F$26/12),60))))))</f>
-        <v>37.51068410228757</v>
-      </c>
-      <c r="C35" s="8" t="inlineStr">
-        <is>
-          <t>60 = the raise outlasts the five-year model</t>
-        </is>
-      </c>
-      <c r="D35" s="7" t="n"/>
-      <c r="E35" s="7" t="n"/>
-      <c r="F35" s="7" t="n"/>
-      <c r="G35" s="7" t="n"/>
-      <c r="H35" s="7" t="n"/>
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>Founder pay, each (cash paid in the year)</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="n"/>
+      <c r="C35" s="7" t="n"/>
+      <c r="D35" s="26">
+        <f>Inputs!$C$134</f>
+        <v>51000</v>
+      </c>
+      <c r="E35" s="26">
+        <f>Inputs!$D$134</f>
+        <v>78000</v>
+      </c>
+      <c r="F35" s="26">
+        <f>Inputs!$E$134</f>
+        <v>105000</v>
+      </c>
+      <c r="G35" s="26">
+        <f>Inputs!$F$134</f>
+        <v>125000</v>
+      </c>
+      <c r="H35" s="42" t="inlineStr">
+        <is>
+          <t>conditional on a first close of at least $150k; starts the month after, on a ramp</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n"/>
@@ -12010,18 +12113,246 @@
       <c r="H36" s="7" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>Runway by raise size (active scenario; burn = costs less revenue, spent evenly within each year)</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="10" t="n"/>
+      <c r="D37" s="10" t="n"/>
+      <c r="E37" s="10" t="n"/>
+      <c r="F37" s="10" t="n"/>
+      <c r="G37" s="10" t="n"/>
+      <c r="H37" s="10" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
+        <is>
+          <t>Net burn by year</t>
+        </is>
+      </c>
+      <c r="B38" s="26">
+        <f>MAX(0,Combined!B62-Combined!B14)</f>
+        <v>170993.86813800002</v>
+      </c>
+      <c r="C38" s="26">
+        <f>MAX(0,Combined!C62-Combined!C14)</f>
+        <v>243589.06409600005</v>
+      </c>
+      <c r="D38" s="26">
+        <f>MAX(0,Combined!D62-Combined!D14)</f>
+        <v>346374.89926400007</v>
+      </c>
+      <c r="E38" s="26">
+        <f>MAX(0,Combined!E62-Combined!E14)</f>
+        <v>339788.393088</v>
+      </c>
+      <c r="F38" s="26">
+        <f>MAX(0,Combined!F62-Combined!F14)</f>
+        <v>7020.472383999964</v>
+      </c>
+      <c r="G38" s="7" t="n"/>
+      <c r="H38" s="7" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>Monthly burn by year</t>
+        </is>
+      </c>
+      <c r="B39" s="41">
+        <f>B38/12</f>
+        <v>14249.489011500002</v>
+      </c>
+      <c r="C39" s="41">
+        <f>C38/12</f>
+        <v>20299.08867466667</v>
+      </c>
+      <c r="D39" s="41">
+        <f>D38/12</f>
+        <v>28864.574938666672</v>
+      </c>
+      <c r="E39" s="41">
+        <f>E38/12</f>
+        <v>28315.699424000002</v>
+      </c>
+      <c r="F39" s="41">
+        <f>F38/12</f>
+        <v>585.0393653333304</v>
+      </c>
+      <c r="G39" s="7" t="n"/>
+      <c r="H39" s="7" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="n"/>
+      <c r="B40" s="7" t="n"/>
+      <c r="C40" s="7" t="n"/>
+      <c r="D40" s="7" t="n"/>
+      <c r="E40" s="7" t="n"/>
+      <c r="F40" s="7" t="n"/>
+      <c r="G40" s="7" t="n"/>
+      <c r="H40" s="7" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="17" t="inlineStr">
+        <is>
+          <t>Raise, $</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t>Runway, months</t>
+        </is>
+      </c>
+      <c r="C41" s="17" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="n"/>
+      <c r="E41" s="7" t="n"/>
+      <c r="F41" s="7" t="n"/>
+      <c r="G41" s="7" t="n"/>
+      <c r="H41" s="7" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="n">
+        <v>150000</v>
+      </c>
+      <c r="B42" s="43">
+        <f>MIN(60,IF(A42&lt;=$B$38,A42/MAX(1,$B$38/12),IF(A42&lt;=$B$38+$C$38,12+(A42-$B$38)/MAX(1,$C$38/12),IF(A42&lt;=$B$38+$C$38+$D$38,24+(A42-$B$38-$C$38)/MAX(1,$D$38/12),IF(A42&lt;=$B$38+$C$38+$D$38+$E$38,36+(A42-$B$38-$C$38-$D$38)/MAX(1,$E$38/12),IF(A42&lt;=$B$38+$C$38+$D$38+$E$38+$F$38,48+(A42-$B$38-$C$38-$D$38-$E$38)/MAX(1,$F$38/12),60))))))</f>
+        <v>10.526693264505345</v>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>60 = the raise outlasts the five-year model</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="n"/>
+      <c r="E42" s="7" t="n"/>
+      <c r="F42" s="7" t="n"/>
+      <c r="G42" s="7" t="n"/>
+      <c r="H42" s="7" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="12" t="n">
+        <v>250000</v>
+      </c>
+      <c r="B43" s="43">
+        <f>MIN(60,IF(A43&lt;=$B$38,A43/MAX(1,$B$38/12),IF(A43&lt;=$B$38+$C$38,12+(A43-$B$38)/MAX(1,$C$38/12),IF(A43&lt;=$B$38+$C$38+$D$38,24+(A43-$B$38-$C$38)/MAX(1,$D$38/12),IF(A43&lt;=$B$38+$C$38+$D$38+$E$38,36+(A43-$B$38-$C$38-$D$38)/MAX(1,$E$38/12),IF(A43&lt;=$B$38+$C$38+$D$38+$E$38+$F$38,48+(A43-$B$38-$C$38-$D$38-$E$38)/MAX(1,$F$38/12),60))))))</f>
+        <v>15.892102405592222</v>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>60 = the raise outlasts the five-year model</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="n"/>
+      <c r="E43" s="7" t="n"/>
+      <c r="F43" s="7" t="n"/>
+      <c r="G43" s="7" t="n"/>
+      <c r="H43" s="7" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="12" t="n">
+        <v>350000</v>
+      </c>
+      <c r="B44" s="43">
+        <f>MIN(60,IF(A44&lt;=$B$38,A44/MAX(1,$B$38/12),IF(A44&lt;=$B$38+$C$38,12+(A44-$B$38)/MAX(1,$C$38/12),IF(A44&lt;=$B$38+$C$38+$D$38,24+(A44-$B$38-$C$38)/MAX(1,$D$38/12),IF(A44&lt;=$B$38+$C$38+$D$38+$E$38,36+(A44-$B$38-$C$38-$D$38)/MAX(1,$E$38/12),IF(A44&lt;=$B$38+$C$38+$D$38+$E$38+$F$38,48+(A44-$B$38-$C$38-$D$38-$E$38)/MAX(1,$F$38/12),60))))))</f>
+        <v>20.818431937065245</v>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>60 = the raise outlasts the five-year model</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="n"/>
+      <c r="E44" s="7" t="n"/>
+      <c r="F44" s="7" t="n"/>
+      <c r="G44" s="7" t="n"/>
+      <c r="H44" s="7" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="12" t="n">
+        <v>500000</v>
+      </c>
+      <c r="B45" s="43">
+        <f>MIN(60,IF(A45&lt;=$B$38,A45/MAX(1,$B$38/12),IF(A45&lt;=$B$38+$C$38,12+(A45-$B$38)/MAX(1,$C$38/12),IF(A45&lt;=$B$38+$C$38+$D$38,24+(A45-$B$38-$C$38)/MAX(1,$D$38/12),IF(A45&lt;=$B$38+$C$38+$D$38+$E$38,36+(A45-$B$38-$C$38-$D$38)/MAX(1,$E$38/12),IF(A45&lt;=$B$38+$C$38+$D$38+$E$38+$F$38,48+(A45-$B$38-$C$38-$D$38-$E$38)/MAX(1,$F$38/12),60))))))</f>
+        <v>26.959235254546435</v>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>60 = the raise outlasts the five-year model</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="n"/>
+      <c r="E45" s="7" t="n"/>
+      <c r="F45" s="7" t="n"/>
+      <c r="G45" s="7" t="n"/>
+      <c r="H45" s="7" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="n">
+        <v>650000</v>
+      </c>
+      <c r="B46" s="43">
+        <f>MIN(60,IF(A46&lt;=$B$38,A46/MAX(1,$B$38/12),IF(A46&lt;=$B$38+$C$38,12+(A46-$B$38)/MAX(1,$C$38/12),IF(A46&lt;=$B$38+$C$38+$D$38,24+(A46-$B$38-$C$38)/MAX(1,$D$38/12),IF(A46&lt;=$B$38+$C$38+$D$38+$E$38,36+(A46-$B$38-$C$38-$D$38)/MAX(1,$E$38/12),IF(A46&lt;=$B$38+$C$38+$D$38+$E$38+$F$38,48+(A46-$B$38-$C$38-$D$38-$E$38)/MAX(1,$F$38/12),60))))))</f>
+        <v>32.15591666484711</v>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>60 = the raise outlasts the five-year model</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="n"/>
+      <c r="E46" s="7" t="n"/>
+      <c r="F46" s="7" t="n"/>
+      <c r="G46" s="7" t="n"/>
+      <c r="H46" s="7" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="12" t="n">
+        <v>800000</v>
+      </c>
+      <c r="B47" s="43">
+        <f>MIN(60,IF(A47&lt;=$B$38,A47/MAX(1,$B$38/12),IF(A47&lt;=$B$38+$C$38,12+(A47-$B$38)/MAX(1,$C$38/12),IF(A47&lt;=$B$38+$C$38+$D$38,24+(A47-$B$38-$C$38)/MAX(1,$D$38/12),IF(A47&lt;=$B$38+$C$38+$D$38+$E$38,36+(A47-$B$38-$C$38-$D$38)/MAX(1,$E$38/12),IF(A47&lt;=$B$38+$C$38+$D$38+$E$38+$F$38,48+(A47-$B$38-$C$38-$D$38-$E$38)/MAX(1,$F$38/12),60))))))</f>
+        <v>37.37881702716862</v>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>60 = the raise outlasts the five-year model</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="n"/>
+      <c r="E47" s="7" t="n"/>
+      <c r="F47" s="7" t="n"/>
+      <c r="G47" s="7" t="n"/>
+      <c r="H47" s="7" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="n"/>
+      <c r="B48" s="7" t="n"/>
+      <c r="C48" s="7" t="n"/>
+      <c r="D48" s="7" t="n"/>
+      <c r="E48" s="7" t="n"/>
+      <c r="F48" s="7" t="n"/>
+      <c r="G48" s="7" t="n"/>
+      <c r="H48" s="7" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
         <is>
           <t>Read: the window budget is what the raise has to cover; the cushion should be positive after the first hire. Runway assumes the scenario's spend from month one; a lean first year stretches it.</t>
         </is>
       </c>
-      <c r="B37" s="7" t="n"/>
-      <c r="C37" s="7" t="n"/>
-      <c r="D37" s="7" t="n"/>
-      <c r="E37" s="7" t="n"/>
-      <c r="F37" s="7" t="n"/>
-      <c r="G37" s="7" t="n"/>
-      <c r="H37" s="7" t="n"/>
+      <c r="B49" s="7" t="n"/>
+      <c r="C49" s="7" t="n"/>
+      <c r="D49" s="7" t="n"/>
+      <c r="E49" s="7" t="n"/>
+      <c r="F49" s="7" t="n"/>
+      <c r="G49" s="7" t="n"/>
+      <c r="H49" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12108,7 +12439,7 @@
           <t>Active scenario Y3 revenue per member</t>
         </is>
       </c>
-      <c r="B5" s="40">
+      <c r="B5" s="44">
         <f>Combined!D28</f>
         <v>67.6296196491228</v>
       </c>
@@ -12127,7 +12458,7 @@
       </c>
       <c r="B6" s="26">
         <f>Combined!D62</f>
-        <v>776113.7312640001</v>
+        <v>731863.7312640001</v>
       </c>
       <c r="C6" s="7" t="n"/>
       <c r="D6" s="7" t="n"/>
@@ -12152,25 +12483,25 @@
           <t>Members \ $ per member</t>
         </is>
       </c>
-      <c r="B8" s="41" t="n">
+      <c r="B8" s="45" t="n">
         <v>20</v>
       </c>
-      <c r="C8" s="41" t="n">
+      <c r="C8" s="45" t="n">
         <v>40</v>
       </c>
-      <c r="D8" s="41" t="n">
+      <c r="D8" s="45" t="n">
         <v>60</v>
       </c>
-      <c r="E8" s="41" t="n">
+      <c r="E8" s="45" t="n">
         <v>90</v>
       </c>
-      <c r="F8" s="41" t="n">
+      <c r="F8" s="45" t="n">
         <v>120</v>
       </c>
-      <c r="G8" s="41" t="n">
+      <c r="G8" s="45" t="n">
         <v>160</v>
       </c>
-      <c r="H8" s="41" t="n">
+      <c r="H8" s="45" t="n">
         <v>200</v>
       </c>
     </row>
@@ -12178,31 +12509,31 @@
       <c r="A9" s="18" t="n">
         <v>1000</v>
       </c>
-      <c r="B9" s="38">
+      <c r="B9" s="41">
         <f>$A9*B$8</f>
         <v>20000</v>
       </c>
-      <c r="C9" s="38">
+      <c r="C9" s="41">
         <f>$A9*C$8</f>
         <v>40000</v>
       </c>
-      <c r="D9" s="38">
+      <c r="D9" s="41">
         <f>$A9*D$8</f>
         <v>60000</v>
       </c>
-      <c r="E9" s="38">
+      <c r="E9" s="41">
         <f>$A9*E$8</f>
         <v>90000</v>
       </c>
-      <c r="F9" s="38">
+      <c r="F9" s="41">
         <f>$A9*F$8</f>
         <v>120000</v>
       </c>
-      <c r="G9" s="38">
+      <c r="G9" s="41">
         <f>$A9*G$8</f>
         <v>160000</v>
       </c>
-      <c r="H9" s="38">
+      <c r="H9" s="41">
         <f>$A9*H$8</f>
         <v>200000</v>
       </c>
@@ -12211,31 +12542,31 @@
       <c r="A10" s="18" t="n">
         <v>2500</v>
       </c>
-      <c r="B10" s="38">
+      <c r="B10" s="41">
         <f>$A10*B$8</f>
         <v>50000</v>
       </c>
-      <c r="C10" s="38">
+      <c r="C10" s="41">
         <f>$A10*C$8</f>
         <v>100000</v>
       </c>
-      <c r="D10" s="38">
+      <c r="D10" s="41">
         <f>$A10*D$8</f>
         <v>150000</v>
       </c>
-      <c r="E10" s="38">
+      <c r="E10" s="41">
         <f>$A10*E$8</f>
         <v>225000</v>
       </c>
-      <c r="F10" s="38">
+      <c r="F10" s="41">
         <f>$A10*F$8</f>
         <v>300000</v>
       </c>
-      <c r="G10" s="38">
+      <c r="G10" s="41">
         <f>$A10*G$8</f>
         <v>400000</v>
       </c>
-      <c r="H10" s="38">
+      <c r="H10" s="41">
         <f>$A10*H$8</f>
         <v>500000</v>
       </c>
@@ -12244,31 +12575,31 @@
       <c r="A11" s="18" t="n">
         <v>5000</v>
       </c>
-      <c r="B11" s="38">
+      <c r="B11" s="41">
         <f>$A11*B$8</f>
         <v>100000</v>
       </c>
-      <c r="C11" s="38">
+      <c r="C11" s="41">
         <f>$A11*C$8</f>
         <v>200000</v>
       </c>
-      <c r="D11" s="38">
+      <c r="D11" s="41">
         <f>$A11*D$8</f>
         <v>300000</v>
       </c>
-      <c r="E11" s="38">
+      <c r="E11" s="41">
         <f>$A11*E$8</f>
         <v>450000</v>
       </c>
-      <c r="F11" s="38">
+      <c r="F11" s="41">
         <f>$A11*F$8</f>
         <v>600000</v>
       </c>
-      <c r="G11" s="38">
+      <c r="G11" s="41">
         <f>$A11*G$8</f>
         <v>800000</v>
       </c>
-      <c r="H11" s="38">
+      <c r="H11" s="41">
         <f>$A11*H$8</f>
         <v>1000000</v>
       </c>
@@ -12277,31 +12608,31 @@
       <c r="A12" s="18" t="n">
         <v>10000</v>
       </c>
-      <c r="B12" s="38">
+      <c r="B12" s="41">
         <f>$A12*B$8</f>
         <v>200000</v>
       </c>
-      <c r="C12" s="38">
+      <c r="C12" s="41">
         <f>$A12*C$8</f>
         <v>400000</v>
       </c>
-      <c r="D12" s="38">
+      <c r="D12" s="41">
         <f>$A12*D$8</f>
         <v>600000</v>
       </c>
-      <c r="E12" s="38">
+      <c r="E12" s="41">
         <f>$A12*E$8</f>
         <v>900000</v>
       </c>
-      <c r="F12" s="38">
+      <c r="F12" s="41">
         <f>$A12*F$8</f>
         <v>1200000</v>
       </c>
-      <c r="G12" s="38">
+      <c r="G12" s="41">
         <f>$A12*G$8</f>
         <v>1600000</v>
       </c>
-      <c r="H12" s="38">
+      <c r="H12" s="41">
         <f>$A12*H$8</f>
         <v>2000000</v>
       </c>
@@ -12310,31 +12641,31 @@
       <c r="A13" s="18" t="n">
         <v>20000</v>
       </c>
-      <c r="B13" s="38">
+      <c r="B13" s="41">
         <f>$A13*B$8</f>
         <v>400000</v>
       </c>
-      <c r="C13" s="38">
+      <c r="C13" s="41">
         <f>$A13*C$8</f>
         <v>800000</v>
       </c>
-      <c r="D13" s="38">
+      <c r="D13" s="41">
         <f>$A13*D$8</f>
         <v>1200000</v>
       </c>
-      <c r="E13" s="38">
+      <c r="E13" s="41">
         <f>$A13*E$8</f>
         <v>1800000</v>
       </c>
-      <c r="F13" s="38">
+      <c r="F13" s="41">
         <f>$A13*F$8</f>
         <v>2400000</v>
       </c>
-      <c r="G13" s="38">
+      <c r="G13" s="41">
         <f>$A13*G$8</f>
         <v>3200000</v>
       </c>
-      <c r="H13" s="38">
+      <c r="H13" s="41">
         <f>$A13*H$8</f>
         <v>4000000</v>
       </c>
@@ -12343,31 +12674,31 @@
       <c r="A14" s="18" t="n">
         <v>40000</v>
       </c>
-      <c r="B14" s="38">
+      <c r="B14" s="41">
         <f>$A14*B$8</f>
         <v>800000</v>
       </c>
-      <c r="C14" s="38">
+      <c r="C14" s="41">
         <f>$A14*C$8</f>
         <v>1600000</v>
       </c>
-      <c r="D14" s="38">
+      <c r="D14" s="41">
         <f>$A14*D$8</f>
         <v>2400000</v>
       </c>
-      <c r="E14" s="38">
+      <c r="E14" s="41">
         <f>$A14*E$8</f>
         <v>3600000</v>
       </c>
-      <c r="F14" s="38">
+      <c r="F14" s="41">
         <f>$A14*F$8</f>
         <v>4800000</v>
       </c>
-      <c r="G14" s="38">
+      <c r="G14" s="41">
         <f>$A14*G$8</f>
         <v>6400000</v>
       </c>
-      <c r="H14" s="38">
+      <c r="H14" s="41">
         <f>$A14*H$8</f>
         <v>8000000</v>
       </c>

--- a/docs/financial-model-5yr-v2.xlsx
+++ b/docs/financial-model-5yr-v2.xlsx
@@ -176,9 +176,9 @@
     <xf numFmtId="164" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -640,7 +640,7 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>4b. The ask (Use of Funds sheet): an 18-month window at Base, what it spends by function, what it earns, and the net cash need; runway by raise size below it. Founder pay in Base is conditional on a first close of at least $150k and starts the month after it on a ramp ($4k/mo, then $5.5k/mo; $51k each in Y1, $78k in Y2, then $105k / $125k / $140k). The first employee (community &amp; partnerships lead) starts at month 18; the team is 2 / 2.5 / 4.5 / 7 / 8 FTE including founders (Headcount plan on the Use of Funds sheet).</t>
+          <t>4b. The ask (Use of Funds sheet): an 18-month window at Base, what it spends by function, what it earns, and the net cash need; runway by raise size below it. Founder pay in Base is conditional on a first close of at least $150k and starts the month after it on a ramp ($4k/mo, then $5.5k/mo; $51k each in Y1, $78k in Y2, then $105k / $125k / $140k). Part-time marketing and launch help from month 1 (0.25 FTE, 0.5 in Y2) and part-time coordinator hours; the first full-time employee (community &amp; partnerships lead) starts at month 18; the team is 2.25 / 3 / 4.5 / 7 / 8 FTE including founders (Headcount plan on the Use of Funds sheet).</t>
         </is>
       </c>
     </row>
@@ -4206,7 +4206,7 @@
     <row r="156">
       <c r="A156" s="11" t="inlineStr">
         <is>
-          <t>Marketing hires, FTE</t>
+          <t>Marketing and launch help, FTE (part-time before Y4)</t>
         </is>
       </c>
       <c r="B156" s="8" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="H156" s="8" t="inlineStr">
         <is>
-          <t>Base: a half-time marketer in Y3, full in Y4; contractors before that</t>
+          <t>Base: a quarter-time launch and content helper from month 1, half-time from Y2, full time in Y4; part-time help gets the launches done without a hire</t>
         </is>
       </c>
     </row>
@@ -4243,10 +4243,10 @@
         </is>
       </c>
       <c r="C157" s="18" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D157" s="18" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E157" s="18" t="n">
         <v>0.5</v>
@@ -4267,7 +4267,7 @@
         </is>
       </c>
       <c r="C158" s="18" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D158" s="18" t="n">
         <v>1</v>
@@ -4292,11 +4292,11 @@
       </c>
       <c r="C159" s="19">
         <f>CHOOSE(Inputs!$B$29,C156,C157,C158)</f>
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="D159" s="19">
         <f>CHOOSE(Inputs!$B$29,D156,D157,D158)</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E159" s="19">
         <f>CHOOSE(Inputs!$B$29,E156,E157,E158)</f>
@@ -9756,11 +9756,11 @@
       </c>
       <c r="B38" s="26">
         <f>Inputs!$C$159*Inputs!$B$25*(1+Inputs!$C$144)</f>
-        <v>0.0</v>
+        <v>21000.000000000004</v>
       </c>
       <c r="C38" s="26">
         <f>Inputs!$D$159*Inputs!$B$25*(1+Inputs!$D$144)</f>
-        <v>0.0</v>
+        <v>43125.0</v>
       </c>
       <c r="D38" s="26">
         <f>Inputs!$E$159*Inputs!$B$25*(1+Inputs!$E$144)</f>
@@ -9896,11 +9896,11 @@
       </c>
       <c r="B43" s="28">
         <f>SUM(B38:B42)</f>
-        <v>29000.0</v>
+        <v>50000.0</v>
       </c>
       <c r="C43" s="28">
         <f>SUM(C38:C42)</f>
-        <v>51000.0</v>
+        <v>94125.0</v>
       </c>
       <c r="D43" s="28">
         <f>SUM(D38:D42)</f>
@@ -10409,11 +10409,11 @@
       </c>
       <c r="B62" s="28">
         <f>B37+B43+B46+B52+B58+B60</f>
-        <v>207165.713538</v>
+        <v>228165.713538</v>
       </c>
       <c r="C62" s="28">
         <f>C37+C43+C46+C52+C58+C60</f>
-        <v>376952.580896</v>
+        <v>420077.580896</v>
       </c>
       <c r="D62" s="28">
         <f>D37+D43+D46+D52+D58+D60</f>
@@ -10437,11 +10437,11 @@
       </c>
       <c r="B63" s="27">
         <f>B32+B33+B38+B44+B47+B48+B53</f>
-        <v>114240.00000000001</v>
+        <v>135240.00000000003</v>
       </c>
       <c r="C63" s="27">
         <f>C32+C33+C38+C44+C47+C48+C53</f>
-        <v>216775</v>
+        <v>259900</v>
       </c>
       <c r="D63" s="27">
         <f>D32+D33+D38+D44+D47+D48+D53</f>
@@ -10493,11 +10493,11 @@
       </c>
       <c r="B65" s="31">
         <f>IF(B62=0,0,B63/B62)</f>
-        <v>0.5514426014276015</v>
+        <v>0.5927270925281961</v>
       </c>
       <c r="C65" s="31">
         <f>IF(C62=0,0,C63/C62)</f>
-        <v>0.5750723326651198</v>
+        <v>0.6186952406401909</v>
       </c>
       <c r="D65" s="31">
         <f>IF(D62=0,0,D63/D62)</f>
@@ -10543,11 +10543,11 @@
       </c>
       <c r="B68" s="28">
         <f>B14-B62</f>
-        <v>-170993.86813800002</v>
+        <v>-191993.86813800002</v>
       </c>
       <c r="C68" s="28">
         <f>C14-C62</f>
-        <v>-243589.06409600005</v>
+        <v>-286714.06409600005</v>
       </c>
       <c r="D68" s="28">
         <f>D14-D62</f>
@@ -10571,23 +10571,23 @@
       </c>
       <c r="B69" s="32">
         <f>MIN(0,B68)</f>
-        <v>-170993.86813800002</v>
+        <v>-191993.86813800002</v>
       </c>
       <c r="C69" s="32">
         <f>B69+C68</f>
-        <v>-414582.93223400007</v>
+        <v>-478707.93223400007</v>
       </c>
       <c r="D69" s="32">
         <f>C69+D68</f>
-        <v>-760957.8314980001</v>
+        <v>-825082.8314980001</v>
       </c>
       <c r="E69" s="32">
         <f>D69+E68</f>
-        <v>-1100746.2245860002</v>
+        <v>-1164871.2245860002</v>
       </c>
       <c r="F69" s="32">
         <f>E69+F68</f>
-        <v>-1107766.6969700002</v>
+        <v>-1171891.6969700002</v>
       </c>
       <c r="G69" s="8" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="B70" s="28">
         <f>-MIN(0,MIN(B69:F69))</f>
-        <v>1107766.6969700002</v>
+        <v>1171891.6969700002</v>
       </c>
       <c r="C70" s="28" t="inlineStr"/>
       <c r="D70" s="28" t="inlineStr"/>
@@ -10623,11 +10623,11 @@
       </c>
       <c r="B71" s="33">
         <f>2+Inputs!$C$149+Inputs!$C$154+Inputs!$C$159+Inputs!$C$164+Inputs!$C$169</f>
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="C71" s="33">
         <f>2+Inputs!$D$149+Inputs!$D$154+Inputs!$D$159+Inputs!$D$164+Inputs!$D$169</f>
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="D71" s="33">
         <f>2+Inputs!$E$149+Inputs!$E$154+Inputs!$E$159+Inputs!$E$164+Inputs!$E$169</f>
@@ -10651,11 +10651,11 @@
       </c>
       <c r="B72" s="27">
         <f>B14/B71</f>
-        <v>18085.922700000003</v>
+        <v>16076.375733333336</v>
       </c>
       <c r="C72" s="27">
         <f>C14/C71</f>
-        <v>53345.40671999999</v>
+        <v>44454.5056</v>
       </c>
       <c r="D72" s="27">
         <f>D14/D71</f>
@@ -11215,7 +11215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -11410,7 +11410,7 @@
       </c>
       <c r="C11" s="38">
         <f>IF(B17=0,0,B11/B17)</f>
-        <v>0.4245188789558938</v>
+        <v>0.38328565423728733</v>
       </c>
       <c r="D11" s="26">
         <f>Combined!B37</f>
@@ -11442,19 +11442,19 @@
       </c>
       <c r="B12" s="26">
         <f>Combined!B43*$B$6+Combined!C43*$B$7</f>
-        <v>54500</v>
+        <v>97062.5</v>
       </c>
       <c r="C12" s="38">
         <f>IF(B17=0,0,B12/B17)</f>
-        <v>0.13775079352274364</v>
+        <v>0.22150046180972388</v>
       </c>
       <c r="D12" s="26">
         <f>Combined!B43</f>
-        <v>29000.0</v>
+        <v>50000.0</v>
       </c>
       <c r="E12" s="26">
         <f>Combined!C43</f>
-        <v>51000.0</v>
+        <v>94125.0</v>
       </c>
       <c r="F12" s="26">
         <f>Combined!D43</f>
@@ -11482,7 +11482,7 @@
       </c>
       <c r="C13" s="38">
         <f>IF(B17=0,0,B13/B17)</f>
-        <v>0.012637687479150792</v>
+        <v>0.011410197646347656</v>
       </c>
       <c r="D13" s="26">
         <f>Combined!B46</f>
@@ -11518,7 +11518,7 @@
       </c>
       <c r="C14" s="38">
         <f>IF(B17=0,0,B14/B17)</f>
-        <v>0.3196576670976401</v>
+        <v>0.2886095392667176</v>
       </c>
       <c r="D14" s="26">
         <f>Combined!B52</f>
@@ -11554,7 +11554,7 @@
       </c>
       <c r="C15" s="38">
         <f>IF(B17=0,0,B15/B17)</f>
-        <v>0.08720004360614046</v>
+        <v>0.07873036375979883</v>
       </c>
       <c r="D15" s="26">
         <f>Combined!B58</f>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="C16" s="38">
         <f>IF(B17=0,0,B16/B17)</f>
-        <v>0.018234929338431138</v>
+        <v>0.016463783280124603</v>
       </c>
       <c r="D16" s="26">
         <f>Combined!B60</f>
@@ -11622,16 +11622,16 @@
       </c>
       <c r="B17" s="32">
         <f>SUM(B11:B16)</f>
-        <v>395642.003986</v>
+        <v>438204.503986</v>
       </c>
       <c r="C17" s="7" t="n"/>
       <c r="D17" s="32">
         <f>SUM(D11:D16)</f>
-        <v>207165.713538</v>
+        <v>228165.713538</v>
       </c>
       <c r="E17" s="32">
         <f>SUM(E11:E16)</f>
-        <v>376952.580896</v>
+        <v>420077.580896</v>
       </c>
       <c r="F17" s="32">
         <f>SUM(F11:F16)</f>
@@ -11655,7 +11655,7 @@
       </c>
       <c r="C18" s="38">
         <f>IF(B17=0,0,B18/B17)</f>
-        <v>0.5154659968996025</v>
+        <v>0.46539914159922824</v>
       </c>
       <c r="D18" s="26">
         <f>Combined!B64</f>
@@ -11678,114 +11678,156 @@
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
+          <t xml:space="preserve">    founder 2 (Haley), loaded, inside Programs &amp; community</t>
+        </is>
+      </c>
+      <c r="B19" s="26">
+        <f>Combined!B32*$B$6+Combined!C32*$B$7</f>
+        <v>101970.0</v>
+      </c>
+      <c r="C19" s="7" t="n"/>
+      <c r="D19" s="26">
+        <f>Combined!B32</f>
+        <v>57120.00000000001</v>
+      </c>
+      <c r="E19" s="26">
+        <f>Combined!C32</f>
+        <v>89700.0</v>
+      </c>
+      <c r="F19" s="26">
+        <f>Combined!D32</f>
+        <v>123900.0</v>
+      </c>
+      <c r="G19" s="26">
+        <f>Combined!E32</f>
+        <v>150000.0</v>
+      </c>
+      <c r="H19" s="8" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    founder 1 (Rick), loaded, inside Engineering &amp; platform</t>
+        </is>
+      </c>
+      <c r="B20" s="26">
+        <f>Combined!B47*$B$6+Combined!C47*$B$7</f>
+        <v>101970.0</v>
+      </c>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="26">
+        <f>Combined!B47</f>
+        <v>57120.00000000001</v>
+      </c>
+      <c r="E20" s="26">
+        <f>Combined!C47</f>
+        <v>89700.0</v>
+      </c>
+      <c r="F20" s="26">
+        <f>Combined!D47</f>
+        <v>123900.0</v>
+      </c>
+      <c r="G20" s="26">
+        <f>Combined!E47</f>
+        <v>150000.0</v>
+      </c>
+      <c r="H20" s="8" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>Programs &amp; community excluding founder pay</t>
+        </is>
+      </c>
+      <c r="B21" s="39">
+        <f>B11-B19</f>
+        <v>65987.5</v>
+      </c>
+      <c r="C21" s="38">
+        <f>IF(B17=0,0,B21/B17)</f>
+        <v>0.1505860834376732</v>
+      </c>
+      <c r="D21" s="39">
+        <f>D11-D19</f>
+        <v>25599.999999999993</v>
+      </c>
+      <c r="E21" s="39">
+        <f>E11-E19</f>
+        <v>80775</v>
+      </c>
+      <c r="F21" s="39">
+        <f>F11-F19</f>
+        <v>127820</v>
+      </c>
+      <c r="G21" s="39">
+        <f>G11-G19</f>
+        <v>172000</v>
+      </c>
+      <c r="H21" s="7" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>Engineering &amp; platform excluding founder pay</t>
+        </is>
+      </c>
+      <c r="B22" s="39">
+        <f>B14-B20</f>
+        <v>24500</v>
+      </c>
+      <c r="C22" s="38">
+        <f>IF(B17=0,0,B22/B17)</f>
+        <v>0.05590996846710352</v>
+      </c>
+      <c r="D22" s="39">
+        <f>D14-D20</f>
+        <v>12499.999999999993</v>
+      </c>
+      <c r="E22" s="39">
+        <f>E14-E20</f>
+        <v>24000</v>
+      </c>
+      <c r="F22" s="39">
+        <f>F14-F20</f>
+        <v>112700</v>
+      </c>
+      <c r="G22" s="39">
+        <f>G14-G20</f>
+        <v>205000</v>
+      </c>
+      <c r="H22" s="7" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">  of which all people (founders + staff, loaded)</t>
         </is>
       </c>
-      <c r="B19" s="26">
+      <c r="B23" s="26">
         <f>Combined!B63*$B$6+Combined!C63*$B$7</f>
-        <v>222627.5</v>
-      </c>
-      <c r="C19" s="38">
-        <f>IF(B17=0,0,B19/B17)</f>
-        <v>0.5626993538529286</v>
-      </c>
-      <c r="D19" s="26">
+        <v>265190.0</v>
+      </c>
+      <c r="C23" s="38">
+        <f>IF(B17=0,0,B23/B17)</f>
+        <v>0.605174062766987</v>
+      </c>
+      <c r="D23" s="26">
         <f>Combined!B63</f>
-        <v>114240.00000000001</v>
-      </c>
-      <c r="E19" s="26">
+        <v>135240.00000000003</v>
+      </c>
+      <c r="E23" s="26">
         <f>Combined!C63</f>
-        <v>216775</v>
-      </c>
-      <c r="F19" s="26">
+        <v>259900</v>
+      </c>
+      <c r="F23" s="26">
         <f>Combined!D63</f>
         <v>477900</v>
       </c>
-      <c r="G19" s="26">
+      <c r="G23" s="26">
         <f>Combined!E63</f>
         <v>771000</v>
       </c>
-      <c r="H19" s="7" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="n"/>
-      <c r="B20" s="7" t="n"/>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="7" t="n"/>
-      <c r="F20" s="7" t="n"/>
-      <c r="G20" s="7" t="n"/>
-      <c r="H20" s="7" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>Platform revenue in the window</t>
-        </is>
-      </c>
-      <c r="B21" s="26">
-        <f>Combined!B14*$B$6+Combined!C14*$B$7</f>
-        <v>102853.6038</v>
-      </c>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="26">
-        <f>Combined!B14</f>
-        <v>36171.845400000006</v>
-      </c>
-      <c r="E21" s="26">
-        <f>Combined!C14</f>
-        <v>133363.51679999998</v>
-      </c>
-      <c r="F21" s="26">
-        <f>Combined!D14</f>
-        <v>385488.832</v>
-      </c>
-      <c r="G21" s="26">
-        <f>Combined!E14</f>
-        <v>810207.792</v>
-      </c>
-      <c r="H21" s="7" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>NET CASH NEED IN THE WINDOW (spend less revenue)</t>
-        </is>
-      </c>
-      <c r="B22" s="32">
-        <f>B17-B21</f>
-        <v>292788.40018600004</v>
-      </c>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
-      <c r="E22" s="7" t="n"/>
-      <c r="F22" s="7" t="n"/>
-      <c r="G22" s="7" t="n"/>
-      <c r="H22" s="7" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>Raise less net need (cushion)</t>
-        </is>
-      </c>
-      <c r="B23" s="32">
-        <f>B4-B22</f>
-        <v>57211.59981399996</v>
-      </c>
-      <c r="C23" s="38">
-        <f>IF(B22=0,0,B23/B22)</f>
-        <v>0.19540254934162377</v>
-      </c>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="7" t="n"/>
-      <c r="F23" s="7" t="n"/>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>negative = the raise does not cover the window</t>
-        </is>
-      </c>
+      <c r="H23" s="7" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n"/>
@@ -11798,391 +11840,389 @@
       <c r="H24" s="7" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>Headcount plan (FTE by year; founders first, then hires gated on revenue)</t>
-        </is>
-      </c>
-      <c r="B25" s="10" t="n"/>
-      <c r="C25" s="10" t="n"/>
-      <c r="D25" s="10" t="n"/>
-      <c r="E25" s="10" t="n"/>
-      <c r="F25" s="10" t="n"/>
-      <c r="G25" s="10" t="n"/>
-      <c r="H25" s="10" t="n"/>
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>Platform revenue in the window</t>
+        </is>
+      </c>
+      <c r="B25" s="26">
+        <f>Combined!B14*$B$6+Combined!C14*$B$7</f>
+        <v>102853.6038</v>
+      </c>
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="26">
+        <f>Combined!B14</f>
+        <v>36171.845400000006</v>
+      </c>
+      <c r="E25" s="26">
+        <f>Combined!C14</f>
+        <v>133363.51679999998</v>
+      </c>
+      <c r="F25" s="26">
+        <f>Combined!D14</f>
+        <v>385488.832</v>
+      </c>
+      <c r="G25" s="26">
+        <f>Combined!E14</f>
+        <v>810207.792</v>
+      </c>
+      <c r="H25" s="7" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="17" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr"/>
-      <c r="C26" s="17" t="inlineStr"/>
-      <c r="D26" s="17" t="inlineStr">
-        <is>
-          <t>Y1</t>
-        </is>
-      </c>
-      <c r="E26" s="17" t="inlineStr">
-        <is>
-          <t>Y2</t>
-        </is>
-      </c>
-      <c r="F26" s="17" t="inlineStr">
-        <is>
-          <t>Y3</t>
-        </is>
-      </c>
-      <c r="G26" s="17" t="inlineStr">
-        <is>
-          <t>Y4</t>
-        </is>
-      </c>
-      <c r="H26" s="17" t="inlineStr">
-        <is>
-          <t>Y5</t>
-        </is>
-      </c>
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>NET CASH NEED IN THE WINDOW (spend less revenue)</t>
+        </is>
+      </c>
+      <c r="B26" s="32">
+        <f>B17-B25</f>
+        <v>335350.90018600004</v>
+      </c>
+      <c r="C26" s="7" t="n"/>
+      <c r="D26" s="7" t="n"/>
+      <c r="E26" s="7" t="n"/>
+      <c r="F26" s="7" t="n"/>
+      <c r="G26" s="7" t="n"/>
+      <c r="H26" s="7" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>Founders (Rick: product &amp; engineering; Haley: community &amp; programs)</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="n"/>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="E27" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="F27" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="G27" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="H27" s="39" t="n">
-        <v>2</v>
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>Raise less net need (cushion)</t>
+        </is>
+      </c>
+      <c r="B27" s="32">
+        <f>B4-B26</f>
+        <v>14649.099813999957</v>
+      </c>
+      <c r="C27" s="38">
+        <f>IF(B26=0,0,B27/B26)</f>
+        <v>0.0436828999292232</v>
+      </c>
+      <c r="D27" s="7" t="n"/>
+      <c r="E27" s="7" t="n"/>
+      <c r="F27" s="7" t="n"/>
+      <c r="G27" s="7" t="n"/>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>negative = the raise does not cover the window</t>
+        </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="inlineStr">
-        <is>
-          <t>Community &amp; partnerships</t>
-        </is>
-      </c>
+      <c r="A28" s="7" t="n"/>
       <c r="B28" s="7" t="n"/>
       <c r="C28" s="7" t="n"/>
-      <c r="D28" s="33">
-        <f>Inputs!$C$149</f>
-        <v>0</v>
-      </c>
-      <c r="E28" s="33">
-        <f>Inputs!$D$149</f>
-        <v>0.5</v>
-      </c>
-      <c r="F28" s="33">
-        <f>Inputs!$E$149</f>
-        <v>1</v>
-      </c>
-      <c r="G28" s="33">
-        <f>Inputs!$F$149</f>
-        <v>1.5</v>
-      </c>
-      <c r="H28" s="33">
-        <f>Inputs!$G$149</f>
-        <v>2</v>
-      </c>
+      <c r="D28" s="7" t="n"/>
+      <c r="E28" s="7" t="n"/>
+      <c r="F28" s="7" t="n"/>
+      <c r="G28" s="7" t="n"/>
+      <c r="H28" s="7" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t>Member support</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="n"/>
-      <c r="C29" s="7" t="n"/>
-      <c r="D29" s="33">
-        <f>Inputs!$C$154</f>
-        <v>0</v>
-      </c>
-      <c r="E29" s="33">
-        <f>Inputs!$D$154</f>
-        <v>0</v>
-      </c>
-      <c r="F29" s="33">
-        <f>Inputs!$E$154</f>
-        <v>0.5</v>
-      </c>
-      <c r="G29" s="33">
-        <f>Inputs!$F$154</f>
-        <v>1</v>
-      </c>
-      <c r="H29" s="33">
-        <f>Inputs!$G$154</f>
-        <v>1</v>
-      </c>
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>Headcount plan (FTE by year; founders first, then hires gated on revenue)</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="10" t="n"/>
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="10" t="n"/>
+      <c r="F29" s="10" t="n"/>
+      <c r="G29" s="10" t="n"/>
+      <c r="H29" s="10" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="inlineStr">
-        <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="n"/>
-      <c r="C30" s="7" t="n"/>
-      <c r="D30" s="33">
-        <f>Inputs!$C$159</f>
-        <v>0</v>
-      </c>
-      <c r="E30" s="33">
-        <f>Inputs!$D$159</f>
-        <v>0</v>
-      </c>
-      <c r="F30" s="33">
-        <f>Inputs!$E$159</f>
-        <v>0.5</v>
-      </c>
-      <c r="G30" s="33">
-        <f>Inputs!$F$159</f>
-        <v>1</v>
-      </c>
-      <c r="H30" s="33">
-        <f>Inputs!$G$159</f>
-        <v>1</v>
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="inlineStr"/>
+      <c r="C30" s="17" t="inlineStr"/>
+      <c r="D30" s="17" t="inlineStr">
+        <is>
+          <t>Y1</t>
+        </is>
+      </c>
+      <c r="E30" s="17" t="inlineStr">
+        <is>
+          <t>Y2</t>
+        </is>
+      </c>
+      <c r="F30" s="17" t="inlineStr">
+        <is>
+          <t>Y3</t>
+        </is>
+      </c>
+      <c r="G30" s="17" t="inlineStr">
+        <is>
+          <t>Y4</t>
+        </is>
+      </c>
+      <c r="H30" s="17" t="inlineStr">
+        <is>
+          <t>Y5</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Founders (Rick: product &amp; engineering; Haley: community &amp; programs)</t>
         </is>
       </c>
       <c r="B31" s="7" t="n"/>
       <c r="C31" s="7" t="n"/>
-      <c r="D31" s="33">
-        <f>Inputs!$C$164</f>
-        <v>0</v>
-      </c>
-      <c r="E31" s="33">
-        <f>Inputs!$D$164</f>
-        <v>0</v>
-      </c>
-      <c r="F31" s="33">
-        <f>Inputs!$E$164</f>
-        <v>0.5</v>
-      </c>
-      <c r="G31" s="33">
-        <f>Inputs!$F$164</f>
-        <v>1</v>
-      </c>
-      <c r="H31" s="33">
-        <f>Inputs!$G$164</f>
-        <v>1.5</v>
+      <c r="D31" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="G31" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="H31" s="40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>Operations / finance</t>
+          <t>Community &amp; partnerships</t>
         </is>
       </c>
       <c r="B32" s="7" t="n"/>
       <c r="C32" s="7" t="n"/>
       <c r="D32" s="33">
+        <f>Inputs!$C$149</f>
+        <v>0</v>
+      </c>
+      <c r="E32" s="33">
+        <f>Inputs!$D$149</f>
+        <v>0.5</v>
+      </c>
+      <c r="F32" s="33">
+        <f>Inputs!$E$149</f>
+        <v>1</v>
+      </c>
+      <c r="G32" s="33">
+        <f>Inputs!$F$149</f>
+        <v>1.5</v>
+      </c>
+      <c r="H32" s="33">
+        <f>Inputs!$G$149</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>Member support</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="n"/>
+      <c r="C33" s="7" t="n"/>
+      <c r="D33" s="33">
+        <f>Inputs!$C$154</f>
+        <v>0</v>
+      </c>
+      <c r="E33" s="33">
+        <f>Inputs!$D$154</f>
+        <v>0</v>
+      </c>
+      <c r="F33" s="33">
+        <f>Inputs!$E$154</f>
+        <v>0.5</v>
+      </c>
+      <c r="G33" s="33">
+        <f>Inputs!$F$154</f>
+        <v>1</v>
+      </c>
+      <c r="H33" s="33">
+        <f>Inputs!$G$154</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="n"/>
+      <c r="C34" s="7" t="n"/>
+      <c r="D34" s="33">
+        <f>Inputs!$C$159</f>
+        <v>0.25</v>
+      </c>
+      <c r="E34" s="33">
+        <f>Inputs!$D$159</f>
+        <v>0.5</v>
+      </c>
+      <c r="F34" s="33">
+        <f>Inputs!$E$159</f>
+        <v>0.5</v>
+      </c>
+      <c r="G34" s="33">
+        <f>Inputs!$F$159</f>
+        <v>1</v>
+      </c>
+      <c r="H34" s="33">
+        <f>Inputs!$G$159</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="n"/>
+      <c r="C35" s="7" t="n"/>
+      <c r="D35" s="33">
+        <f>Inputs!$C$164</f>
+        <v>0</v>
+      </c>
+      <c r="E35" s="33">
+        <f>Inputs!$D$164</f>
+        <v>0</v>
+      </c>
+      <c r="F35" s="33">
+        <f>Inputs!$E$164</f>
+        <v>0.5</v>
+      </c>
+      <c r="G35" s="33">
+        <f>Inputs!$F$164</f>
+        <v>1</v>
+      </c>
+      <c r="H35" s="33">
+        <f>Inputs!$G$164</f>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>Operations / finance</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="n"/>
+      <c r="C36" s="7" t="n"/>
+      <c r="D36" s="33">
         <f>Inputs!$C$169</f>
         <v>0</v>
       </c>
-      <c r="E32" s="33">
+      <c r="E36" s="33">
         <f>Inputs!$D$169</f>
         <v>0</v>
       </c>
-      <c r="F32" s="33">
+      <c r="F36" s="33">
         <f>Inputs!$E$169</f>
         <v>0</v>
       </c>
-      <c r="G32" s="33">
+      <c r="G36" s="33">
         <f>Inputs!$F$169</f>
         <v>0.5</v>
       </c>
-      <c r="H32" s="33">
+      <c r="H36" s="33">
         <f>Inputs!$G$169</f>
         <v>0.5</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="15" t="inlineStr">
         <is>
           <t>TOTAL FTE</t>
         </is>
       </c>
-      <c r="B33" s="7" t="n"/>
-      <c r="C33" s="7" t="n"/>
-      <c r="D33" s="40">
-        <f>SUM(D27:D32)</f>
-        <v>2</v>
-      </c>
-      <c r="E33" s="40">
-        <f>SUM(E27:E32)</f>
-        <v>2.5</v>
-      </c>
-      <c r="F33" s="40">
-        <f>SUM(F27:F32)</f>
+      <c r="B37" s="7" t="n"/>
+      <c r="C37" s="7" t="n"/>
+      <c r="D37" s="41">
+        <f>SUM(D31:D36)</f>
+        <v>2.25</v>
+      </c>
+      <c r="E37" s="41">
+        <f>SUM(E31:E36)</f>
+        <v>3.0</v>
+      </c>
+      <c r="F37" s="41">
+        <f>SUM(F31:F36)</f>
         <v>4.5</v>
       </c>
-      <c r="G33" s="40">
-        <f>SUM(G27:G32)</f>
+      <c r="G37" s="41">
+        <f>SUM(G31:G36)</f>
         <v>7.0</v>
       </c>
-      <c r="H33" s="40">
-        <f>SUM(H27:H32)</f>
+      <c r="H37" s="41">
+        <f>SUM(H31:H36)</f>
         <v>8.0</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="11" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>Revenue per FTE</t>
         </is>
       </c>
-      <c r="B34" s="7" t="n"/>
-      <c r="C34" s="7" t="n"/>
-      <c r="D34" s="41">
-        <f>IF(D33=0,0,Combined!B14/D33)</f>
-        <v>18085.922700000003</v>
-      </c>
-      <c r="E34" s="41">
-        <f>IF(E33=0,0,Combined!C14/E33)</f>
-        <v>53345.40671999999</v>
-      </c>
-      <c r="F34" s="41">
-        <f>IF(F33=0,0,Combined!D14/F33)</f>
+      <c r="B38" s="7" t="n"/>
+      <c r="C38" s="7" t="n"/>
+      <c r="D38" s="39">
+        <f>IF(D37=0,0,Combined!B14/D37)</f>
+        <v>16076.375733333336</v>
+      </c>
+      <c r="E38" s="39">
+        <f>IF(E37=0,0,Combined!C14/E37)</f>
+        <v>44454.5056</v>
+      </c>
+      <c r="F38" s="39">
+        <f>IF(F37=0,0,Combined!D14/F37)</f>
         <v>85664.18488888889</v>
       </c>
-      <c r="G34" s="41">
-        <f>IF(G33=0,0,Combined!E14/G33)</f>
+      <c r="G38" s="39">
+        <f>IF(G37=0,0,Combined!E14/G37)</f>
         <v>115743.97028571428</v>
       </c>
-      <c r="H34" s="41">
-        <f>IF(H33=0,0,Combined!F14/H33)</f>
+      <c r="H38" s="39">
+        <f>IF(H37=0,0,Combined!F14/H37)</f>
         <v>183972.052</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="11" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>Founder pay, each (cash paid in the year)</t>
         </is>
       </c>
-      <c r="B35" s="7" t="n"/>
-      <c r="C35" s="7" t="n"/>
-      <c r="D35" s="26">
+      <c r="B39" s="7" t="n"/>
+      <c r="C39" s="7" t="n"/>
+      <c r="D39" s="26">
         <f>Inputs!$C$134</f>
         <v>51000</v>
       </c>
-      <c r="E35" s="26">
+      <c r="E39" s="26">
         <f>Inputs!$D$134</f>
         <v>78000</v>
       </c>
-      <c r="F35" s="26">
+      <c r="F39" s="26">
         <f>Inputs!$E$134</f>
         <v>105000</v>
       </c>
-      <c r="G35" s="26">
+      <c r="G39" s="26">
         <f>Inputs!$F$134</f>
         <v>125000</v>
       </c>
-      <c r="H35" s="42" t="inlineStr">
+      <c r="H39" s="42" t="inlineStr">
         <is>
           <t>conditional on a first close of at least $150k; starts the month after, on a ramp</t>
         </is>
       </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="n"/>
-      <c r="B36" s="7" t="n"/>
-      <c r="C36" s="7" t="n"/>
-      <c r="D36" s="7" t="n"/>
-      <c r="E36" s="7" t="n"/>
-      <c r="F36" s="7" t="n"/>
-      <c r="G36" s="7" t="n"/>
-      <c r="H36" s="7" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="9" t="inlineStr">
-        <is>
-          <t>Runway by raise size (active scenario; burn = costs less revenue, spent evenly within each year)</t>
-        </is>
-      </c>
-      <c r="B37" s="10" t="n"/>
-      <c r="C37" s="10" t="n"/>
-      <c r="D37" s="10" t="n"/>
-      <c r="E37" s="10" t="n"/>
-      <c r="F37" s="10" t="n"/>
-      <c r="G37" s="10" t="n"/>
-      <c r="H37" s="10" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="15" t="inlineStr">
-        <is>
-          <t>Net burn by year</t>
-        </is>
-      </c>
-      <c r="B38" s="26">
-        <f>MAX(0,Combined!B62-Combined!B14)</f>
-        <v>170993.86813800002</v>
-      </c>
-      <c r="C38" s="26">
-        <f>MAX(0,Combined!C62-Combined!C14)</f>
-        <v>243589.06409600005</v>
-      </c>
-      <c r="D38" s="26">
-        <f>MAX(0,Combined!D62-Combined!D14)</f>
-        <v>346374.89926400007</v>
-      </c>
-      <c r="E38" s="26">
-        <f>MAX(0,Combined!E62-Combined!E14)</f>
-        <v>339788.393088</v>
-      </c>
-      <c r="F38" s="26">
-        <f>MAX(0,Combined!F62-Combined!F14)</f>
-        <v>7020.472383999964</v>
-      </c>
-      <c r="G38" s="7" t="n"/>
-      <c r="H38" s="7" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="11" t="inlineStr">
-        <is>
-          <t>Monthly burn by year</t>
-        </is>
-      </c>
-      <c r="B39" s="41">
-        <f>B38/12</f>
-        <v>14249.489011500002</v>
-      </c>
-      <c r="C39" s="41">
-        <f>C38/12</f>
-        <v>20299.08867466667</v>
-      </c>
-      <c r="D39" s="41">
-        <f>D38/12</f>
-        <v>28864.574938666672</v>
-      </c>
-      <c r="E39" s="41">
-        <f>E38/12</f>
-        <v>28315.699424000002</v>
-      </c>
-      <c r="F39" s="41">
-        <f>F38/12</f>
-        <v>585.0393653333304</v>
-      </c>
-      <c r="G39" s="7" t="n"/>
-      <c r="H39" s="7" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n"/>
@@ -12195,78 +12235,81 @@
       <c r="H40" s="7" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="17" t="inlineStr">
-        <is>
-          <t>Raise, $</t>
-        </is>
-      </c>
-      <c r="B41" s="17" t="inlineStr">
-        <is>
-          <t>Runway, months</t>
-        </is>
-      </c>
-      <c r="C41" s="17" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="n"/>
-      <c r="E41" s="7" t="n"/>
-      <c r="F41" s="7" t="n"/>
-      <c r="G41" s="7" t="n"/>
-      <c r="H41" s="7" t="n"/>
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>Runway by raise size (active scenario; burn = costs less revenue, spent evenly within each year)</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="n"/>
+      <c r="C41" s="10" t="n"/>
+      <c r="D41" s="10" t="n"/>
+      <c r="E41" s="10" t="n"/>
+      <c r="F41" s="10" t="n"/>
+      <c r="G41" s="10" t="n"/>
+      <c r="H41" s="10" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="12" t="n">
-        <v>150000</v>
-      </c>
-      <c r="B42" s="43">
-        <f>MIN(60,IF(A42&lt;=$B$38,A42/MAX(1,$B$38/12),IF(A42&lt;=$B$38+$C$38,12+(A42-$B$38)/MAX(1,$C$38/12),IF(A42&lt;=$B$38+$C$38+$D$38,24+(A42-$B$38-$C$38)/MAX(1,$D$38/12),IF(A42&lt;=$B$38+$C$38+$D$38+$E$38,36+(A42-$B$38-$C$38-$D$38)/MAX(1,$E$38/12),IF(A42&lt;=$B$38+$C$38+$D$38+$E$38+$F$38,48+(A42-$B$38-$C$38-$D$38-$E$38)/MAX(1,$F$38/12),60))))))</f>
-        <v>10.526693264505345</v>
-      </c>
-      <c r="C42" s="8" t="inlineStr">
-        <is>
-          <t>60 = the raise outlasts the five-year model</t>
-        </is>
-      </c>
-      <c r="D42" s="7" t="n"/>
-      <c r="E42" s="7" t="n"/>
-      <c r="F42" s="7" t="n"/>
+      <c r="A42" s="15" t="inlineStr">
+        <is>
+          <t>Net burn by year</t>
+        </is>
+      </c>
+      <c r="B42" s="26">
+        <f>MAX(0,Combined!B62-Combined!B14)</f>
+        <v>191993.86813800002</v>
+      </c>
+      <c r="C42" s="26">
+        <f>MAX(0,Combined!C62-Combined!C14)</f>
+        <v>286714.06409600005</v>
+      </c>
+      <c r="D42" s="26">
+        <f>MAX(0,Combined!D62-Combined!D14)</f>
+        <v>346374.89926400007</v>
+      </c>
+      <c r="E42" s="26">
+        <f>MAX(0,Combined!E62-Combined!E14)</f>
+        <v>339788.393088</v>
+      </c>
+      <c r="F42" s="26">
+        <f>MAX(0,Combined!F62-Combined!F14)</f>
+        <v>7020.472383999964</v>
+      </c>
       <c r="G42" s="7" t="n"/>
       <c r="H42" s="7" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="12" t="n">
-        <v>250000</v>
-      </c>
-      <c r="B43" s="43">
-        <f>MIN(60,IF(A43&lt;=$B$38,A43/MAX(1,$B$38/12),IF(A43&lt;=$B$38+$C$38,12+(A43-$B$38)/MAX(1,$C$38/12),IF(A43&lt;=$B$38+$C$38+$D$38,24+(A43-$B$38-$C$38)/MAX(1,$D$38/12),IF(A43&lt;=$B$38+$C$38+$D$38+$E$38,36+(A43-$B$38-$C$38-$D$38)/MAX(1,$E$38/12),IF(A43&lt;=$B$38+$C$38+$D$38+$E$38+$F$38,48+(A43-$B$38-$C$38-$D$38-$E$38)/MAX(1,$F$38/12),60))))))</f>
-        <v>15.892102405592222</v>
-      </c>
-      <c r="C43" s="8" t="inlineStr">
-        <is>
-          <t>60 = the raise outlasts the five-year model</t>
-        </is>
-      </c>
-      <c r="D43" s="7" t="n"/>
-      <c r="E43" s="7" t="n"/>
-      <c r="F43" s="7" t="n"/>
+      <c r="A43" s="11" t="inlineStr">
+        <is>
+          <t>Monthly burn by year</t>
+        </is>
+      </c>
+      <c r="B43" s="39">
+        <f>B42/12</f>
+        <v>15999.489011500002</v>
+      </c>
+      <c r="C43" s="39">
+        <f>C42/12</f>
+        <v>23892.83867466667</v>
+      </c>
+      <c r="D43" s="39">
+        <f>D42/12</f>
+        <v>28864.574938666672</v>
+      </c>
+      <c r="E43" s="39">
+        <f>E42/12</f>
+        <v>28315.699424000002</v>
+      </c>
+      <c r="F43" s="39">
+        <f>F42/12</f>
+        <v>585.0393653333304</v>
+      </c>
       <c r="G43" s="7" t="n"/>
       <c r="H43" s="7" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="12" t="n">
-        <v>350000</v>
-      </c>
-      <c r="B44" s="43">
-        <f>MIN(60,IF(A44&lt;=$B$38,A44/MAX(1,$B$38/12),IF(A44&lt;=$B$38+$C$38,12+(A44-$B$38)/MAX(1,$C$38/12),IF(A44&lt;=$B$38+$C$38+$D$38,24+(A44-$B$38-$C$38)/MAX(1,$D$38/12),IF(A44&lt;=$B$38+$C$38+$D$38+$E$38,36+(A44-$B$38-$C$38-$D$38)/MAX(1,$E$38/12),IF(A44&lt;=$B$38+$C$38+$D$38+$E$38+$F$38,48+(A44-$B$38-$C$38-$D$38-$E$38)/MAX(1,$F$38/12),60))))))</f>
-        <v>20.818431937065245</v>
-      </c>
-      <c r="C44" s="8" t="inlineStr">
-        <is>
-          <t>60 = the raise outlasts the five-year model</t>
-        </is>
-      </c>
+      <c r="A44" s="7" t="n"/>
+      <c r="B44" s="7" t="n"/>
+      <c r="C44" s="7" t="n"/>
       <c r="D44" s="7" t="n"/>
       <c r="E44" s="7" t="n"/>
       <c r="F44" s="7" t="n"/>
@@ -12274,16 +12317,19 @@
       <c r="H44" s="7" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="12" t="n">
-        <v>500000</v>
-      </c>
-      <c r="B45" s="43">
-        <f>MIN(60,IF(A45&lt;=$B$38,A45/MAX(1,$B$38/12),IF(A45&lt;=$B$38+$C$38,12+(A45-$B$38)/MAX(1,$C$38/12),IF(A45&lt;=$B$38+$C$38+$D$38,24+(A45-$B$38-$C$38)/MAX(1,$D$38/12),IF(A45&lt;=$B$38+$C$38+$D$38+$E$38,36+(A45-$B$38-$C$38-$D$38)/MAX(1,$E$38/12),IF(A45&lt;=$B$38+$C$38+$D$38+$E$38+$F$38,48+(A45-$B$38-$C$38-$D$38-$E$38)/MAX(1,$F$38/12),60))))))</f>
-        <v>26.959235254546435</v>
-      </c>
-      <c r="C45" s="8" t="inlineStr">
-        <is>
-          <t>60 = the raise outlasts the five-year model</t>
+      <c r="A45" s="17" t="inlineStr">
+        <is>
+          <t>Raise, $</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="inlineStr">
+        <is>
+          <t>Runway, months</t>
+        </is>
+      </c>
+      <c r="C45" s="17" t="inlineStr">
+        <is>
+          <t>Note</t>
         </is>
       </c>
       <c r="D45" s="7" t="n"/>
@@ -12294,11 +12340,11 @@
     </row>
     <row r="46">
       <c r="A46" s="12" t="n">
-        <v>650000</v>
+        <v>150000</v>
       </c>
       <c r="B46" s="43">
-        <f>MIN(60,IF(A46&lt;=$B$38,A46/MAX(1,$B$38/12),IF(A46&lt;=$B$38+$C$38,12+(A46-$B$38)/MAX(1,$C$38/12),IF(A46&lt;=$B$38+$C$38+$D$38,24+(A46-$B$38-$C$38)/MAX(1,$D$38/12),IF(A46&lt;=$B$38+$C$38+$D$38+$E$38,36+(A46-$B$38-$C$38-$D$38)/MAX(1,$E$38/12),IF(A46&lt;=$B$38+$C$38+$D$38+$E$38+$F$38,48+(A46-$B$38-$C$38-$D$38-$E$38)/MAX(1,$F$38/12),60))))))</f>
-        <v>32.15591666484711</v>
+        <f>MIN(60,IF(A46&lt;=$B$42,A46/MAX(1,$B$42/12),IF(A46&lt;=$B$42+$C$42,12+(A46-$B$42)/MAX(1,$C$42/12),IF(A46&lt;=$B$42+$C$42+$D$42,24+(A46-$B$42-$C$42)/MAX(1,$D$42/12),IF(A46&lt;=$B$42+$C$42+$D$42+$E$42,36+(A46-$B$42-$C$42-$D$42)/MAX(1,$E$42/12),IF(A46&lt;=$B$42+$C$42+$D$42+$E$42+$F$42,48+(A46-$B$42-$C$42-$D$42-$E$42)/MAX(1,$F$42/12),60))))))</f>
+        <v>9.37529941688663</v>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
@@ -12313,11 +12359,11 @@
     </row>
     <row r="47">
       <c r="A47" s="12" t="n">
-        <v>800000</v>
+        <v>250000</v>
       </c>
       <c r="B47" s="43">
-        <f>MIN(60,IF(A47&lt;=$B$38,A47/MAX(1,$B$38/12),IF(A47&lt;=$B$38+$C$38,12+(A47-$B$38)/MAX(1,$C$38/12),IF(A47&lt;=$B$38+$C$38+$D$38,24+(A47-$B$38-$C$38)/MAX(1,$D$38/12),IF(A47&lt;=$B$38+$C$38+$D$38+$E$38,36+(A47-$B$38-$C$38-$D$38)/MAX(1,$E$38/12),IF(A47&lt;=$B$38+$C$38+$D$38+$E$38+$F$38,48+(A47-$B$38-$C$38-$D$38-$E$38)/MAX(1,$F$38/12),60))))))</f>
-        <v>37.37881702716862</v>
+        <f>MIN(60,IF(A47&lt;=$B$42,A47/MAX(1,$B$42/12),IF(A47&lt;=$B$42+$C$42,12+(A47-$B$42)/MAX(1,$C$42/12),IF(A47&lt;=$B$42+$C$42+$D$42,24+(A47-$B$42-$C$42)/MAX(1,$D$42/12),IF(A47&lt;=$B$42+$C$42+$D$42+$E$42,36+(A47-$B$42-$C$42-$D$42)/MAX(1,$E$42/12),IF(A47&lt;=$B$42+$C$42+$D$42+$E$42+$F$42,48+(A47-$B$42-$C$42-$D$42-$E$42)/MAX(1,$F$42/12),60))))))</f>
+        <v>14.427762253444723</v>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
@@ -12331,9 +12377,18 @@
       <c r="H47" s="7" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="7" t="n"/>
-      <c r="B48" s="7" t="n"/>
-      <c r="C48" s="7" t="n"/>
+      <c r="A48" s="12" t="n">
+        <v>350000</v>
+      </c>
+      <c r="B48" s="43">
+        <f>MIN(60,IF(A48&lt;=$B$42,A48/MAX(1,$B$42/12),IF(A48&lt;=$B$42+$C$42,12+(A48-$B$42)/MAX(1,$C$42/12),IF(A48&lt;=$B$42+$C$42+$D$42,24+(A48-$B$42-$C$42)/MAX(1,$D$42/12),IF(A48&lt;=$B$42+$C$42+$D$42+$E$42,36+(A48-$B$42-$C$42-$D$42)/MAX(1,$E$42/12),IF(A48&lt;=$B$42+$C$42+$D$42+$E$42+$F$42,48+(A48-$B$42-$C$42-$D$42-$E$42)/MAX(1,$F$42/12),60))))))</f>
+        <v>18.613116759103733</v>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>60 = the raise outlasts the five-year model</t>
+        </is>
+      </c>
       <c r="D48" s="7" t="n"/>
       <c r="E48" s="7" t="n"/>
       <c r="F48" s="7" t="n"/>
@@ -12341,18 +12396,85 @@
       <c r="H48" s="7" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="8" t="inlineStr">
-        <is>
-          <t>Read: the window budget is what the raise has to cover; the cushion should be positive after the first hire. Runway assumes the scenario's spend from month one; a lean first year stretches it.</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="n"/>
-      <c r="C49" s="7" t="n"/>
+      <c r="A49" s="12" t="n">
+        <v>500000</v>
+      </c>
+      <c r="B49" s="43">
+        <f>MIN(60,IF(A49&lt;=$B$42,A49/MAX(1,$B$42/12),IF(A49&lt;=$B$42+$C$42,12+(A49-$B$42)/MAX(1,$C$42/12),IF(A49&lt;=$B$42+$C$42+$D$42,24+(A49-$B$42-$C$42)/MAX(1,$D$42/12),IF(A49&lt;=$B$42+$C$42+$D$42+$E$42,36+(A49-$B$42-$C$42-$D$42)/MAX(1,$E$42/12),IF(A49&lt;=$B$42+$C$42+$D$42+$E$42+$F$42,48+(A49-$B$42-$C$42-$D$42-$E$42)/MAX(1,$F$42/12),60))))))</f>
+        <v>24.737653951642894</v>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>60 = the raise outlasts the five-year model</t>
+        </is>
+      </c>
       <c r="D49" s="7" t="n"/>
       <c r="E49" s="7" t="n"/>
       <c r="F49" s="7" t="n"/>
       <c r="G49" s="7" t="n"/>
       <c r="H49" s="7" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="12" t="n">
+        <v>650000</v>
+      </c>
+      <c r="B50" s="43">
+        <f>MIN(60,IF(A50&lt;=$B$42,A50/MAX(1,$B$42/12),IF(A50&lt;=$B$42+$C$42,12+(A50-$B$42)/MAX(1,$C$42/12),IF(A50&lt;=$B$42+$C$42+$D$42,24+(A50-$B$42-$C$42)/MAX(1,$D$42/12),IF(A50&lt;=$B$42+$C$42+$D$42+$E$42,36+(A50-$B$42-$C$42-$D$42)/MAX(1,$E$42/12),IF(A50&lt;=$B$42+$C$42+$D$42+$E$42+$F$42,48+(A50-$B$42-$C$42-$D$42-$E$42)/MAX(1,$F$42/12),60))))))</f>
+        <v>29.934335361943575</v>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>60 = the raise outlasts the five-year model</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="n"/>
+      <c r="E50" s="7" t="n"/>
+      <c r="F50" s="7" t="n"/>
+      <c r="G50" s="7" t="n"/>
+      <c r="H50" s="7" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="12" t="n">
+        <v>800000</v>
+      </c>
+      <c r="B51" s="43">
+        <f>MIN(60,IF(A51&lt;=$B$42,A51/MAX(1,$B$42/12),IF(A51&lt;=$B$42+$C$42,12+(A51-$B$42)/MAX(1,$C$42/12),IF(A51&lt;=$B$42+$C$42+$D$42,24+(A51-$B$42-$C$42)/MAX(1,$D$42/12),IF(A51&lt;=$B$42+$C$42+$D$42+$E$42,36+(A51-$B$42-$C$42-$D$42)/MAX(1,$E$42/12),IF(A51&lt;=$B$42+$C$42+$D$42+$E$42+$F$42,48+(A51-$B$42-$C$42-$D$42-$E$42)/MAX(1,$F$42/12),60))))))</f>
+        <v>35.13101677224425</v>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>60 = the raise outlasts the five-year model</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="n"/>
+      <c r="E51" s="7" t="n"/>
+      <c r="F51" s="7" t="n"/>
+      <c r="G51" s="7" t="n"/>
+      <c r="H51" s="7" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="n"/>
+      <c r="B52" s="7" t="n"/>
+      <c r="C52" s="7" t="n"/>
+      <c r="D52" s="7" t="n"/>
+      <c r="E52" s="7" t="n"/>
+      <c r="F52" s="7" t="n"/>
+      <c r="G52" s="7" t="n"/>
+      <c r="H52" s="7" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>Read: the window budget is what the raise has to cover; the cushion should be positive after the first hire. Runway assumes the scenario's spend from month one; a lean first year stretches it.</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="n"/>
+      <c r="C53" s="7" t="n"/>
+      <c r="D53" s="7" t="n"/>
+      <c r="E53" s="7" t="n"/>
+      <c r="F53" s="7" t="n"/>
+      <c r="G53" s="7" t="n"/>
+      <c r="H53" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12509,31 +12631,31 @@
       <c r="A9" s="18" t="n">
         <v>1000</v>
       </c>
-      <c r="B9" s="41">
+      <c r="B9" s="39">
         <f>$A9*B$8</f>
         <v>20000</v>
       </c>
-      <c r="C9" s="41">
+      <c r="C9" s="39">
         <f>$A9*C$8</f>
         <v>40000</v>
       </c>
-      <c r="D9" s="41">
+      <c r="D9" s="39">
         <f>$A9*D$8</f>
         <v>60000</v>
       </c>
-      <c r="E9" s="41">
+      <c r="E9" s="39">
         <f>$A9*E$8</f>
         <v>90000</v>
       </c>
-      <c r="F9" s="41">
+      <c r="F9" s="39">
         <f>$A9*F$8</f>
         <v>120000</v>
       </c>
-      <c r="G9" s="41">
+      <c r="G9" s="39">
         <f>$A9*G$8</f>
         <v>160000</v>
       </c>
-      <c r="H9" s="41">
+      <c r="H9" s="39">
         <f>$A9*H$8</f>
         <v>200000</v>
       </c>
@@ -12542,31 +12664,31 @@
       <c r="A10" s="18" t="n">
         <v>2500</v>
       </c>
-      <c r="B10" s="41">
+      <c r="B10" s="39">
         <f>$A10*B$8</f>
         <v>50000</v>
       </c>
-      <c r="C10" s="41">
+      <c r="C10" s="39">
         <f>$A10*C$8</f>
         <v>100000</v>
       </c>
-      <c r="D10" s="41">
+      <c r="D10" s="39">
         <f>$A10*D$8</f>
         <v>150000</v>
       </c>
-      <c r="E10" s="41">
+      <c r="E10" s="39">
         <f>$A10*E$8</f>
         <v>225000</v>
       </c>
-      <c r="F10" s="41">
+      <c r="F10" s="39">
         <f>$A10*F$8</f>
         <v>300000</v>
       </c>
-      <c r="G10" s="41">
+      <c r="G10" s="39">
         <f>$A10*G$8</f>
         <v>400000</v>
       </c>
-      <c r="H10" s="41">
+      <c r="H10" s="39">
         <f>$A10*H$8</f>
         <v>500000</v>
       </c>
@@ -12575,31 +12697,31 @@
       <c r="A11" s="18" t="n">
         <v>5000</v>
       </c>
-      <c r="B11" s="41">
+      <c r="B11" s="39">
         <f>$A11*B$8</f>
         <v>100000</v>
       </c>
-      <c r="C11" s="41">
+      <c r="C11" s="39">
         <f>$A11*C$8</f>
         <v>200000</v>
       </c>
-      <c r="D11" s="41">
+      <c r="D11" s="39">
         <f>$A11*D$8</f>
         <v>300000</v>
       </c>
-      <c r="E11" s="41">
+      <c r="E11" s="39">
         <f>$A11*E$8</f>
         <v>450000</v>
       </c>
-      <c r="F11" s="41">
+      <c r="F11" s="39">
         <f>$A11*F$8</f>
         <v>600000</v>
       </c>
-      <c r="G11" s="41">
+      <c r="G11" s="39">
         <f>$A11*G$8</f>
         <v>800000</v>
       </c>
-      <c r="H11" s="41">
+      <c r="H11" s="39">
         <f>$A11*H$8</f>
         <v>1000000</v>
       </c>
@@ -12608,31 +12730,31 @@
       <c r="A12" s="18" t="n">
         <v>10000</v>
       </c>
-      <c r="B12" s="41">
+      <c r="B12" s="39">
         <f>$A12*B$8</f>
         <v>200000</v>
       </c>
-      <c r="C12" s="41">
+      <c r="C12" s="39">
         <f>$A12*C$8</f>
         <v>400000</v>
       </c>
-      <c r="D12" s="41">
+      <c r="D12" s="39">
         <f>$A12*D$8</f>
         <v>600000</v>
       </c>
-      <c r="E12" s="41">
+      <c r="E12" s="39">
         <f>$A12*E$8</f>
         <v>900000</v>
       </c>
-      <c r="F12" s="41">
+      <c r="F12" s="39">
         <f>$A12*F$8</f>
         <v>1200000</v>
       </c>
-      <c r="G12" s="41">
+      <c r="G12" s="39">
         <f>$A12*G$8</f>
         <v>1600000</v>
       </c>
-      <c r="H12" s="41">
+      <c r="H12" s="39">
         <f>$A12*H$8</f>
         <v>2000000</v>
       </c>
@@ -12641,31 +12763,31 @@
       <c r="A13" s="18" t="n">
         <v>20000</v>
       </c>
-      <c r="B13" s="41">
+      <c r="B13" s="39">
         <f>$A13*B$8</f>
         <v>400000</v>
       </c>
-      <c r="C13" s="41">
+      <c r="C13" s="39">
         <f>$A13*C$8</f>
         <v>800000</v>
       </c>
-      <c r="D13" s="41">
+      <c r="D13" s="39">
         <f>$A13*D$8</f>
         <v>1200000</v>
       </c>
-      <c r="E13" s="41">
+      <c r="E13" s="39">
         <f>$A13*E$8</f>
         <v>1800000</v>
       </c>
-      <c r="F13" s="41">
+      <c r="F13" s="39">
         <f>$A13*F$8</f>
         <v>2400000</v>
       </c>
-      <c r="G13" s="41">
+      <c r="G13" s="39">
         <f>$A13*G$8</f>
         <v>3200000</v>
       </c>
-      <c r="H13" s="41">
+      <c r="H13" s="39">
         <f>$A13*H$8</f>
         <v>4000000</v>
       </c>
@@ -12674,31 +12796,31 @@
       <c r="A14" s="18" t="n">
         <v>40000</v>
       </c>
-      <c r="B14" s="41">
+      <c r="B14" s="39">
         <f>$A14*B$8</f>
         <v>800000</v>
       </c>
-      <c r="C14" s="41">
+      <c r="C14" s="39">
         <f>$A14*C$8</f>
         <v>1600000</v>
       </c>
-      <c r="D14" s="41">
+      <c r="D14" s="39">
         <f>$A14*D$8</f>
         <v>2400000</v>
       </c>
-      <c r="E14" s="41">
+      <c r="E14" s="39">
         <f>$A14*E$8</f>
         <v>3600000</v>
       </c>
-      <c r="F14" s="41">
+      <c r="F14" s="39">
         <f>$A14*F$8</f>
         <v>4800000</v>
       </c>
-      <c r="G14" s="41">
+      <c r="G14" s="39">
         <f>$A14*G$8</f>
         <v>6400000</v>
       </c>
-      <c r="H14" s="41">
+      <c r="H14" s="39">
         <f>$A14*H$8</f>
         <v>8000000</v>
       </c>

--- a/docs/financial-model-5yr-v2.xlsx
+++ b/docs/financial-model-5yr-v2.xlsx
@@ -4973,7 +4973,7 @@
       </c>
       <c r="H188" s="8" t="inlineStr">
         <is>
-          <t>Nov 6: ~$12k (UNVERIFIED range $11–14k)</t>
+          <t>Launch events after the close; Nov 6 (~$12k) itself is paid from current cash and sponsorships, before the round</t>
         </is>
       </c>
     </row>

--- a/docs/financial-model-5yr-v2.xlsx
+++ b/docs/financial-model-5yr-v2.xlsx
@@ -634,7 +634,7 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>4. Results (cost side rebuilt 2026-09-30: budget by function, founders full time before any employee, founder pay starting when there is money for it and ramping, payroll load applied). Revenue is unchanged: Base $36k / $133k / $385k / $810k / $1.47M. The Base and Fundable cost, EBITDA and cash figures are on the Combined sheet; the README of the docs folder and docs/funding/cfo-memo-ask-and-spend.md carry the discussion.</t>
+          <t>4. Results (2026-09-30: franchise metros as explicit drivers, a Base team of four, founder pay inside the functions). Base revenue $36k / $146k / $461k / $1.06M / $2.11M; EBITDA -$192k / -$313k / -$318k / -$3k / +$672k, so breakeven in year four and about $826k of cumulative capital at the low point. Fundable revenue $80k / $363k / $1.38M / $3.89M / $9.29M with 40 metros and a team of 18, EBITDA positive in year four. Conservative: $17k growing to $313k with 5 metros, not profitable in five years. Costs, EBITDA and cash are on the Combined sheet; docs/funding/cfo-memo-ask-and-spend.md carries the discussion.</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>4c. Founder targets (2026-09-30): at least 3,000 paying INDIVIDUALS by year three, and 5,000-10,000 members once organizations buy seats for their stakeholders. Base meets both (about 3,200 individuals and 5,700 members in Y3); Conservative does not (about 950 individuals). Organization-bought seats are about 20% of Y3 revenue. Neither target is sourced yet.</t>
+          <t>4c. Founder targets (2026-09-30): at least 3,000 paying INDIVIDUALS by year three, and 5,000-10,000 members once organizations buy seats for their stakeholders. Base meets both (about 5,100 individuals and 7,600 members in Y3, with 6 franchise metros live); Conservative does not (about 1,250 individuals and 1,570 members). Organization-bought seats are about 17% of Y3 Base revenue. Neither target is sourced yet.</t>
         </is>
       </c>
     </row>
@@ -660,12 +660,16 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr"/>
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>4d. Franchise metros (Exchange sheet, rows 16 to 19; every number is a variable): new metros launched per year (cumulative by Y5: Conservative 5, Base 20, Fundable 40), cost to launch a metro ($8k / $12k / $20k, one time), cost to support an active metro ($4k / $6k / $10k a year) and partner communities per active metro (Base: 2 in the launch year rising to 6). A metro costs relationships and some marketing, not staff.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>VALUES: this file was built with openpyxl and its formulas were evaluated with a Python formula engine (pycel; 1,009 formulas, 0 errors in every scenario) because LibreOffice is not available in the build sandbox. Excel and Google Sheets recalculate every formula on open, so what you see is live.</t>
+          <t>VALUES: this file was built with openpyxl and its formulas were evaluated with a Python formula engine (pycel; 1,138 formulas, 0 errors in every scenario) because LibreOffice is not available in the build sandbox. Excel and Google Sheets recalculate every formula on open, so what you see is live.</t>
         </is>
       </c>
     </row>

--- a/docs/financial-model-5yr-v2.xlsx
+++ b/docs/financial-model-5yr-v2.xlsx
@@ -634,7 +634,7 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>4. Results (2026-09-30: franchise metros as explicit drivers, a Base team of four, founder pay inside the functions). Base revenue $36k / $146k / $461k / $1.06M / $2.11M; EBITDA -$192k / -$313k / -$318k / -$3k / +$672k, so breakeven in year four and about $826k of cumulative capital at the low point. Fundable revenue $80k / $363k / $1.38M / $3.89M / $9.29M with 40 metros and a team of 18, EBITDA positive in year four. Conservative: $17k growing to $313k with 5 metros, not profitable in five years. Costs, EBITDA and cash are on the Combined sheet; docs/funding/cfo-memo-ask-and-spend.md carries the discussion.</t>
+          <t>4. Results (2026-10-01: metros as explicit drivers, a Base team of four, founder pay inside the functions). Base revenue $36k / $172k / $499k / $1.11M / $2.11M; EBITDA -$192k / -$365k / -$294k / +$30k / +$696k, so breakeven in year four and about $851k of cumulative capital at the low point, in year three. Fundable revenue $80k / $363k / $1.38M / $3.89M / $9.29M with 40 metros and a team of 18, EBITDA positive in year four. Conservative: $17k growing to $313k with 5 metros, not profitable in five years. Costs, EBITDA and cash are on the Combined sheet; docs/funding/cfo-memo-ask-and-spend.md carries the discussion.</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>4c. Founder targets (2026-09-30): at least 3,000 paying INDIVIDUALS by year three, and 5,000-10,000 members once organizations buy seats for their stakeholders. Base meets both (about 5,100 individuals and 7,600 members in Y3, with 6 franchise metros live); Conservative does not (about 1,250 individuals and 1,570 members). Organization-bought seats are about 17% of Y3 Base revenue. Neither target is sourced yet.</t>
+          <t>4c. Founder targets (2026-09-30): at least 3,000 paying INDIVIDUALS by year three, and 5,000-10,000 members once organizations buy seats for their stakeholders. Base meets both (about 6,100 individuals and 8,600 members in Y3, with 9 metros live); Conservative does not (about 1,250 individuals and 1,570 members). Organization-bought seats are about 15% of Y3 Base revenue. Neither target is sourced yet.</t>
         </is>
       </c>
     </row>
@@ -662,7 +662,7 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>4d. Franchise metros (Exchange sheet, rows 16 to 19; every number is a variable): new metros launched per year (cumulative by Y5: Conservative 5, Base 20, Fundable 40), cost to launch a metro ($8k / $12k / $20k, one time), cost to support an active metro ($4k / $6k / $10k a year) and partner communities per active metro (Base: 2 in the launch year rising to 6). A metro costs relationships and some marketing, not staff.</t>
+          <t>4d. Metros (Exchange sheet, rows 16 to 19; every number is a variable): new metros launched per year (Base 0 / 6 / 3 / 5 / 6: three by month 18, six by the end of year two, nine by the end of year three, ten cities with San Diego; cumulative by Y5 Conservative 5, Base 20, Fundable 40), cost to launch a metro ($8k / $12k / $20k, one time), cost to support an active metro ($4k / $6k / $10k a year) and partner communities per active metro (Base: 2 in the launch year rising to 6). A metro costs relationships and some marketing, not staff.</t>
         </is>
       </c>
     </row>
@@ -3627,7 +3627,7 @@
       </c>
       <c r="H130" s="8" t="inlineStr">
         <is>
-          <t>A metro is a cluster of communities led by their own people on our infrastructure (Nashville, Las Vegas, Los Angeles, Austin, Atlanta, Dallas-Fort Worth, Phoenix, Denver, Seattle first). Cumulative by Y5: Conservative 5, Base 20, Fundable 40</t>
+          <t>A metro is a cluster of communities led by their own people on our infrastructure (Nashville, Las Vegas, Los Angeles, Austin, Atlanta, Dallas-Fort Worth, Phoenix, Denver, Seattle first). Cumulative by Y5: Conservative 5, Base 20, Fundable 40. Base: 3 launched by month 18, 6 by the end of year two, 9 by the end of year three (San Diego plus nine metros is ten cities)</t>
         </is>
       </c>
     </row>
@@ -3642,16 +3642,16 @@
         <v>0</v>
       </c>
       <c r="D131" s="18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E131" s="18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F131" s="18" t="n">
+        <v>5</v>
+      </c>
+      <c r="G131" s="18" t="n">
         <v>6</v>
-      </c>
-      <c r="G131" s="18" t="n">
-        <v>8</v>
       </c>
       <c r="H131" s="7" t="n"/>
     </row>
@@ -3692,19 +3692,19 @@
       </c>
       <c r="D133" s="19">
         <f>CHOOSE(Inputs!$B$29,D130,D131,D132)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E133" s="19">
         <f>CHOOSE(Inputs!$B$29,E130,E131,E132)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F133" s="19">
         <f>CHOOSE(Inputs!$B$29,F130,F131,F132)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G133" s="19">
         <f>CHOOSE(Inputs!$B$29,G130,G131,G132)</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H133" s="7" t="n"/>
     </row>
@@ -8532,19 +8532,19 @@
       </c>
       <c r="C16" s="24">
         <f>Inputs!$D$133</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D16" s="24">
         <f>Inputs!$E$133</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E16" s="24">
         <f>Inputs!$F$133</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F16" s="24">
         <f>Inputs!$G$133</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G16" s="7" t="n"/>
     </row>
@@ -8644,15 +8644,15 @@
       </c>
       <c r="C20" s="29">
         <f>B20+C16</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D20" s="29">
         <f>C20+D16</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E20" s="29">
         <f>D20+E16</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F20" s="29">
         <f>E20+F16</f>
@@ -8676,15 +8676,15 @@
       </c>
       <c r="C21" s="29">
         <f>C20*C19</f>
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="D21" s="29">
         <f>D20*D19</f>
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="E21" s="29">
         <f>E20*E19</f>
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F21" s="29">
         <f>F20*F19</f>
@@ -8708,15 +8708,15 @@
       </c>
       <c r="C22" s="31">
         <f>C6+C21</f>
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D22" s="31">
         <f>D6+D21</f>
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="E22" s="31">
         <f>E6+E21</f>
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="F22" s="31">
         <f>F6+F21</f>
@@ -8736,15 +8736,15 @@
       </c>
       <c r="C23" s="29">
         <f>C22*C7</f>
-        <v>1080</v>
+        <v>1800</v>
       </c>
       <c r="D23" s="29">
         <f>D22*D7</f>
-        <v>4320</v>
+        <v>5280</v>
       </c>
       <c r="E23" s="29">
         <f>E22*E7</f>
-        <v>12000</v>
+        <v>13000</v>
       </c>
       <c r="F23" s="29">
         <f>F22*F7</f>
@@ -8790,15 +8790,15 @@
       </c>
       <c r="C26" s="27">
         <f>C23*12*Inputs!$B$5*(1-Inputs!$B$7*(1-Inputs!$B$21))</f>
-        <v>120958.27200000001</v>
+        <v>201597.12</v>
       </c>
       <c r="D26" s="27">
         <f>D23*12*Inputs!$B$5*(1-Inputs!$B$7*(1-Inputs!$B$21))</f>
-        <v>483833.08800000005</v>
+        <v>591351.552</v>
       </c>
       <c r="E26" s="27">
         <f>E23*12*Inputs!$B$5*(1-Inputs!$B$7*(1-Inputs!$B$21))</f>
-        <v>1343980.8</v>
+        <v>1455979.2</v>
       </c>
       <c r="F26" s="27">
         <f>F23*12*Inputs!$B$5*(1-Inputs!$B$7*(1-Inputs!$B$21))</f>
@@ -8850,15 +8850,15 @@
       </c>
       <c r="C28" s="27">
         <f>(C23+C8)*C10</f>
-        <v>110400</v>
+        <v>168000</v>
       </c>
       <c r="D28" s="27">
         <f>(D23+D8)*D10</f>
-        <v>632000</v>
+        <v>728000</v>
       </c>
       <c r="E28" s="27">
         <f>(E23+E8)*E10</f>
-        <v>1860000</v>
+        <v>1980000</v>
       </c>
       <c r="F28" s="27">
         <f>(F23+F8)*F10</f>
@@ -8878,15 +8878,15 @@
       </c>
       <c r="C29" s="27">
         <f>C22*C9</f>
-        <v>144000</v>
+        <v>240000</v>
       </c>
       <c r="D29" s="27">
         <f>D22*D9</f>
-        <v>648000</v>
+        <v>792000</v>
       </c>
       <c r="E29" s="27">
         <f>E22*E9</f>
-        <v>1920000</v>
+        <v>2080000</v>
       </c>
       <c r="F29" s="27">
         <f>F22*F9</f>
@@ -8990,15 +8990,15 @@
       </c>
       <c r="C33" s="27">
         <f>C22*C11*Inputs!$B$15*12</f>
-        <v>3780</v>
+        <v>6300</v>
       </c>
       <c r="D33" s="27">
         <f>D22*D11*Inputs!$B$15*12</f>
-        <v>14580</v>
+        <v>17820</v>
       </c>
       <c r="E33" s="27">
         <f>E22*E11*Inputs!$B$15*12</f>
-        <v>36000</v>
+        <v>39000</v>
       </c>
       <c r="F33" s="27">
         <f>F22*F11*Inputs!$B$15*12</f>
@@ -9046,15 +9046,15 @@
       </c>
       <c r="C35" s="28">
         <f>SUM(C26:C34)</f>
-        <v>478098.272</v>
+        <v>714857.12</v>
       </c>
       <c r="D35" s="28">
         <f>SUM(D26:D34)</f>
-        <v>2185293.088</v>
+        <v>2536051.552</v>
       </c>
       <c r="E35" s="28">
         <f>SUM(E26:E34)</f>
-        <v>6012180.8</v>
+        <v>6407179.2</v>
       </c>
       <c r="F35" s="28">
         <f>SUM(F26:F34)</f>
@@ -9096,15 +9096,15 @@
       </c>
       <c r="C38" s="27">
         <f>(C26+C27)*Inputs!$B$10</f>
-        <v>15095.8272</v>
+        <v>23159.712</v>
       </c>
       <c r="D38" s="27">
         <f>(D26+D27)*Inputs!$B$10</f>
-        <v>68383.3088</v>
+        <v>79135.15520000001</v>
       </c>
       <c r="E38" s="27">
         <f>(E26+E27)*Inputs!$B$10</f>
-        <v>169398.08000000002</v>
+        <v>180597.92</v>
       </c>
       <c r="F38" s="27">
         <f>(F26+F27)*Inputs!$B$10</f>
@@ -9124,15 +9124,15 @@
       </c>
       <c r="C39" s="27">
         <f>C28*Inputs!$B$11</f>
-        <v>11040.0</v>
+        <v>16800.0</v>
       </c>
       <c r="D39" s="27">
         <f>D28*Inputs!$B$11</f>
-        <v>63200.0</v>
+        <v>72800.0</v>
       </c>
       <c r="E39" s="27">
         <f>E28*Inputs!$B$11</f>
-        <v>186000.0</v>
+        <v>198000.0</v>
       </c>
       <c r="F39" s="27">
         <f>F28*Inputs!$B$11</f>
@@ -9152,15 +9152,15 @@
       </c>
       <c r="C40" s="27">
         <f>C29*Inputs!$B$12</f>
-        <v>14400.0</v>
+        <v>24000.0</v>
       </c>
       <c r="D40" s="27">
         <f>D29*Inputs!$B$12</f>
-        <v>64800.0</v>
+        <v>79200.0</v>
       </c>
       <c r="E40" s="27">
         <f>E29*Inputs!$B$12</f>
-        <v>192000.0</v>
+        <v>208000.0</v>
       </c>
       <c r="F40" s="27">
         <f>F29*Inputs!$B$12</f>
@@ -9264,15 +9264,15 @@
       </c>
       <c r="C44" s="27">
         <f>C33</f>
-        <v>3780</v>
+        <v>6300</v>
       </c>
       <c r="D44" s="27">
         <f>D33</f>
-        <v>14580</v>
+        <v>17820</v>
       </c>
       <c r="E44" s="27">
         <f>E33</f>
-        <v>36000</v>
+        <v>39000</v>
       </c>
       <c r="F44" s="27">
         <f>F33</f>
@@ -9320,15 +9320,15 @@
       </c>
       <c r="C46" s="28">
         <f>SUM(C38:C45)</f>
-        <v>75275.8272</v>
+        <v>101219.712</v>
       </c>
       <c r="D46" s="28">
         <f>SUM(D38:D45)</f>
-        <v>303843.3088</v>
+        <v>341835.15520000004</v>
       </c>
       <c r="E46" s="28">
         <f>SUM(E38:E45)</f>
-        <v>800598.0800000001</v>
+        <v>842797.92</v>
       </c>
       <c r="F46" s="28">
         <f>SUM(F38:F45)</f>
@@ -9370,15 +9370,15 @@
       </c>
       <c r="C49" s="27">
         <f>(C26+C27)*(1-Inputs!$B$10)</f>
-        <v>135862.4448</v>
+        <v>208437.408</v>
       </c>
       <c r="D49" s="27">
         <f>(D26+D27)*(1-Inputs!$B$10)</f>
-        <v>615449.7792</v>
+        <v>712216.3968</v>
       </c>
       <c r="E49" s="27">
         <f>(E26+E27)*(1-Inputs!$B$10)</f>
-        <v>1524582.72</v>
+        <v>1625381.28</v>
       </c>
       <c r="F49" s="27">
         <f>(F26+F27)*(1-Inputs!$B$10)</f>
@@ -9398,15 +9398,15 @@
       </c>
       <c r="C50" s="27">
         <f>C28*(1-Inputs!$B$11)+C29*(1-Inputs!$B$12)</f>
-        <v>228960</v>
+        <v>367200</v>
       </c>
       <c r="D50" s="27">
         <f>D28*(1-Inputs!$B$11)+D29*(1-Inputs!$B$12)</f>
-        <v>1152000</v>
+        <v>1368000</v>
       </c>
       <c r="E50" s="27">
         <f>E28*(1-Inputs!$B$11)+E29*(1-Inputs!$B$12)</f>
-        <v>3402000</v>
+        <v>3654000</v>
       </c>
       <c r="F50" s="27">
         <f>F28*(1-Inputs!$B$11)+F29*(1-Inputs!$B$12)</f>
@@ -9476,15 +9476,15 @@
       </c>
       <c r="C54" s="27">
         <f>C26*Inputs!$B$21*(Inputs!$B$19+Inputs!$B$20/Inputs!$B$5)+C26*(1-Inputs!$B$21)*Inputs!$B$19</f>
-        <v>5685.038783999999</v>
+        <v>9475.06464</v>
       </c>
       <c r="D54" s="27">
         <f>D26*Inputs!$B$21*(Inputs!$B$19+Inputs!$B$20/Inputs!$B$5)+D26*(1-Inputs!$B$21)*Inputs!$B$19</f>
-        <v>22740.155135999998</v>
+        <v>27793.522944</v>
       </c>
       <c r="E54" s="27">
         <f>E26*Inputs!$B$21*(Inputs!$B$19+Inputs!$B$20/Inputs!$B$5)+E26*(1-Inputs!$B$21)*Inputs!$B$19</f>
-        <v>63167.0976</v>
+        <v>68431.02239999999</v>
       </c>
       <c r="F54" s="27">
         <f>F26*Inputs!$B$21*(Inputs!$B$19+Inputs!$B$20/Inputs!$B$5)+F26*(1-Inputs!$B$21)*Inputs!$B$19</f>
@@ -9504,15 +9504,15 @@
       </c>
       <c r="C55" s="27">
         <f>(C49+C50)*Inputs!$B$22</f>
-        <v>3648.224448</v>
+        <v>5756.3740800000005</v>
       </c>
       <c r="D55" s="27">
         <f>(D49+D50)*Inputs!$B$22</f>
-        <v>17674.497792000002</v>
+        <v>20802.163968</v>
       </c>
       <c r="E55" s="27">
         <f>(E49+E50)*Inputs!$B$22</f>
-        <v>49265.8272</v>
+        <v>52793.81280000001</v>
       </c>
       <c r="F55" s="27">
         <f>(F49+F50)*Inputs!$B$22</f>
@@ -9532,15 +9532,15 @@
       </c>
       <c r="C56" s="28">
         <f>C46-C54-C55</f>
-        <v>65942.563968</v>
+        <v>85988.27328000001</v>
       </c>
       <c r="D56" s="28">
         <f>D46-D54-D55</f>
-        <v>263428.655872</v>
+        <v>293239.46828800003</v>
       </c>
       <c r="E56" s="28">
         <f>E46-E54-E55</f>
-        <v>688165.1552000002</v>
+        <v>721573.0848000001</v>
       </c>
       <c r="F56" s="28">
         <f>F46-F54-F55</f>
@@ -9569,15 +9569,15 @@
       </c>
       <c r="C58" s="30">
         <f>IF((C23+C8)=0,0,C46/(C23+C8))</f>
-        <v>54.54770086956522</v>
+        <v>48.199862857142854</v>
       </c>
       <c r="D58" s="30">
         <f>IF((D23+D8)=0,0,D46/(D23+D8))</f>
-        <v>48.07647291139241</v>
+        <v>46.955378461538466</v>
       </c>
       <c r="E58" s="30">
         <f>IF((E23+E8)=0,0,E46/(E23+E8))</f>
-        <v>51.65148903225807</v>
+        <v>51.07866181818182</v>
       </c>
       <c r="F58" s="30">
         <f>IF((F23+F8)=0,0,F46/(F23+F8))</f>
@@ -9597,15 +9597,15 @@
       </c>
       <c r="C59" s="27">
         <f>IF(C6=0,0,C46/C6)</f>
-        <v>6272.9856</v>
+        <v>8434.976</v>
       </c>
       <c r="D59" s="27">
         <f>IF(D6=0,0,D46/D6)</f>
-        <v>10128.110293333333</v>
+        <v>11394.505173333335</v>
       </c>
       <c r="E59" s="27">
         <f>IF(E6=0,0,E46/E6)</f>
-        <v>13343.301333333335</v>
+        <v>14046.632000000001</v>
       </c>
       <c r="F59" s="27">
         <f>IF(F6=0,0,F46/F6)</f>
@@ -9732,15 +9732,15 @@
       </c>
       <c r="C6" s="26">
         <f>Garden!C27+Exchange!C38</f>
-        <v>50855.4592</v>
+        <v>58919.344</v>
       </c>
       <c r="D6" s="26">
         <f>Garden!D27+Exchange!D38</f>
-        <v>148262.5248</v>
+        <v>159014.3712</v>
       </c>
       <c r="E6" s="26">
         <f>Garden!E27+Exchange!E38</f>
-        <v>301756.83200000005</v>
+        <v>312956.672</v>
       </c>
       <c r="F6" s="26">
         <f>Garden!F27+Exchange!F38</f>
@@ -9760,15 +9760,15 @@
       </c>
       <c r="C7" s="26">
         <f>Garden!C28+Exchange!C39</f>
-        <v>17040</v>
+        <v>22800</v>
       </c>
       <c r="D7" s="26">
         <f>Garden!D28+Exchange!D39</f>
-        <v>79450</v>
+        <v>89050</v>
       </c>
       <c r="E7" s="26">
         <f>Garden!E28+Exchange!E39</f>
-        <v>217500</v>
+        <v>229500</v>
       </c>
       <c r="F7" s="26">
         <f>Garden!F28+Exchange!F39</f>
@@ -9788,15 +9788,15 @@
       </c>
       <c r="C8" s="26">
         <f>Garden!C29+Exchange!C40</f>
-        <v>19200</v>
+        <v>28800</v>
       </c>
       <c r="D8" s="26">
         <f>Garden!D29+Exchange!D40</f>
-        <v>77800</v>
+        <v>92200</v>
       </c>
       <c r="E8" s="26">
         <f>Garden!E29+Exchange!E40</f>
-        <v>217200</v>
+        <v>233200</v>
       </c>
       <c r="F8" s="26">
         <f>Garden!F29+Exchange!F40</f>
@@ -9900,15 +9900,15 @@
       </c>
       <c r="C12" s="26">
         <f>Exchange!C44</f>
-        <v>3780</v>
+        <v>6300</v>
       </c>
       <c r="D12" s="26">
         <f>Exchange!D44</f>
-        <v>14580</v>
+        <v>17820</v>
       </c>
       <c r="E12" s="26">
         <f>Exchange!E44</f>
-        <v>36000</v>
+        <v>39000</v>
       </c>
       <c r="F12" s="26">
         <f>Exchange!F44</f>
@@ -9956,15 +9956,15 @@
       </c>
       <c r="C14" s="28">
         <f>SUM(C6:C13)</f>
-        <v>146335.45919999998</v>
+        <v>172279.34399999998</v>
       </c>
       <c r="D14" s="28">
         <f>SUM(D6:D13)</f>
-        <v>461472.5248</v>
+        <v>499464.3712</v>
       </c>
       <c r="E14" s="28">
         <f>SUM(E6:E13)</f>
-        <v>1063406.832</v>
+        <v>1105606.672</v>
       </c>
       <c r="F14" s="28">
         <f>SUM(F6:F13)</f>
@@ -10012,15 +10012,15 @@
       </c>
       <c r="C16" s="26">
         <f>Exchange!C46</f>
-        <v>75275.8272</v>
+        <v>101219.712</v>
       </c>
       <c r="D16" s="26">
         <f>Exchange!D46</f>
-        <v>303843.3088</v>
+        <v>341835.15520000004</v>
       </c>
       <c r="E16" s="26">
         <f>Exchange!E46</f>
-        <v>800598.0800000001</v>
+        <v>842797.92</v>
       </c>
       <c r="F16" s="26">
         <f>Exchange!F46</f>
@@ -10040,15 +10040,15 @@
       </c>
       <c r="C17" s="32">
         <f>IF(C14=0,0,(C10+C12+C13)/C14)</f>
-        <v>0.17248040999757905</v>
+        <v>0.16113365279589179</v>
       </c>
       <c r="D17" s="32">
         <f>IF(D14=0,0,(D10+D12+D13)/D14)</f>
-        <v>0.16677049198834556</v>
+        <v>0.16057201399033447</v>
       </c>
       <c r="E17" s="32">
         <f>IF(E14=0,0,(E10+E12+E13)/E14)</f>
-        <v>0.17815383002918306</v>
+        <v>0.17406732871091066</v>
       </c>
       <c r="F17" s="32">
         <f>IF(F14=0,0,(F10+F12+F13)/F14)</f>
@@ -10090,15 +10090,15 @@
       </c>
       <c r="C20" s="26">
         <f>Garden!C24+Exchange!C35</f>
-        <v>767617.536</v>
+        <v>1004376.384</v>
       </c>
       <c r="D20" s="26">
         <f>Garden!D24+Exchange!D35</f>
-        <v>2847551.52</v>
+        <v>3198309.984</v>
       </c>
       <c r="E20" s="26">
         <f>Garden!E24+Exchange!E35</f>
-        <v>7178898.304</v>
+        <v>7573896.704</v>
       </c>
       <c r="F20" s="26">
         <f>Garden!F24+Exchange!F35</f>
@@ -10118,15 +10118,15 @@
       </c>
       <c r="C21" s="24">
         <f>Garden!C6+Garden!C7+Exchange!C23+Exchange!C8</f>
-        <v>1980</v>
+        <v>2700</v>
       </c>
       <c r="D21" s="24">
         <f>Garden!D6+Garden!D7+Exchange!D23+Exchange!D8</f>
-        <v>7620</v>
+        <v>8580</v>
       </c>
       <c r="E21" s="24">
         <f>Garden!E6+Garden!E7+Exchange!E23+Exchange!E8</f>
-        <v>17600</v>
+        <v>18600</v>
       </c>
       <c r="F21" s="24">
         <f>Garden!F6+Garden!F7+Exchange!F23+Exchange!F8</f>
@@ -10146,15 +10146,15 @@
       </c>
       <c r="C22" s="24">
         <f>Garden!C6+Exchange!C23</f>
-        <v>1480</v>
+        <v>2200</v>
       </c>
       <c r="D22" s="24">
         <f>Garden!D6+Exchange!D23</f>
-        <v>5120</v>
+        <v>6080</v>
       </c>
       <c r="E22" s="24">
         <f>Garden!E6+Exchange!E23</f>
-        <v>13200</v>
+        <v>14200</v>
       </c>
       <c r="F22" s="24">
         <f>Garden!F6+Exchange!F23</f>
@@ -10238,15 +10238,15 @@
       </c>
       <c r="C25" s="32">
         <f>IF(C14=0,0,C24/C14)</f>
-        <v>0.12983866045776554</v>
+        <v>0.11028600155338415</v>
       </c>
       <c r="D25" s="32">
         <f>IF(D14=0,0,D24/D14)</f>
-        <v>0.1652319388527982</v>
+        <v>0.15266354197958856</v>
       </c>
       <c r="E25" s="32">
         <f>IF(E14=0,0,E24/E14)</f>
-        <v>0.1375766974572155</v>
+        <v>0.13232554009044548</v>
       </c>
       <c r="F25" s="32">
         <f>IF(F14=0,0,F24/F14)</f>
@@ -10266,15 +10266,15 @@
       </c>
       <c r="C26" s="24">
         <f>1+Exchange!C22</f>
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="D26" s="24">
         <f>1+Exchange!D22</f>
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="E26" s="24">
         <f>1+Exchange!E22</f>
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="F26" s="24">
         <f>1+Exchange!F22</f>
@@ -10294,15 +10294,15 @@
       </c>
       <c r="C27" s="24">
         <f>Exchange!C20</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D27" s="24">
         <f>Exchange!D20</f>
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E27" s="24">
         <f>Exchange!E20</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F27" s="24">
         <f>Exchange!F20</f>
@@ -10322,15 +10322,15 @@
       </c>
       <c r="C28" s="26">
         <f>Garden!C19*(1-Inputs!$B$11)+Garden!C20*(1-Inputs!$B$12)+Garden!C38+Exchange!C50+Exchange!C51</f>
-        <v>433919.632</v>
+        <v>572159.632</v>
       </c>
       <c r="D28" s="26">
         <f>Garden!D19*(1-Inputs!$B$11)+Garden!D20*(1-Inputs!$B$12)+Garden!D38+Exchange!D50+Exchange!D51</f>
-        <v>1657129.216</v>
+        <v>1873129.216</v>
       </c>
       <c r="E28" s="26">
         <f>Garden!E19*(1-Inputs!$B$11)+Garden!E20*(1-Inputs!$B$12)+Garden!E38+Exchange!E50+Exchange!E51</f>
-        <v>4359658.752</v>
+        <v>4611658.752</v>
       </c>
       <c r="F28" s="26">
         <f>Garden!F19*(1-Inputs!$B$11)+Garden!F20*(1-Inputs!$B$12)+Garden!F38+Exchange!F50+Exchange!F51</f>
@@ -10354,15 +10354,15 @@
       </c>
       <c r="C29" s="30">
         <f>IF(C21=0,0,C14/C21)</f>
-        <v>73.90679757575757</v>
+        <v>63.80716444444444</v>
       </c>
       <c r="D29" s="30">
         <f>IF(D21=0,0,D14/D21)</f>
-        <v>60.56069879265092</v>
+        <v>58.212630675990674</v>
       </c>
       <c r="E29" s="30">
         <f>IF(E21=0,0,E14/E21)</f>
-        <v>60.42084272727272</v>
+        <v>59.44121892473118</v>
       </c>
       <c r="F29" s="30">
         <f>IF(F21=0,0,F14/F21)</f>
@@ -10382,15 +10382,15 @@
       </c>
       <c r="C30" s="32">
         <f>IF(C20=0,0,C14/C20)</f>
-        <v>0.19063589917779053</v>
+        <v>0.17152866867885255</v>
       </c>
       <c r="D30" s="32">
         <f>IF(D20=0,0,D14/D20)</f>
-        <v>0.16205941193998133</v>
+        <v>0.1561650914697579</v>
       </c>
       <c r="E30" s="32">
         <f>IF(E20=0,0,E14/E20)</f>
-        <v>0.14812953004327722</v>
+        <v>0.14597593751392152</v>
       </c>
       <c r="F30" s="32">
         <f>IF(F20=0,0,F14/F20)</f>
@@ -10740,11 +10740,11 @@
       </c>
       <c r="C44" s="26">
         <f>Exchange!C16*Exchange!C17+Exchange!C20*Exchange!C18</f>
-        <v>36000</v>
+        <v>108000</v>
       </c>
       <c r="D44" s="26">
         <f>Exchange!D16*Exchange!D17+Exchange!D20*Exchange!D18</f>
-        <v>84000</v>
+        <v>90000</v>
       </c>
       <c r="E44" s="26">
         <f>Exchange!E16*Exchange!E17+Exchange!E20*Exchange!E18</f>
@@ -10752,7 +10752,7 @@
       </c>
       <c r="F44" s="26">
         <f>Exchange!F16*Exchange!F17+Exchange!F20*Exchange!F18</f>
-        <v>216000</v>
+        <v>192000</v>
       </c>
       <c r="G44" s="7" t="n"/>
     </row>
@@ -10796,11 +10796,11 @@
       </c>
       <c r="C46" s="28">
         <f>SUM(C39:C45)</f>
-        <v>174975.0</v>
+        <v>246975.0</v>
       </c>
       <c r="D46" s="28">
         <f>SUM(D39:D45)</f>
-        <v>321450.0</v>
+        <v>327450.0</v>
       </c>
       <c r="E46" s="28">
         <f>SUM(E39:E45)</f>
@@ -10808,7 +10808,7 @@
       </c>
       <c r="F46" s="28">
         <f>SUM(F39:F45)</f>
-        <v>575000.0</v>
+        <v>551000.0</v>
       </c>
       <c r="G46" s="7" t="n"/>
     </row>
@@ -11244,15 +11244,15 @@
       </c>
       <c r="C62" s="26">
         <f>Garden!C43+Garden!C44+Exchange!C54+Exchange!C55</f>
-        <v>12726.66864</v>
+        <v>18624.844128</v>
       </c>
       <c r="D62" s="26">
         <f>Garden!D43+Garden!D44+Exchange!D54+Exchange!D55</f>
-        <v>48205.799232</v>
+        <v>56386.833216</v>
       </c>
       <c r="E62" s="26">
         <f>Garden!E43+Garden!E44+Exchange!E54+Exchange!E55</f>
-        <v>125747.647488</v>
+        <v>134539.55788799998</v>
       </c>
       <c r="F62" s="26">
         <f>Garden!F43+Garden!F44+Exchange!F54+Exchange!F55</f>
@@ -11272,15 +11272,15 @@
       </c>
       <c r="C63" s="28">
         <f>C62</f>
-        <v>12726.66864</v>
+        <v>18624.844128</v>
       </c>
       <c r="D63" s="28">
         <f>D62</f>
-        <v>48205.799232</v>
+        <v>56386.833216</v>
       </c>
       <c r="E63" s="28">
         <f>E62</f>
-        <v>125747.647488</v>
+        <v>134539.55788799998</v>
       </c>
       <c r="F63" s="28">
         <f>F62</f>
@@ -11309,19 +11309,19 @@
       </c>
       <c r="C65" s="28">
         <f>C38+C46+C49+C55+C61+C63</f>
-        <v>459026.66864</v>
+        <v>536924.844128</v>
       </c>
       <c r="D65" s="28">
         <f>D38+D46+D49+D55+D61+D63</f>
-        <v>779325.799232</v>
+        <v>793506.833216</v>
       </c>
       <c r="E65" s="28">
         <f>E38+E46+E49+E55+E61+E63</f>
-        <v>1066747.647488</v>
+        <v>1075539.557888</v>
       </c>
       <c r="F65" s="28">
         <f>F38+F46+F49+F55+F61+F63</f>
-        <v>1438856.398144</v>
+        <v>1414856.398144</v>
       </c>
       <c r="G65" s="7" t="n"/>
     </row>
@@ -11393,19 +11393,19 @@
       </c>
       <c r="C68" s="32">
         <f>IF(C65=0,0,C66/C65)</f>
-        <v>0.566198039800235</v>
+        <v>0.4840528480705602</v>
       </c>
       <c r="D68" s="32">
         <f>IF(D65=0,0,D66/D65)</f>
-        <v>0.529945242935622</v>
+        <v>0.5204744089299828</v>
       </c>
       <c r="E68" s="32">
         <f>IF(E65=0,0,E66/E65)</f>
-        <v>0.4387166928392636</v>
+        <v>0.43513043901332227</v>
       </c>
       <c r="F68" s="32">
         <f>IF(F65=0,0,F66/F65)</f>
-        <v>0.35027817970585273</v>
+        <v>0.3562198967055202</v>
       </c>
       <c r="G68" s="7" t="n"/>
     </row>
@@ -11443,19 +11443,19 @@
       </c>
       <c r="C71" s="28">
         <f>C14-C65</f>
-        <v>-312691.20944</v>
+        <v>-364645.500128</v>
       </c>
       <c r="D71" s="28">
         <f>D14-D65</f>
-        <v>-317853.274432</v>
+        <v>-294042.462016</v>
       </c>
       <c r="E71" s="28">
         <f>E14-E65</f>
-        <v>-3340.8154880001675</v>
+        <v>30067.11411199998</v>
       </c>
       <c r="F71" s="28">
         <f>F14-F65</f>
-        <v>671797.7138560002</v>
+        <v>695797.7138560002</v>
       </c>
       <c r="G71" s="7" t="n"/>
     </row>
@@ -11471,19 +11471,19 @@
       </c>
       <c r="C72" s="33">
         <f>B72+C71</f>
-        <v>-504685.077578</v>
+        <v>-556639.368266</v>
       </c>
       <c r="D72" s="33">
         <f>C72+D71</f>
-        <v>-822538.35201</v>
+        <v>-850681.8302819999</v>
       </c>
       <c r="E72" s="33">
         <f>D72+E71</f>
-        <v>-825879.1674980002</v>
+        <v>-820614.7161699999</v>
       </c>
       <c r="F72" s="33">
         <f>E72+F71</f>
-        <v>-154081.45364199998</v>
+        <v>-124817.00231399969</v>
       </c>
       <c r="G72" s="8" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
       </c>
       <c r="B73" s="28">
         <f>-MIN(0,MIN(B72:F72))</f>
-        <v>825879.1674980002</v>
+        <v>850681.8302819999</v>
       </c>
       <c r="C73" s="28" t="inlineStr"/>
       <c r="D73" s="28" t="inlineStr"/>
@@ -11551,15 +11551,15 @@
       </c>
       <c r="C75" s="27">
         <f>C14/C74</f>
-        <v>48778.486399999994</v>
+        <v>57426.448</v>
       </c>
       <c r="D75" s="27">
         <f>D14/D74</f>
-        <v>115368.1312</v>
+        <v>124866.0928</v>
       </c>
       <c r="E75" s="27">
         <f>E14/E74</f>
-        <v>265851.708</v>
+        <v>276401.668</v>
       </c>
       <c r="F75" s="27">
         <f>F14/F74</f>
@@ -11992,7 +11992,7 @@
       </c>
       <c r="B31" s="29">
         <f>Combined!D21</f>
-        <v>7620</v>
+        <v>8580</v>
       </c>
       <c r="C31" s="8" t="inlineStr"/>
     </row>
@@ -12004,7 +12004,7 @@
       </c>
       <c r="B32" s="32">
         <f>B31/B22</f>
-        <v>0.21598639455782312</v>
+        <v>0.24319727891156462</v>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
@@ -12306,7 +12306,7 @@
       </c>
       <c r="C11" s="39">
         <f>IF(B17=0,0,B11/B17)</f>
-        <v>0.3669765980900019</v>
+        <v>0.33819570008132177</v>
       </c>
       <c r="D11" s="26">
         <f>Combined!B38</f>
@@ -12338,11 +12338,11 @@
       </c>
       <c r="B12" s="26">
         <f>Combined!B46*$B$6+Combined!C46*$B$7</f>
-        <v>166047.5</v>
+        <v>202047.5</v>
       </c>
       <c r="C12" s="39">
         <f>IF(B17=0,0,B12/B17)</f>
-        <v>0.3628033679433761</v>
+        <v>0.4068386092444866</v>
       </c>
       <c r="D12" s="26">
         <f>Combined!B46</f>
@@ -12350,11 +12350,11 @@
       </c>
       <c r="E12" s="26">
         <f>Combined!C46</f>
-        <v>174975.0</v>
+        <v>246975.0</v>
       </c>
       <c r="F12" s="26">
         <f>Combined!D46</f>
-        <v>321450.0</v>
+        <v>327450.0</v>
       </c>
       <c r="G12" s="26">
         <f>Combined!E46</f>
@@ -12378,7 +12378,7 @@
       </c>
       <c r="C13" s="39">
         <f>IF(B17=0,0,B13/B17)</f>
-        <v>0.010924686247711531</v>
+        <v>0.010067895154468296</v>
       </c>
       <c r="D13" s="26">
         <f>Combined!B49</f>
@@ -12414,7 +12414,7 @@
       </c>
       <c r="C14" s="39">
         <f>IF(B17=0,0,B14/B17)</f>
-        <v>0.164929988281701</v>
+        <v>0.1519950131470079</v>
       </c>
       <c r="D14" s="26">
         <f>Combined!B55</f>
@@ -12450,7 +12450,7 @@
       </c>
       <c r="C15" s="39">
         <f>IF(B17=0,0,B15/B17)</f>
-        <v>0.07538033510920956</v>
+        <v>0.06946847656583124</v>
       </c>
       <c r="D15" s="26">
         <f>Combined!B61</f>
@@ -12482,11 +12482,11 @@
       </c>
       <c r="B16" s="26">
         <f>Combined!B63*$B$6+Combined!C63*$B$7</f>
-        <v>8689.047858</v>
+        <v>11638.135602</v>
       </c>
       <c r="C16" s="39">
         <f>IF(B17=0,0,B16/B17)</f>
-        <v>0.018985024327999988</v>
+        <v>0.023434305806884156</v>
       </c>
       <c r="D16" s="26">
         <f>Combined!B63</f>
@@ -12494,15 +12494,15 @@
       </c>
       <c r="E16" s="26">
         <f>Combined!C63</f>
-        <v>12726.66864</v>
+        <v>18624.844128</v>
       </c>
       <c r="F16" s="26">
         <f>Combined!D63</f>
-        <v>48205.799232</v>
+        <v>56386.833216</v>
       </c>
       <c r="G16" s="26">
         <f>Combined!E63</f>
-        <v>125747.647488</v>
+        <v>134539.55788799998</v>
       </c>
       <c r="H16" s="8" t="inlineStr">
         <is>
@@ -12518,7 +12518,7 @@
       </c>
       <c r="B17" s="33">
         <f>SUM(B11:B16)</f>
-        <v>457679.047858</v>
+        <v>496628.135602</v>
       </c>
       <c r="C17" s="7" t="n"/>
       <c r="D17" s="33">
@@ -12527,15 +12527,15 @@
       </c>
       <c r="E17" s="33">
         <f>SUM(E11:E16)</f>
-        <v>459026.66864</v>
+        <v>536924.844128</v>
       </c>
       <c r="F17" s="33">
         <f>SUM(F11:F16)</f>
-        <v>779325.799232</v>
+        <v>793506.833216</v>
       </c>
       <c r="G17" s="33">
         <f>SUM(G11:G16)</f>
-        <v>1066747.647488</v>
+        <v>1075539.557888</v>
       </c>
       <c r="H17" s="7" t="n"/>
     </row>
@@ -12551,7 +12551,7 @@
       </c>
       <c r="C18" s="39">
         <f>IF(B17=0,0,B18/B17)</f>
-        <v>0.44559610267165795</v>
+        <v>0.41064930756045287</v>
       </c>
       <c r="D18" s="26">
         <f>Combined!B67</f>
@@ -12670,7 +12670,7 @@
       </c>
       <c r="C22" s="39">
         <f>IF(B17=0,0,B22/B17)</f>
-        <v>0.5794235092061242</v>
+        <v>0.5339810232026895</v>
       </c>
       <c r="D22" s="26">
         <f>Combined!B66</f>
@@ -12708,7 +12708,7 @@
       </c>
       <c r="B24" s="26">
         <f>Combined!B14*$B$6+Combined!C14*$B$7</f>
-        <v>109339.575</v>
+        <v>122311.5174</v>
       </c>
       <c r="C24" s="7" t="n"/>
       <c r="D24" s="26">
@@ -12717,15 +12717,15 @@
       </c>
       <c r="E24" s="26">
         <f>Combined!C14</f>
-        <v>146335.45919999998</v>
+        <v>172279.34399999998</v>
       </c>
       <c r="F24" s="26">
         <f>Combined!D14</f>
-        <v>461472.5248</v>
+        <v>499464.3712</v>
       </c>
       <c r="G24" s="26">
         <f>Combined!E14</f>
-        <v>1063406.832</v>
+        <v>1105606.672</v>
       </c>
       <c r="H24" s="7" t="n"/>
     </row>
@@ -12737,7 +12737,7 @@
       </c>
       <c r="B25" s="33">
         <f>B17-B24</f>
-        <v>348339.47285799996</v>
+        <v>374316.618202</v>
       </c>
       <c r="C25" s="7" t="n"/>
       <c r="D25" s="7" t="n"/>
@@ -12754,11 +12754,11 @@
       </c>
       <c r="B26" s="33">
         <f>B4-B25</f>
-        <v>1660.5271420000354</v>
+        <v>-24316.618201999983</v>
       </c>
       <c r="C26" s="39">
         <f>IF(B25=0,0,B26/B25)</f>
-        <v>0.004766979545487647</v>
+        <v>-0.06496270007675031</v>
       </c>
       <c r="D26" s="7" t="n"/>
       <c r="E26" s="7" t="n"/>
@@ -13040,15 +13040,15 @@
       </c>
       <c r="E37" s="42">
         <f>IF(E36=0,0,Combined!C14/E36)</f>
-        <v>48778.486399999994</v>
+        <v>57426.448</v>
       </c>
       <c r="F37" s="42">
         <f>IF(F36=0,0,Combined!D14/F36)</f>
-        <v>115368.1312</v>
+        <v>124866.0928</v>
       </c>
       <c r="G37" s="42">
         <f>IF(G36=0,0,Combined!E14/G36)</f>
-        <v>265851.708</v>
+        <v>276401.668</v>
       </c>
       <c r="H37" s="42">
         <f>IF(H36=0,0,Combined!F14/H36)</f>
@@ -13121,15 +13121,15 @@
       </c>
       <c r="C41" s="26">
         <f>MAX(0,Combined!C65-Combined!C14)</f>
-        <v>312691.20944</v>
+        <v>364645.500128</v>
       </c>
       <c r="D41" s="26">
         <f>MAX(0,Combined!D65-Combined!D14)</f>
-        <v>317853.274432</v>
+        <v>294042.462016</v>
       </c>
       <c r="E41" s="26">
         <f>MAX(0,Combined!E65-Combined!E14)</f>
-        <v>3340.8154880001675</v>
+        <v>0</v>
       </c>
       <c r="F41" s="26">
         <f>MAX(0,Combined!F65-Combined!F14)</f>
@@ -13150,15 +13150,15 @@
       </c>
       <c r="C42" s="42">
         <f>C41/12</f>
-        <v>26057.600786666666</v>
+        <v>30387.125010666667</v>
       </c>
       <c r="D42" s="42">
         <f>D41/12</f>
-        <v>26487.772869333334</v>
+        <v>24503.538501333333</v>
       </c>
       <c r="E42" s="42">
         <f>E41/12</f>
-        <v>278.4012906666806</v>
+        <v>0.0</v>
       </c>
       <c r="F42" s="42">
         <f>F41/12</f>
@@ -13224,7 +13224,7 @@
       </c>
       <c r="B46" s="44">
         <f>MIN(60,IF(A46&lt;=$B$41,A46/MAX(1,$B$41/12),IF(A46&lt;=$B$41+$C$41,12+(A46-$B$41)/MAX(1,$C$41/12),IF(A46&lt;=$B$41+$C$41+$D$41,24+(A46-$B$41-$C$41)/MAX(1,$D$41/12),IF(A46&lt;=$B$41+$C$41+$D$41+$E$41,36+(A46-$B$41-$C$41-$D$41)/MAX(1,$E$41/12),IF(A46&lt;=$B$41+$C$41+$D$41+$E$41+$F$41,48+(A46-$B$41-$C$41-$D$41-$E$41)/MAX(1,$F$41/12),60))))))</f>
-        <v>14.226073395509266</v>
+        <v>13.90890490106051</v>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
       </c>
       <c r="B47" s="44">
         <f>MIN(60,IF(A47&lt;=$B$41,A47/MAX(1,$B$41/12),IF(A47&lt;=$B$41+$C$41,12+(A47-$B$41)/MAX(1,$C$41/12),IF(A47&lt;=$B$41+$C$41+$D$41,24+(A47-$B$41-$C$41)/MAX(1,$D$41/12),IF(A47&lt;=$B$41+$C$41+$D$41+$E$41,36+(A47-$B$41-$C$41-$D$41)/MAX(1,$E$41/12),IF(A47&lt;=$B$41+$C$41+$D$41+$E$41+$F$41,48+(A47-$B$41-$C$41-$D$41-$E$41)/MAX(1,$F$41/12),60))))))</f>
-        <v>18.063725250670416</v>
+        <v>17.199772331424434</v>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
       </c>
       <c r="B48" s="44">
         <f>MIN(60,IF(A48&lt;=$B$41,A48/MAX(1,$B$41/12),IF(A48&lt;=$B$41+$C$41,12+(A48-$B$41)/MAX(1,$C$41/12),IF(A48&lt;=$B$41+$C$41+$D$41,24+(A48-$B$41-$C$41)/MAX(1,$D$41/12),IF(A48&lt;=$B$41+$C$41+$D$41+$E$41,36+(A48-$B$41-$C$41-$D$41)/MAX(1,$E$41/12),IF(A48&lt;=$B$41+$C$41+$D$41+$E$41+$F$41,48+(A48-$B$41-$C$41-$D$41-$E$41)/MAX(1,$F$41/12),60))))))</f>
-        <v>23.82020303341214</v>
+        <v>22.136073476970324</v>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
@@ -13281,7 +13281,7 @@
       </c>
       <c r="B49" s="44">
         <f>MIN(60,IF(A49&lt;=$B$41,A49/MAX(1,$B$41/12),IF(A49&lt;=$B$41+$C$41,12+(A49-$B$41)/MAX(1,$C$41/12),IF(A49&lt;=$B$41+$C$41+$D$41,24+(A49-$B$41-$C$41)/MAX(1,$D$41/12),IF(A49&lt;=$B$41+$C$41+$D$41+$E$41,36+(A49-$B$41-$C$41-$D$41)/MAX(1,$E$41/12),IF(A49&lt;=$B$41+$C$41+$D$41+$E$41+$F$41,48+(A49-$B$41-$C$41-$D$41-$E$41)/MAX(1,$F$41/12),60))))))</f>
-        <v>29.48611327720349</v>
+        <v>27.810087744221917</v>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
@@ -13300,7 +13300,7 @@
       </c>
       <c r="B50" s="44">
         <f>MIN(60,IF(A50&lt;=$B$41,A50/MAX(1,$B$41/12),IF(A50&lt;=$B$41+$C$41,12+(A50-$B$41)/MAX(1,$C$41/12),IF(A50&lt;=$B$41+$C$41+$D$41,24+(A50-$B$41-$C$41)/MAX(1,$D$41/12),IF(A50&lt;=$B$41+$C$41+$D$41+$E$41,36+(A50-$B$41-$C$41-$D$41)/MAX(1,$E$41/12),IF(A50&lt;=$B$41+$C$41+$D$41+$E$41+$F$41,48+(A50-$B$41-$C$41-$D$41-$E$41)/MAX(1,$F$41/12),60))))))</f>
-        <v>35.14910354595746</v>
+        <v>33.931652594614356</v>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
       </c>
       <c r="B4" s="24">
         <f>Combined!D21</f>
-        <v>7620</v>
+        <v>8580</v>
       </c>
       <c r="C4" s="7" t="n"/>
       <c r="D4" s="7" t="n"/>
@@ -13424,7 +13424,7 @@
       </c>
       <c r="B5" s="45">
         <f>Combined!D29</f>
-        <v>60.56069879265092</v>
+        <v>58.212630675990674</v>
       </c>
       <c r="C5" s="7" t="n"/>
       <c r="D5" s="7" t="n"/>
@@ -13441,7 +13441,7 @@
       </c>
       <c r="B6" s="26">
         <f>Combined!D65</f>
-        <v>779325.799232</v>
+        <v>793506.833216</v>
       </c>
       <c r="C6" s="7" t="n"/>
       <c r="D6" s="7" t="n"/>

--- a/docs/financial-model-5yr-v2.xlsx
+++ b/docs/financial-model-5yr-v2.xlsx
@@ -634,7 +634,7 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>4. Results (2026-10-01: metros as explicit drivers, a Base team of four, founder pay inside the functions). Base revenue $36k / $172k / $499k / $1.11M / $2.11M; EBITDA -$192k / -$365k / -$294k / +$30k / +$696k, so breakeven in year four and about $851k of cumulative capital at the low point, in year three. Fundable revenue $80k / $363k / $1.38M / $3.89M / $9.29M with 40 metros and a team of 18, EBITDA positive in year four. Conservative: $17k growing to $313k with 5 metros, not profitable in five years. Costs, EBITDA and cash are on the Combined sheet; docs/funding/cfo-memo-ask-and-spend.md carries the discussion.</t>
+          <t>4. Results (2026-10-01: metros as explicit drivers, a Base team of two full-time founders and one part-time founder (unpaid in the plan), plus two hires, founder pay inside the functions). Base revenue $36k / $172k / $499k / $1.11M / $2.11M; EBITDA -$192k / -$365k / -$294k / +$30k / +$696k, so breakeven in year four and about $851k of cumulative capital at the low point, in year three. Fundable revenue $80k / $363k / $1.38M / $3.89M / $9.29M with 40 metros and a team of 18, EBITDA positive in year four. Conservative: $17k growing to $313k with 5 metros, not profitable in five years. Costs, EBITDA and cash are on the Combined sheet; docs/funding/cfo-memo-ask-and-spend.md carries the discussion.</t>
         </is>
       </c>
     </row>
@@ -4593,7 +4593,7 @@
       </c>
       <c r="H171" s="8" t="inlineStr">
         <is>
-          <t>No full-time employee before both founders are full time. Base is a four-person company: one community &amp; partnerships lead from month 18 (half time in Y2, full from Y3); metros run themselves</t>
+          <t>No full-time employee before both founders are full time. Base is two full-time founders plus one part-time founder (Patricia Sinay, no pay in the model) and two hires: one community &amp; partnerships lead from month 18 (half time in Y2, full from Y3); metros run themselves</t>
         </is>
       </c>
     </row>
@@ -12831,7 +12831,7 @@
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>Founders (Rick: product &amp; engineering; Haley: community &amp; programs)</t>
+          <t>Full-time founders (Rick: product &amp; engineering; Haley: chief creative &amp; programs)</t>
         </is>
       </c>
       <c r="B30" s="7" t="n"/>
@@ -13086,14 +13086,28 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="7" t="n"/>
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>Part-time founder (Patricia Sinay, civic partnerships): people, not in FTE or cost</t>
+        </is>
+      </c>
       <c r="B39" s="7" t="n"/>
       <c r="C39" s="7" t="n"/>
-      <c r="D39" s="7" t="n"/>
-      <c r="E39" s="7" t="n"/>
-      <c r="F39" s="7" t="n"/>
-      <c r="G39" s="7" t="n"/>
-      <c r="H39" s="7" t="n"/>
+      <c r="D39" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="40" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
